--- a/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -425,13 +425,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H390"/>
+  <dimension ref="A1:G393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -451,20 +451,15 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>PREVIOUS</t>
+          <t>CONSENSUS</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CONSENSUS</t>
+          <t>FORECAST</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>FORECAST</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>TIER</t>
         </is>
@@ -491,18 +486,13 @@
           <t>7.47%</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>8.89%</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
         <is>
           <t>9.4%</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="G2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -527,18 +517,13 @@
           <t>-2.78%</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>-3.79%</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
         <is>
           <t>-3.5%</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="G3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -565,20 +550,15 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.50%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2.50%</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="G4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -603,18 +583,13 @@
           <t>2.51%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2.14%</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="G5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -641,20 +616,15 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>0.1%</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
+      <c r="G6" t="n">
         <v>2</v>
       </c>
     </row>
@@ -679,18 +649,13 @@
           <t>0.9%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
         <is>
           <t>0.1%</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
+      <c r="G7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -715,14 +680,9 @@
           <t>2.570%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2.570%</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="n">
+      <c r="G8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -749,7 +709,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -757,12 +717,7 @@
           <t>0.2%</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
+      <c r="G9" t="n">
         <v>3</v>
       </c>
     </row>
@@ -789,7 +744,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -797,12 +752,7 @@
           <t>2.9%</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2.9%</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
+      <c r="G10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -829,20 +779,15 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
           <t>3.0%</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="G11" t="n">
         <v>3</v>
       </c>
     </row>
@@ -869,7 +814,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -877,12 +822,7 @@
           <t>2.4%</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2.4%</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
+      <c r="G12" t="n">
         <v>3</v>
       </c>
     </row>
@@ -909,7 +849,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -917,12 +857,7 @@
           <t>-0.1%</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
+      <c r="G13" t="n">
         <v>3</v>
       </c>
     </row>
@@ -949,20 +884,15 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CNY990B</t>
+          <t>CNY800B</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CNY800B</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
           <t>CNY1000.0B</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="G14" t="n">
         <v>2</v>
       </c>
     </row>
@@ -989,20 +919,15 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>7.2%</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
           <t>7.5%</t>
         </is>
       </c>
-      <c r="H15" t="n">
+      <c r="G15" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1029,20 +954,15 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>7.3%</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
           <t>7.4%</t>
         </is>
       </c>
-      <c r="H16" t="n">
+      <c r="G16" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1069,20 +989,15 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CNY2860B</t>
+          <t>CNY6400B</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CNY6400B</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
           <t>CNY6200.0B</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="G17" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1107,18 +1022,13 @@
           <t>$180.7B</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>$147.6B</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
         <is>
           <t>$ 100B</t>
         </is>
       </c>
-      <c r="H18" t="n">
+      <c r="G18" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1145,20 +1055,15 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="H19" t="n">
+      <c r="G19" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1185,20 +1090,15 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
           <t>1.1%</t>
         </is>
       </c>
-      <c r="H20" t="n">
+      <c r="G20" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1225,20 +1125,15 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H21" t="n">
+      <c r="G21" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1273,12 +1168,7 @@
           <t>0.9%</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
+      <c r="G22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1313,12 +1203,7 @@
           <t>21%</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>21%</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
+      <c r="G23" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1343,14 +1228,9 @@
           <t>10.3%</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>10.8%</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="n">
+      <c r="G24" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1375,14 +1255,9 @@
           <t>$638.26B</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>$630.61B</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="n">
+      <c r="G25" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1407,14 +1282,9 @@
           <t>11.4%</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>11.5%</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="n">
+      <c r="G26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1437,8 +1307,7 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="n">
+      <c r="G27" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1463,18 +1332,13 @@
           <t>-0.5%</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
         <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="H28" t="n">
+      <c r="G28" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1499,18 +1363,13 @@
           <t>4.2%</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
         <is>
           <t>3.7%</t>
         </is>
       </c>
-      <c r="H29" t="n">
+      <c r="G29" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1535,18 +1394,13 @@
           <t>1.9%</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
         <is>
           <t>2.8%</t>
         </is>
       </c>
-      <c r="H30" t="n">
+      <c r="G30" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1573,7 +1427,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1581,12 +1435,7 @@
           <t>0.3%</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
+      <c r="G31" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1613,20 +1462,15 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="H32" t="n">
+      <c r="G32" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1651,18 +1495,13 @@
           <t>2.7%</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
         <is>
           <t>2.3%</t>
         </is>
       </c>
-      <c r="H33" t="n">
+      <c r="G33" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1689,7 +1528,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1697,12 +1536,7 @@
           <t>0.3%</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
+      <c r="G34" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1729,20 +1563,15 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="H35" t="n">
+      <c r="G35" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1769,7 +1598,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1777,12 +1606,7 @@
           <t>0.2%</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
+      <c r="G36" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1807,18 +1631,13 @@
           <t>135.5K</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>161.5K</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
         <is>
           <t>153K</t>
         </is>
       </c>
-      <c r="H37" t="n">
+      <c r="G37" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1850,15 +1669,10 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.7%</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
           <t>0.6%</t>
         </is>
       </c>
-      <c r="H38" t="n">
+      <c r="G38" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1885,20 +1699,15 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="H39" t="n">
+      <c r="G39" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1925,7 +1734,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1933,12 +1742,7 @@
           <t>0.3%</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
+      <c r="G40" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1965,20 +1769,15 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>77.7%</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
           <t>77.4%</t>
         </is>
       </c>
-      <c r="H41" t="n">
+      <c r="G41" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2003,18 +1802,13 @@
           <t>2%</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
         <is>
           <t>0.9%</t>
         </is>
       </c>
-      <c r="H42" t="n">
+      <c r="G42" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2041,20 +1835,15 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="H43" t="n">
+      <c r="G43" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2079,18 +1868,13 @@
           <t>1%</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
         <is>
           <t>0.8%</t>
         </is>
       </c>
-      <c r="H44" t="n">
+      <c r="G44" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2117,7 +1901,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2125,12 +1909,7 @@
           <t>0.2%</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="H45" t="n">
+      <c r="G45" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2157,20 +1936,15 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
           <t>-0.1%</t>
         </is>
       </c>
-      <c r="H46" t="n">
+      <c r="G46" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2193,8 +1967,7 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="n">
+      <c r="G47" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2221,20 +1994,15 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
           <t>9.9%</t>
         </is>
       </c>
-      <c r="H48" t="n">
+      <c r="G48" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2266,15 +2034,10 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1.3%</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
           <t>1.2%</t>
         </is>
       </c>
-      <c r="H49" t="n">
+      <c r="G49" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2299,14 +2062,9 @@
           <t>588</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>586</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="n">
+      <c r="G50" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2331,14 +2089,9 @@
           <t>481</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="n">
+      <c r="G51" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2361,8 +2114,7 @@
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="n">
+      <c r="G52" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2385,20 +2137,15 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="H53" t="n">
+      <c r="G53" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2421,20 +2168,15 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
           <t>2.1%</t>
         </is>
       </c>
-      <c r="H54" t="n">
+      <c r="G54" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2457,20 +2199,15 @@
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="H55" t="n">
+      <c r="G55" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2493,20 +2230,15 @@
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="H56" t="n">
+      <c r="G56" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2527,18 +2259,13 @@
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
         <is>
           <t>2.6%</t>
         </is>
       </c>
-      <c r="H57" t="n">
+      <c r="G57" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2561,20 +2288,15 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="H58" t="n">
+      <c r="G58" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2597,20 +2319,15 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-2.5%</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
           <t>4.8%</t>
         </is>
       </c>
-      <c r="H59" t="n">
+      <c r="G59" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2633,20 +2350,15 @@
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
           <t>1.1%</t>
         </is>
       </c>
-      <c r="H60" t="n">
+      <c r="G60" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2667,18 +2379,13 @@
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>$3.85B</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
         <is>
           <t>$4.5B</t>
         </is>
       </c>
-      <c r="H61" t="n">
+      <c r="G61" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2701,20 +2408,15 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>$2.24B</t>
+          <t>$1.91B</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>$1.91B</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
           <t>$2.2B</t>
         </is>
       </c>
-      <c r="H62" t="n">
+      <c r="G62" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2737,16 +2439,11 @@
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>4.78%</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
           <t>6.99%</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="n">
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2769,16 +2466,11 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>11.07%</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
           <t>9.95%</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="n">
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2801,8 +2493,7 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="n">
+      <c r="G65" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2830,15 +2521,10 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
           <t>2.0%</t>
         </is>
       </c>
-      <c r="H66" t="n">
+      <c r="G66" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2861,7 +2547,7 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2869,12 +2555,7 @@
           <t>0.2%</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="H67" t="n">
+      <c r="G67" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2895,18 +2576,13 @@
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>10.5%</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
         <is>
           <t>12.0%</t>
         </is>
       </c>
-      <c r="H68" t="n">
+      <c r="G68" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2927,18 +2603,13 @@
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
         <is>
           <t>1.3%</t>
         </is>
       </c>
-      <c r="H69" t="n">
+      <c r="G69" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2959,18 +2630,13 @@
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>-2.7%</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr">
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
         <is>
           <t>-1.6%</t>
         </is>
       </c>
-      <c r="H70" t="n">
+      <c r="G70" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2993,7 +2659,7 @@
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3001,12 +2667,7 @@
           <t>0.3%</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="H71" t="n">
+      <c r="G71" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3029,20 +2690,15 @@
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
           <t>0.1%</t>
         </is>
       </c>
-      <c r="H72" t="n">
+      <c r="G72" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3063,18 +2719,13 @@
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>-1.9%</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr">
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
         <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="H73" t="n">
+      <c r="G73" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3095,14 +2746,9 @@
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>2.840%</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="n">
+      <c r="G74" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3125,20 +2771,15 @@
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>€4.218B</t>
+          <t>€4.35B</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>€4.35B</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
           <t>€4.5B</t>
         </is>
       </c>
-      <c r="H75" t="n">
+      <c r="G75" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3159,18 +2800,13 @@
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>€-5.13B</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr">
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
         <is>
           <t>€ -4.9B</t>
         </is>
       </c>
-      <c r="H76" t="n">
+      <c r="G76" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3191,18 +2827,13 @@
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>€16.4B</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr">
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
         <is>
           <t>€ 33B</t>
         </is>
       </c>
-      <c r="H77" t="n">
+      <c r="G77" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3223,14 +2854,9 @@
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>2.4019%</t>
-        </is>
-      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="n">
+      <c r="G78" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3253,8 +2879,7 @@
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="n">
+      <c r="G79" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3275,18 +2900,13 @@
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr">
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
         <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="H80" t="n">
+      <c r="G80" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3309,20 +2929,15 @@
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>231.5K</t>
+          <t>250K</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>250K</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
           <t>220.0K</t>
         </is>
       </c>
-      <c r="H81" t="n">
+      <c r="G81" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3345,16 +2960,11 @@
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>C$16.4B</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
           <t>C$14.23B</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="n">
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3375,14 +2985,9 @@
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>C$17.85B</t>
-        </is>
-      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="n">
+      <c r="G83" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3403,14 +3008,9 @@
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>2.224%</t>
-        </is>
-      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="n">
+      <c r="G84" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3431,14 +3031,9 @@
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>2.450%</t>
-        </is>
-      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="n">
+      <c r="G85" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3459,14 +3054,9 @@
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>2.358%</t>
-        </is>
-      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="n">
+      <c r="G86" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3489,8 +3079,7 @@
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="n">
+      <c r="G87" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3513,8 +3102,7 @@
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="n">
+      <c r="G88" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3537,8 +3125,7 @@
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="n">
+      <c r="G89" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3561,8 +3148,7 @@
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="n">
+      <c r="G90" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3585,7 +3171,7 @@
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3593,12 +3179,7 @@
           <t>4.1%</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="H91" t="n">
+      <c r="G91" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3619,14 +3200,9 @@
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>1.983%</t>
-        </is>
-      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="n">
+      <c r="G92" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3649,8 +3225,7 @@
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="n">
+      <c r="G93" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3673,8 +3248,7 @@
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="n">
+      <c r="G94" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3691,18 +3265,13 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>$59.95B</t>
-        </is>
-      </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="n">
+      <c r="G95" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3725,8 +3294,7 @@
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="n">
+      <c r="G96" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3743,18 +3311,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>$38.01B</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="n">
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>$-24.0B</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3771,22 +3338,13 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>$-21.94B</t>
-        </is>
-      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>$-24.0B</t>
-        </is>
-      </c>
-      <c r="H98" t="n">
+      <c r="G98" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3803,22 +3361,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Budget BalanceJAN</t>
+          <t>Auto Sales YoYJAN</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>TRY-829.2B</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>TRY-150.0B</t>
-        </is>
-      </c>
-      <c r="H99" t="n">
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>6.0%</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3830,27 +3383,18 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Auto Sales YoYJAN</t>
+          <t>RBA Press Conference</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>7.3%</t>
-        </is>
-      </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>6.0%</t>
-        </is>
-      </c>
-      <c r="H100" t="n">
+      <c r="G100" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3867,22 +3411,17 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Auto Production YoYJAN</t>
+          <t>Budget BalanceJAN</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
-      <c r="H101" t="n">
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>TRY-150.0B</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3894,19 +3433,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>RBA Press Conference</t>
+          <t>Auto Production YoYJAN</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="n">
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3927,14 +3469,9 @@
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>2.99%</t>
-        </is>
-      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="n">
+      <c r="G103" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3955,14 +3492,9 @@
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>2.98%</t>
-        </is>
-      </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="n">
+      <c r="G104" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3985,20 +3517,15 @@
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0.7K</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
           <t>7.0K</t>
         </is>
       </c>
-      <c r="H105" t="n">
+      <c r="G105" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4015,22 +3542,17 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>HMRC Payrolls ChangeJAN</t>
+          <t>Average Earnings excl. Bonus (3Mo/Yr)DEC</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>-47K</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>-55.0K</t>
-        </is>
-      </c>
-      <c r="H106" t="n">
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>5.9%</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4051,18 +3573,13 @@
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>36K</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr">
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
         <is>
           <t>-130K</t>
         </is>
       </c>
-      <c r="H107" t="n">
+      <c r="G107" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4079,22 +3596,17 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Average Earnings excl. Bonus (3Mo/Yr)DEC</t>
+          <t>HMRC Payrolls ChangeJAN</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>5.6%</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>5.9%</t>
-        </is>
-      </c>
-      <c r="H108" t="n">
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>-55.0K</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4117,20 +3629,15 @@
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
+          <t>4.5%</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
           <t>4.4%</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
-      <c r="H109" t="n">
+      <c r="G109" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4153,7 +3660,7 @@
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4161,12 +3668,7 @@
           <t>5.9%</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>5.9%</t>
-        </is>
-      </c>
-      <c r="H110" t="n">
+      <c r="G110" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4189,7 +3691,7 @@
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4197,12 +3699,7 @@
           <t>-0.1%</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="H111" t="n">
+      <c r="G111" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4225,7 +3722,7 @@
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4233,12 +3730,7 @@
           <t>1.4%</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>1.4%</t>
-        </is>
-      </c>
-      <c r="H112" t="n">
+      <c r="G112" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4261,7 +3753,7 @@
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4269,12 +3761,7 @@
           <t>-0.2%</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="H113" t="n">
+      <c r="G113" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4305,12 +3792,7 @@
           <t>1.8%</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="H114" t="n">
+      <c r="G114" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4327,19 +3809,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Labour Productivity QoQ PrelQ4</t>
+          <t>BoE Gov Bailey Speech</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="H115" t="n">
-        <v>3</v>
+      <c r="G115" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="116">
@@ -4350,28 +3827,23 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Unemployment RateQ4</t>
+          <t>Labour Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>32.1%</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>32.4%</t>
-        </is>
-      </c>
-      <c r="H116" t="n">
-        <v>2</v>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="117">
@@ -4387,23 +3859,18 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Unemployed PersonsQ4</t>
+          <t>Unemployment RateQ4</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>8.011M</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>8.1M</t>
-        </is>
-      </c>
-      <c r="H117" t="n">
-        <v>3</v>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>32.4%</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="118">
@@ -4414,20 +3881,23 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>BoE Gov Bailey Speech</t>
+          <t>Unemployed PersonsQ4</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="n">
-        <v>2</v>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>8.1M</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="119">
@@ -4449,7 +3919,7 @@
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4457,12 +3927,7 @@
           <t>-0.8%</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
-      <c r="H119" t="n">
+      <c r="G119" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4485,8 +3950,7 @@
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="n">
+      <c r="G120" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4509,7 +3973,7 @@
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>-90.4</t>
+          <t>-89</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4517,12 +3981,7 @@
           <t>-89</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>-89</t>
-        </is>
-      </c>
-      <c r="H121" t="n">
+      <c r="G121" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4545,20 +4004,15 @@
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H122" t="n">
+      <c r="G122" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4579,18 +4033,13 @@
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr">
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H123" t="n">
+      <c r="G123" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4611,14 +4060,9 @@
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>2.26%</t>
-        </is>
-      </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="n">
+      <c r="G124" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4639,18 +4083,13 @@
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr">
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
         <is>
           <t>1.8%</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="H125" t="n">
+      <c r="G125" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4671,18 +4110,13 @@
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr">
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
         <is>
           <t>1.7%</t>
         </is>
       </c>
-      <c r="H126" t="n">
+      <c r="G126" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4705,20 +4139,15 @@
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="H127" t="n">
+      <c r="G127" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4739,18 +4168,13 @@
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr">
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
         <is>
           <t>-0.1%</t>
         </is>
       </c>
-      <c r="H128" t="n">
+      <c r="G128" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4781,12 +4205,7 @@
           <t>2.4%</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>2.4%</t>
-        </is>
-      </c>
-      <c r="H129" t="n">
+      <c r="G129" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4809,20 +4228,15 @@
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="H130" t="n">
+      <c r="G130" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4845,20 +4259,15 @@
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>-12.6</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H131" t="n">
+      <c r="G131" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4881,8 +4290,7 @@
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="n">
+      <c r="G132" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4910,15 +4318,10 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="H133" t="n">
+      <c r="G133" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4930,20 +4333,19 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Bundesbank Balz Speech</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="n">
-        <v>2</v>
+      <c r="G134" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="135">
@@ -4954,20 +4356,19 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bundesbank Balz Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="n">
-        <v>3</v>
+      <c r="G135" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="136">
@@ -4987,14 +4388,9 @@
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>4.225%</t>
-        </is>
-      </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="n">
+      <c r="G136" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5015,14 +4411,9 @@
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>4.185%</t>
-        </is>
-      </c>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="n">
+      <c r="G137" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5045,8 +4436,7 @@
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="n">
+      <c r="G138" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5069,8 +4459,7 @@
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="n">
+      <c r="G139" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5091,14 +4480,9 @@
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>4.025%</t>
-        </is>
-      </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="n">
+      <c r="G140" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5119,18 +4503,13 @@
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>$1666M</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr">
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
         <is>
           <t>$1500.0M</t>
         </is>
       </c>
-      <c r="H141" t="n">
+      <c r="G141" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5147,19 +4526,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>$79B</t>
-        </is>
-      </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="n">
-        <v>2</v>
+      <c r="G142" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="143">
@@ -5175,19 +4549,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>$-15.8B</t>
-        </is>
-      </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="n">
-        <v>3</v>
+      <c r="G143" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="144">
@@ -5203,18 +4572,13 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>$159.9B</t>
-        </is>
-      </c>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="n">
+      <c r="G144" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5231,27 +4595,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Imports YoYJAN</t>
+          <t>Machinery Orders YoYDEC</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>9.7%</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>2.0%</t>
-        </is>
-      </c>
-      <c r="H145" t="n">
-        <v>3</v>
+          <t>7.6%</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -5267,27 +4626,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Machinery Orders YoYDEC</t>
+          <t>Imports YoYJAN</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>6.9%</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>7.6%</t>
-        </is>
-      </c>
-      <c r="H146" t="n">
-        <v>2</v>
+          <t>2.0%</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="147">
@@ -5309,20 +4663,15 @@
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
           <t>2.2%</t>
         </is>
       </c>
-      <c r="H147" t="n">
+      <c r="G147" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5345,20 +4694,15 @@
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>¥130.9B</t>
+          <t>¥-2104B</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>¥-2104B</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
           <t>¥-1400.0B</t>
         </is>
       </c>
-      <c r="H148" t="n">
+      <c r="G148" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5381,20 +4725,15 @@
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>7.9%</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
           <t>3.0%</t>
         </is>
       </c>
-      <c r="H149" t="n">
+      <c r="G149" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5415,18 +4754,13 @@
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr">
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
         <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="H150" t="n">
+      <c r="G150" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5449,8 +4783,7 @@
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="n">
+      <c r="G151" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5478,15 +4811,10 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="H152" t="n">
+      <c r="G152" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5509,20 +4837,15 @@
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
           <t>3.3%</t>
         </is>
       </c>
-      <c r="H153" t="n">
+      <c r="G153" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5543,18 +4866,13 @@
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>-5.3%</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr">
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
         <is>
           <t>-5.0%</t>
         </is>
       </c>
-      <c r="H154" t="n">
+      <c r="G154" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5575,14 +4893,9 @@
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>0.5429%</t>
-        </is>
-      </c>
+      <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
-      <c r="H155" t="n">
+      <c r="G155" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5605,8 +4918,7 @@
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="n">
+      <c r="G156" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5623,26 +4935,17 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Retail Price Index YoYJAN</t>
+          <t>Retail Price Index MoMJAN</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
+      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="H157" t="n">
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5663,18 +4966,13 @@
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr">
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr">
         <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="H158" t="n">
+      <c r="G158" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5697,20 +4995,15 @@
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="H159" t="n">
+      <c r="G159" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5731,18 +5024,13 @@
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>-1.5%</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr">
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
         <is>
           <t>-0.8%</t>
         </is>
       </c>
-      <c r="H160" t="n">
+      <c r="G160" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5765,20 +5053,15 @@
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>0.7%</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="H161" t="n">
+      <c r="G161" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5799,18 +5082,13 @@
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr">
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
         <is>
           <t>1.3%</t>
         </is>
       </c>
-      <c r="H162" t="n">
+      <c r="G162" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5827,23 +5105,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Retail Price Index MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="H163" t="n">
-        <v>3</v>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="164">
@@ -5863,18 +5140,13 @@
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr">
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
         <is>
           <t>-0.7%</t>
         </is>
       </c>
-      <c r="H164" t="n">
+      <c r="G164" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5895,18 +5167,13 @@
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr">
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
         <is>
           <t>-0.3%</t>
         </is>
       </c>
-      <c r="H165" t="n">
+      <c r="G165" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5923,27 +5190,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="H166" t="n">
-        <v>1</v>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="167">
@@ -5959,22 +5221,21 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>PPI Core Output MoMJAN</t>
+          <t>Retail Price Index YoYJAN</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="H167" t="n">
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5991,27 +5252,18 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>PPI Core Output MoMJAN</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="H168" t="n">
-        <v>2</v>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="169">
@@ -6031,18 +5283,13 @@
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>10.39%</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr">
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
         <is>
           <t>10.5%</t>
         </is>
       </c>
-      <c r="H169" t="n">
+      <c r="G169" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6059,26 +5306,21 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Deposit Facility RateFEB</t>
+          <t>Lending Facility RateFEB</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="H170" t="n">
+          <t>6.5%</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6095,26 +5337,21 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Lending Facility RateFEB</t>
+          <t>Deposit Facility RateFEB</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>6.5%</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>6.5%</t>
-        </is>
-      </c>
-      <c r="H171" t="n">
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6145,12 +5382,7 @@
           <t>5.75%</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>5.75%</t>
-        </is>
-      </c>
-      <c r="H172" t="n">
+      <c r="G172" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6173,8 +5405,7 @@
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr"/>
-      <c r="G173" t="inlineStr"/>
-      <c r="H173" t="n">
+      <c r="G173" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6195,18 +5426,13 @@
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr">
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
         <is>
           <t>0.1%</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="H174" t="n">
+      <c r="G174" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6227,18 +5453,13 @@
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr">
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
         <is>
           <t>3.2%</t>
         </is>
       </c>
-      <c r="H175" t="n">
+      <c r="G175" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6259,18 +5480,13 @@
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr">
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
         <is>
           <t>0.1%</t>
         </is>
       </c>
-      <c r="H176" t="n">
+      <c r="G176" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6291,18 +5507,13 @@
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr">
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
         <is>
           <t>3.6%</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="H177" t="n">
+      <c r="G177" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6323,18 +5534,13 @@
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>€34.6B</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr">
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr">
         <is>
           <t>€32B</t>
         </is>
       </c>
-      <c r="H178" t="n">
+      <c r="G178" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6357,7 +5563,7 @@
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>€27B</t>
+          <t>€30B</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6365,12 +5571,7 @@
           <t>€30B</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>€30B</t>
-        </is>
-      </c>
-      <c r="H179" t="n">
+      <c r="G179" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6382,27 +5583,18 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Current AccountDEC</t>
+          <t>4-Year Treasury Gilt Auction</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>€-332M</t>
-        </is>
-      </c>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>€ 3780M</t>
-        </is>
-      </c>
-      <c r="H180" t="n">
+      <c r="G180" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6414,23 +5606,22 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>4-Year Treasury Gilt Auction</t>
+          <t>Current AccountDEC</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>4.384%</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
-      <c r="H181" t="n">
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>€ 3780M</t>
+        </is>
+      </c>
+      <c r="G181" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6451,14 +5642,9 @@
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>2.54%</t>
-        </is>
-      </c>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr"/>
-      <c r="G182" t="inlineStr"/>
-      <c r="H182" t="n">
+      <c r="G182" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6475,22 +5661,17 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>1.3%</t>
-        </is>
-      </c>
-      <c r="H183" t="n">
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="G183" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6507,22 +5688,17 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>7.7%</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="H184" t="n">
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="G184" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6543,14 +5719,9 @@
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>2.487%</t>
-        </is>
-      </c>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr"/>
-      <c r="H185" t="n">
+      <c r="G185" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6571,14 +5742,9 @@
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>2.350%</t>
-        </is>
-      </c>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="n">
+      <c r="G186" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6599,14 +5765,9 @@
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>9.6%</t>
-        </is>
-      </c>
+      <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr"/>
-      <c r="H187" t="n">
+      <c r="G187" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6623,19 +5784,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>640.6</t>
-        </is>
-      </c>
+      <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" t="n">
-        <v>3</v>
+      <c r="G188" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="189">
@@ -6651,18 +5807,13 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>230.0</t>
-        </is>
-      </c>
+      <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr"/>
-      <c r="H189" t="n">
+      <c r="G189" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6679,18 +5830,13 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>153.1</t>
-        </is>
-      </c>
+      <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr"/>
-      <c r="H190" t="n">
+      <c r="G190" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6707,19 +5853,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>6.95%</t>
-        </is>
-      </c>
+      <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr"/>
-      <c r="H191" t="n">
-        <v>2</v>
+      <c r="G191" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="192">
@@ -6735,18 +5876,13 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr"/>
-      <c r="H192" t="n">
+      <c r="G192" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6763,23 +5899,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
-      <c r="H193" t="n">
-        <v>2</v>
+          <t>1.39M</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>1.35M</t>
+        </is>
+      </c>
+      <c r="G193" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="194">
@@ -6795,27 +5930,18 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>1.499M</t>
-        </is>
-      </c>
+      <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
-          <t>1.39M</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>1.35M</t>
-        </is>
-      </c>
-      <c r="H194" t="n">
-        <v>1</v>
+          <t>-9.0%</t>
+        </is>
+      </c>
+      <c r="G194" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="195">
@@ -6831,22 +5957,17 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>15.8%</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr"/>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>-9.0%</t>
-        </is>
-      </c>
-      <c r="H195" t="n">
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="G195" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6869,20 +5990,15 @@
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
-          <t>1.482M</t>
+          <t>1.45M</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>1.45M</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
           <t>1.47M</t>
         </is>
       </c>
-      <c r="H196" t="n">
+      <c r="G196" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6903,14 +6019,9 @@
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>5.3%</t>
-        </is>
-      </c>
+      <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
-      <c r="G197" t="inlineStr"/>
-      <c r="H197" t="n">
+      <c r="G197" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6931,14 +6042,13 @@
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
-      <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr">
+      <c r="E198" t="inlineStr">
         <is>
           <t>$50 million</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr"/>
-      <c r="H198" t="n">
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6959,18 +6069,13 @@
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr">
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr">
         <is>
           <t>0.6%</t>
         </is>
       </c>
-      <c r="H199" t="n">
+      <c r="G199" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6991,18 +6096,13 @@
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>7.9%</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr">
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr">
         <is>
           <t>8.2%</t>
         </is>
       </c>
-      <c r="H200" t="n">
+      <c r="G200" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7023,14 +6123,9 @@
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>4.230%</t>
-        </is>
-      </c>
+      <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr"/>
-      <c r="G201" t="inlineStr"/>
-      <c r="H201" t="n">
+      <c r="G201" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7051,18 +6146,13 @@
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr">
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr">
         <is>
           <t>48.8</t>
         </is>
       </c>
-      <c r="H202" t="n">
+      <c r="G202" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7083,14 +6173,9 @@
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>4.900%</t>
-        </is>
-      </c>
+      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr"/>
-      <c r="G203" t="inlineStr"/>
-      <c r="H203" t="n">
+      <c r="G203" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7113,8 +6198,7 @@
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr"/>
-      <c r="G204" t="inlineStr"/>
-      <c r="H204" t="n">
+      <c r="G204" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7131,23 +6215,18 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>1.7%</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr"/>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="H205" t="n">
-        <v>3</v>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="G205" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="206">
@@ -7163,23 +6242,18 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Consumer ConfidenceFEB</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>91.2</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr"/>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="H206" t="n">
-        <v>2</v>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="G206" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="207">
@@ -7195,22 +6269,17 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr"/>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="H207" t="n">
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="G207" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7231,14 +6300,9 @@
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>9.043M</t>
-        </is>
-      </c>
+      <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr"/>
-      <c r="G208" t="inlineStr"/>
-      <c r="H208" t="n">
+      <c r="G208" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7261,8 +6325,7 @@
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr"/>
-      <c r="G209" t="inlineStr"/>
-      <c r="H209" t="n">
+      <c r="G209" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7283,14 +6346,9 @@
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>¥1752.9B</t>
-        </is>
-      </c>
+      <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr"/>
-      <c r="G210" t="inlineStr"/>
-      <c r="H210" t="n">
+      <c r="G210" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7311,14 +6369,9 @@
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>¥-384.4B</t>
-        </is>
-      </c>
+      <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr"/>
-      <c r="G211" t="inlineStr"/>
-      <c r="H211" t="n">
+      <c r="G211" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7341,20 +6394,15 @@
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
           <t>4.0%</t>
         </is>
       </c>
-      <c r="H212" t="n">
+      <c r="G212" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7377,20 +6425,15 @@
       <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr">
         <is>
-          <t>56.3K</t>
+          <t>20K</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>20K</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
           <t>23.0K</t>
         </is>
       </c>
-      <c r="H213" t="n">
+      <c r="G213" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7411,18 +6454,13 @@
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>-23.7K</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr"/>
-      <c r="G214" t="inlineStr">
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr">
         <is>
           <t>33.0K</t>
         </is>
       </c>
-      <c r="H214" t="n">
+      <c r="G214" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7443,18 +6481,13 @@
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>80K</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr"/>
-      <c r="G215" t="inlineStr">
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr">
         <is>
           <t>-10.0K</t>
         </is>
       </c>
-      <c r="H215" t="n">
+      <c r="G215" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7482,15 +6515,10 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>67.1%</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
           <t>67.0%</t>
         </is>
       </c>
-      <c r="H216" t="n">
+      <c r="G216" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7511,18 +6539,13 @@
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
-      <c r="E217" t="inlineStr">
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr">
         <is>
           <t>3.1%</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr"/>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
-      <c r="H217" t="n">
+      <c r="G217" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7543,18 +6566,13 @@
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
-      <c r="E218" t="inlineStr">
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr">
         <is>
           <t>3.6%</t>
         </is>
       </c>
-      <c r="F218" t="inlineStr"/>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="H218" t="n">
+      <c r="G218" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7566,23 +6584,22 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>M2 Money Supply YoYJAN</t>
+          <t>Leading Indicator MoMJAN</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr"/>
-      <c r="G219" t="inlineStr"/>
-      <c r="H219" t="n">
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="G219" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7599,22 +6616,13 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Current AccountQ4</t>
+          <t>M2 Money Supply YoYJAN</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>$-2.2B</t>
-        </is>
-      </c>
+      <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr"/>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>$ -0.6B</t>
-        </is>
-      </c>
-      <c r="H220" t="n">
+      <c r="G220" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7626,27 +6634,22 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Leading Indicator MoMJAN</t>
+          <t>Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>2.45%</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr"/>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="H221" t="n">
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="G221" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7658,27 +6661,22 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Consumer ConfidenceJAN</t>
+          <t>Current AccountQ4</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr"/>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>85.5</t>
-        </is>
-      </c>
-      <c r="H222" t="n">
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>$ -0.6B</t>
+        </is>
+      </c>
+      <c r="G222" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7690,27 +6688,22 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr"/>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>1.1%</t>
-        </is>
-      </c>
-      <c r="H223" t="n">
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="G223" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7733,20 +6726,15 @@
       <c r="D224" t="inlineStr"/>
       <c r="E224" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="H224" t="n">
+      <c r="G224" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7758,27 +6746,22 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Consumer ConfidenceFEB</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr"/>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="H225" t="n">
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>1.1%</t>
+        </is>
+      </c>
+      <c r="G225" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7799,18 +6782,13 @@
         </is>
       </c>
       <c r="D226" t="inlineStr"/>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr"/>
-      <c r="G226" t="inlineStr">
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr">
         <is>
           <t>3.2%</t>
         </is>
       </c>
-      <c r="H226" t="n">
+      <c r="G226" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7831,14 +6809,9 @@
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>2.388%</t>
-        </is>
-      </c>
+      <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr"/>
-      <c r="G227" t="inlineStr"/>
-      <c r="H227" t="n">
+      <c r="G227" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7859,14 +6832,9 @@
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>2.763%</t>
-        </is>
-      </c>
+      <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr"/>
-      <c r="G228" t="inlineStr"/>
-      <c r="H228" t="n">
+      <c r="G228" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7887,14 +6855,9 @@
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
+      <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr"/>
-      <c r="G229" t="inlineStr"/>
-      <c r="H229" t="n">
+      <c r="G229" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7915,18 +6878,13 @@
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>1.4%</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr"/>
-      <c r="G230" t="inlineStr">
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr">
         <is>
           <t>-0.5%</t>
         </is>
       </c>
-      <c r="H230" t="n">
+      <c r="G230" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7947,14 +6905,9 @@
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>2.51%</t>
-        </is>
-      </c>
+      <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr"/>
-      <c r="G231" t="inlineStr"/>
-      <c r="H231" t="n">
+      <c r="G231" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7975,14 +6928,9 @@
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>2.74%</t>
-        </is>
-      </c>
+      <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr"/>
-      <c r="G232" t="inlineStr"/>
-      <c r="H232" t="n">
+      <c r="G232" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8003,14 +6951,9 @@
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>2.84%</t>
-        </is>
-      </c>
+      <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr"/>
-      <c r="G233" t="inlineStr"/>
-      <c r="H233" t="n">
+      <c r="G233" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8022,32 +6965,19 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>CBI Industrial Trends OrdersFEB</t>
+          <t>11-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>-34</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>-30</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>-25</t>
-        </is>
-      </c>
-      <c r="H234" t="n">
-        <v>2</v>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="235">
@@ -8058,27 +6988,18 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Building Permits YoYDEC</t>
+          <t>18-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>-2%</t>
-        </is>
-      </c>
+      <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr"/>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>18.0%</t>
-        </is>
-      </c>
-      <c r="H235" t="n">
+      <c r="G235" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8095,14 +7016,13 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>7-Year OATi Auction</t>
+          <t>6-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr"/>
-      <c r="G236" t="inlineStr"/>
-      <c r="H236" t="n">
+      <c r="G236" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8119,18 +7039,13 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>11-Year Index-Linked OAT Auction</t>
+          <t>7-Year OATi Auction</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>1.14%</t>
-        </is>
-      </c>
+      <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr"/>
-      <c r="G237" t="inlineStr"/>
-      <c r="H237" t="n">
+      <c r="G237" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8142,19 +7057,22 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>18-Year Index-Linked OAT Auction</t>
+          <t>Building Permits YoYDEC</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
-      <c r="F238" t="inlineStr"/>
-      <c r="G238" t="inlineStr"/>
-      <c r="H238" t="n">
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>18.0%</t>
+        </is>
+      </c>
+      <c r="G238" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8166,20 +7084,27 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>6-Year Index-Linked OAT Auction</t>
+          <t>CBI Industrial Trends OrdersFEB</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
-      <c r="E239" t="inlineStr"/>
-      <c r="F239" t="inlineStr"/>
-      <c r="G239" t="inlineStr"/>
-      <c r="H239" t="n">
-        <v>3</v>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>-30</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>-25</t>
+        </is>
+      </c>
+      <c r="G239" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="240">
@@ -8199,14 +7124,9 @@
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>$96.93B</t>
-        </is>
-      </c>
+      <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr"/>
-      <c r="G240" t="inlineStr"/>
-      <c r="H240" t="n">
+      <c r="G240" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8227,18 +7147,13 @@
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="F241" t="inlineStr"/>
-      <c r="G241" t="inlineStr">
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr">
         <is>
           <t>-0.4%</t>
         </is>
       </c>
-      <c r="H241" t="n">
+      <c r="G241" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8259,18 +7174,13 @@
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>-1.9%</t>
-        </is>
-      </c>
-      <c r="F242" t="inlineStr"/>
-      <c r="G242" t="inlineStr">
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="H242" t="n">
+      <c r="G242" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8287,27 +7197,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H243" t="n">
-        <v>2</v>
+      <c r="E243" t="inlineStr"/>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="244">
@@ -8327,14 +7224,9 @@
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+      <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr"/>
-      <c r="G244" t="inlineStr"/>
-      <c r="H244" t="n">
+      <c r="G244" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8346,23 +7238,22 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Raw Materials Prices MoMJAN</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="F245" t="inlineStr"/>
-      <c r="G245" t="inlineStr"/>
-      <c r="H245" t="n">
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="G245" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8379,22 +7270,13 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr"/>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
-      <c r="H246" t="n">
+      <c r="G246" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8411,22 +7293,17 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>1850K</t>
-        </is>
-      </c>
-      <c r="F247" t="inlineStr"/>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
-      <c r="H247" t="n">
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
+      <c r="G247" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8443,27 +7320,14 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
-      <c r="H248" t="n">
-        <v>2</v>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="249">
@@ -8474,28 +7338,19 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>New Housing Price Index YoYJAN</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr"/>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="H249" t="n">
-        <v>2</v>
+      <c r="G249" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="250">
@@ -8506,27 +7361,22 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Raw Materials Prices MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>1.3%</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr"/>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="H250" t="n">
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
+      <c r="G250" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8543,22 +7393,17 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr"/>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="H251" t="n">
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="G251" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8570,28 +7415,27 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="F252" t="inlineStr"/>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="H252" t="n">
-        <v>3</v>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
+      <c r="G252" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="253">
@@ -8602,24 +7446,23 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>New Housing Price Index MoMJAN</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>31.9</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr"/>
-      <c r="G253" t="inlineStr"/>
-      <c r="H253" t="n">
-        <v>3</v>
+      <c r="E253" t="inlineStr"/>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G253" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -8635,22 +7478,17 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>New Housing Price Index MoMJAN</t>
+          <t>New Housing Price Index YoYJAN</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="F254" t="inlineStr"/>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="H254" t="n">
+      <c r="E254" t="inlineStr"/>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="G254" t="n">
         <v>2</v>
       </c>
     </row>
@@ -8667,19 +7505,22 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="F255" t="inlineStr"/>
-      <c r="G255" t="inlineStr"/>
-      <c r="H255" t="n">
-        <v>3</v>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G255" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -8695,22 +7536,17 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Raw Materials Prices YoYJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>9.1%</t>
-        </is>
-      </c>
-      <c r="F256" t="inlineStr"/>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>10.0%</t>
-        </is>
-      </c>
-      <c r="H256" t="n">
+      <c r="E256" t="inlineStr"/>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="G256" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8722,23 +7558,22 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Raw Materials Prices YoYJAN</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="F257" t="inlineStr"/>
-      <c r="G257" t="inlineStr"/>
-      <c r="H257" t="n">
+      <c r="E257" t="inlineStr"/>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
+      <c r="G257" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8759,18 +7594,13 @@
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>47.4</t>
-        </is>
-      </c>
-      <c r="F258" t="inlineStr"/>
-      <c r="G258" t="inlineStr">
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="inlineStr">
         <is>
           <t>48.2</t>
         </is>
       </c>
-      <c r="H258" t="n">
+      <c r="G258" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8793,8 +7623,7 @@
       <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr"/>
-      <c r="G259" t="inlineStr"/>
-      <c r="H259" t="n">
+      <c r="G259" t="n">
         <v>2</v>
       </c>
     </row>
@@ -8806,32 +7635,27 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Consumer Confidence FlashFEB</t>
+          <t>CB Leading Index MoMJAN</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
       <c r="E260" t="inlineStr">
         <is>
-          <t>-14.2</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>-14</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>-14.4</t>
-        </is>
-      </c>
-      <c r="H260" t="n">
-        <v>2</v>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G260" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="261">
@@ -8853,8 +7677,7 @@
       <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr"/>
-      <c r="G261" t="inlineStr"/>
-      <c r="H261" t="n">
+      <c r="G261" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8866,32 +7689,27 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>CB Leading Index MoMJAN</t>
+          <t>Consumer Confidence FlashFEB</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H262" t="n">
-        <v>3</v>
+          <t>-14.4</t>
+        </is>
+      </c>
+      <c r="G262" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="263">
@@ -8911,14 +7729,9 @@
         </is>
       </c>
       <c r="D263" t="inlineStr"/>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>-100Bcf</t>
-        </is>
-      </c>
+      <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr"/>
-      <c r="G263" t="inlineStr"/>
-      <c r="H263" t="n">
+      <c r="G263" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8941,8 +7754,7 @@
       <c r="D264" t="inlineStr"/>
       <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr"/>
-      <c r="G264" t="inlineStr"/>
-      <c r="H264" t="n">
+      <c r="G264" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8963,14 +7775,9 @@
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>4.250%</t>
-        </is>
-      </c>
+      <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr"/>
-      <c r="G265" t="inlineStr"/>
-      <c r="H265" t="n">
+      <c r="G265" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8991,14 +7798,9 @@
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>4.240%</t>
-        </is>
-      </c>
+      <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr"/>
-      <c r="G266" t="inlineStr"/>
-      <c r="H266" t="n">
+      <c r="G266" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9015,18 +7817,13 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>0.18M</t>
-        </is>
-      </c>
+      <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr"/>
-      <c r="G267" t="inlineStr"/>
-      <c r="H267" t="n">
+      <c r="G267" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9043,18 +7840,13 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>0.082M</t>
-        </is>
-      </c>
+      <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr"/>
-      <c r="G268" t="inlineStr"/>
-      <c r="H268" t="n">
+      <c r="G268" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9071,18 +7863,13 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>0.159M</t>
-        </is>
-      </c>
+      <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr"/>
-      <c r="G269" t="inlineStr"/>
-      <c r="H269" t="n">
+      <c r="G269" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9099,18 +7886,13 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>-0.009M</t>
-        </is>
-      </c>
+      <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr"/>
-      <c r="G270" t="inlineStr"/>
-      <c r="H270" t="n">
+      <c r="G270" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9127,18 +7909,13 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>0.872M</t>
-        </is>
-      </c>
+      <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr"/>
-      <c r="G271" t="inlineStr"/>
-      <c r="H271" t="n">
+      <c r="G271" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9155,18 +7932,13 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>-0.184M</t>
-        </is>
-      </c>
+      <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr"/>
-      <c r="G272" t="inlineStr"/>
-      <c r="H272" t="n">
+      <c r="G272" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9183,18 +7955,13 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>0.135M</t>
-        </is>
-      </c>
+      <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr"/>
-      <c r="G273" t="inlineStr"/>
-      <c r="H273" t="n">
+      <c r="G273" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9215,14 +7982,9 @@
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>6.09%</t>
-        </is>
-      </c>
+      <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr"/>
-      <c r="G274" t="inlineStr"/>
-      <c r="H274" t="n">
+      <c r="G274" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9243,14 +8005,9 @@
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>-3.035M</t>
-        </is>
-      </c>
+      <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr"/>
-      <c r="G275" t="inlineStr"/>
-      <c r="H275" t="n">
+      <c r="G275" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9267,19 +8024,14 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>6.87%</t>
-        </is>
-      </c>
+      <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr"/>
-      <c r="G276" t="inlineStr"/>
-      <c r="H276" t="n">
-        <v>3</v>
+      <c r="G276" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="277">
@@ -9290,24 +8042,19 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>2-Year Bond Auction</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>4.07M</t>
-        </is>
-      </c>
+      <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr"/>
-      <c r="G277" t="inlineStr"/>
-      <c r="H277" t="n">
-        <v>2</v>
+      <c r="G277" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="278">
@@ -9318,23 +8065,18 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>2-Year Bond Auction</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>2.589%</t>
-        </is>
-      </c>
+      <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr"/>
-      <c r="G278" t="inlineStr"/>
-      <c r="H278" t="n">
+      <c r="G278" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9357,8 +8099,7 @@
       <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr"/>
       <c r="F279" t="inlineStr"/>
-      <c r="G279" t="inlineStr"/>
-      <c r="H279" t="n">
+      <c r="G279" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9379,14 +8120,9 @@
         </is>
       </c>
       <c r="D280" t="inlineStr"/>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>2.055%</t>
-        </is>
-      </c>
+      <c r="E280" t="inlineStr"/>
       <c r="F280" t="inlineStr"/>
-      <c r="G280" t="inlineStr"/>
-      <c r="H280" t="n">
+      <c r="G280" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9409,8 +8145,7 @@
       <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr"/>
-      <c r="G281" t="inlineStr"/>
-      <c r="H281" t="n">
+      <c r="G281" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9431,18 +8166,13 @@
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="F282" t="inlineStr"/>
-      <c r="G282" t="inlineStr">
+      <c r="E282" t="inlineStr"/>
+      <c r="F282" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="H282" t="n">
+      <c r="G282" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9463,14 +8193,9 @@
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>$6.81T</t>
-        </is>
-      </c>
+      <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr"/>
-      <c r="G283" t="inlineStr"/>
-      <c r="H283" t="n">
+      <c r="G283" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9491,18 +8216,13 @@
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
-      </c>
-      <c r="F284" t="inlineStr"/>
-      <c r="G284" t="inlineStr">
+      <c r="E284" t="inlineStr"/>
+      <c r="F284" t="inlineStr">
         <is>
           <t>49.9</t>
         </is>
       </c>
-      <c r="H284" t="n">
+      <c r="G284" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9523,18 +8243,13 @@
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>51.2</t>
-        </is>
-      </c>
-      <c r="F285" t="inlineStr"/>
-      <c r="G285" t="inlineStr">
+      <c r="E285" t="inlineStr"/>
+      <c r="F285" t="inlineStr">
         <is>
           <t>51.3</t>
         </is>
       </c>
-      <c r="H285" t="n">
+      <c r="G285" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9555,18 +8270,13 @@
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
-      </c>
-      <c r="F286" t="inlineStr"/>
-      <c r="G286" t="inlineStr">
+      <c r="E286" t="inlineStr"/>
+      <c r="F286" t="inlineStr">
         <is>
           <t>50.6</t>
         </is>
       </c>
-      <c r="H286" t="n">
+      <c r="G286" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9589,8 +8299,7 @@
       <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr"/>
-      <c r="G287" t="inlineStr"/>
-      <c r="H287" t="n">
+      <c r="G287" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9611,18 +8320,13 @@
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F288" t="inlineStr"/>
-      <c r="G288" t="inlineStr">
+      <c r="E288" t="inlineStr"/>
+      <c r="F288" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H288" t="n">
+      <c r="G288" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9639,23 +8343,18 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Inflation Rate Ex-Food and Energy YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>2.4%</t>
-        </is>
-      </c>
-      <c r="F289" t="inlineStr"/>
-      <c r="G289" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="H289" t="n">
-        <v>3</v>
+      <c r="E289" t="inlineStr"/>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="G289" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="290">
@@ -9671,23 +8370,22 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr">
         <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="F290" t="inlineStr"/>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="H290" t="n">
-        <v>1</v>
+          <t>3.1%</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="G290" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="291">
@@ -9703,27 +8401,18 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate Ex-Food and Energy YoYJAN</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
+      <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
         <is>
-          <t>3.1%</t>
-        </is>
-      </c>
-      <c r="G291" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="H291" t="n">
-        <v>2</v>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="G291" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="292">
@@ -9743,18 +8432,13 @@
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="F292" t="inlineStr"/>
-      <c r="G292" t="inlineStr">
+      <c r="E292" t="inlineStr"/>
+      <c r="F292" t="inlineStr">
         <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="H292" t="n">
+      <c r="G292" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9782,15 +8466,10 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>-22</t>
-        </is>
-      </c>
-      <c r="G293" t="inlineStr">
-        <is>
           <t>-23</t>
         </is>
       </c>
-      <c r="H293" t="n">
+      <c r="G293" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9811,18 +8490,13 @@
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
-      </c>
-      <c r="F294" t="inlineStr"/>
-      <c r="G294" t="inlineStr">
+      <c r="E294" t="inlineStr"/>
+      <c r="F294" t="inlineStr">
         <is>
           <t>51.5</t>
         </is>
       </c>
-      <c r="H294" t="n">
+      <c r="G294" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9843,18 +8517,13 @@
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>53.0</t>
-        </is>
-      </c>
-      <c r="F295" t="inlineStr"/>
-      <c r="G295" t="inlineStr">
+      <c r="E295" t="inlineStr"/>
+      <c r="F295" t="inlineStr">
         <is>
           <t>52.2</t>
         </is>
       </c>
-      <c r="H295" t="n">
+      <c r="G295" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9877,20 +8546,15 @@
       <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="G296" t="inlineStr">
-        <is>
           <t>49.6</t>
         </is>
       </c>
-      <c r="H296" t="n">
+      <c r="G296" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9902,23 +8566,18 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month LTN Auction</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>0.3098%</t>
-        </is>
-      </c>
+      <c r="E297" t="inlineStr"/>
       <c r="F297" t="inlineStr"/>
-      <c r="G297" t="inlineStr"/>
-      <c r="H297" t="n">
+      <c r="G297" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9930,27 +8589,18 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Central Government DebtJAN</t>
+          <t>2-Year LTN Auction</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>TRY9.251T</t>
-        </is>
-      </c>
+      <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr"/>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>TRY 9.4T</t>
-        </is>
-      </c>
-      <c r="H298" t="n">
+      <c r="G298" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9962,23 +8612,18 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>10-Year NTN-F Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>15.035%</t>
-        </is>
-      </c>
+      <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr"/>
-      <c r="G299" t="inlineStr"/>
-      <c r="H299" t="n">
+      <c r="G299" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9990,23 +8635,22 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2-Year LTN Auction</t>
+          <t>Central Government DebtJAN</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>15.031%</t>
-        </is>
-      </c>
-      <c r="F300" t="inlineStr"/>
-      <c r="G300" t="inlineStr"/>
-      <c r="H300" t="n">
+      <c r="E300" t="inlineStr"/>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>TRY 9.4T</t>
+        </is>
+      </c>
+      <c r="G300" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10023,18 +8667,13 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>6-Month LTN Auction</t>
+          <t>10-Year NTN-F Auction</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>14.62%</t>
-        </is>
-      </c>
+      <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr"/>
-      <c r="G301" t="inlineStr"/>
-      <c r="H301" t="n">
+      <c r="G301" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10055,18 +8694,13 @@
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>57.7</t>
-        </is>
-      </c>
-      <c r="F302" t="inlineStr"/>
-      <c r="G302" t="inlineStr">
+      <c r="E302" t="inlineStr"/>
+      <c r="F302" t="inlineStr">
         <is>
           <t>58.2</t>
         </is>
       </c>
-      <c r="H302" t="n">
+      <c r="G302" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10087,18 +8721,13 @@
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>57.7</t>
-        </is>
-      </c>
-      <c r="F303" t="inlineStr"/>
-      <c r="G303" t="inlineStr">
+      <c r="E303" t="inlineStr"/>
+      <c r="F303" t="inlineStr">
         <is>
           <t>57.9</t>
         </is>
       </c>
-      <c r="H303" t="n">
+      <c r="G303" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10119,18 +8748,13 @@
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
-      <c r="E304" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="F304" t="inlineStr"/>
-      <c r="G304" t="inlineStr">
+      <c r="E304" t="inlineStr"/>
+      <c r="F304" t="inlineStr">
         <is>
           <t>57.5</t>
         </is>
       </c>
-      <c r="H304" t="n">
+      <c r="G304" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10147,22 +8771,17 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Retail Sales ex Fuel MoMJAN</t>
+          <t>Retail Sales ex Fuel YoYJAN</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-      <c r="F305" t="inlineStr"/>
-      <c r="G305" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="H305" t="n">
+      <c r="E305" t="inlineStr"/>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
+      <c r="G305" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10179,23 +8798,22 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Retail Sales ex Fuel YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2.9%</t>
-        </is>
-      </c>
-      <c r="F306" t="inlineStr"/>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t>3.0%</t>
-        </is>
-      </c>
-      <c r="H306" t="n">
-        <v>3</v>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="G306" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="307">
@@ -10211,27 +8829,18 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Public Sector Net Borrowing Ex BanksJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="D307" t="inlineStr"/>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>£-17.81B</t>
-        </is>
-      </c>
+      <c r="E307" t="inlineStr"/>
       <c r="F307" t="inlineStr">
         <is>
-          <t>£20.5B</t>
-        </is>
-      </c>
-      <c r="G307" t="inlineStr">
-        <is>
-          <t>£19.0B</t>
-        </is>
-      </c>
-      <c r="H307" t="n">
-        <v>3</v>
+          <t>4.0%</t>
+        </is>
+      </c>
+      <c r="G307" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="308">
@@ -10247,27 +8856,22 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Public Sector Net Borrowing Ex BanksJAN</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>£20.5B</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="H308" t="n">
-        <v>1</v>
+          <t>£19.0B</t>
+        </is>
+      </c>
+      <c r="G308" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="309">
@@ -10283,23 +8887,18 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Retail Sales ex Fuel MoMJAN</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="F309" t="inlineStr"/>
-      <c r="G309" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
-      <c r="H309" t="n">
-        <v>2</v>
+      <c r="E309" t="inlineStr"/>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="G309" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="310">
@@ -10319,18 +8918,13 @@
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="F310" t="inlineStr"/>
-      <c r="G310" t="inlineStr">
+      <c r="E310" t="inlineStr"/>
+      <c r="F310" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="H310" t="n">
+      <c r="G310" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10351,18 +8945,13 @@
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="F311" t="inlineStr"/>
-      <c r="G311" t="inlineStr">
+      <c r="E311" t="inlineStr"/>
+      <c r="F311" t="inlineStr">
         <is>
           <t>92</t>
         </is>
       </c>
-      <c r="H311" t="n">
+      <c r="G311" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10385,8 +8974,7 @@
       <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr"/>
       <c r="F312" t="inlineStr"/>
-      <c r="G312" t="inlineStr"/>
-      <c r="H312" t="n">
+      <c r="G312" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10403,26 +8991,17 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+      <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="G313" t="inlineStr">
-        <is>
-          <t>45.4</t>
-        </is>
-      </c>
-      <c r="H313" t="n">
+          <t>47.2</t>
+        </is>
+      </c>
+      <c r="G313" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10439,22 +9018,21 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>47.6</t>
-        </is>
-      </c>
-      <c r="F314" t="inlineStr"/>
-      <c r="G314" t="inlineStr">
-        <is>
-          <t>47.2</t>
-        </is>
-      </c>
-      <c r="H314" t="n">
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>45.4</t>
+        </is>
+      </c>
+      <c r="G314" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10477,20 +9055,15 @@
       <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="G315" t="inlineStr">
-        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="H315" t="n">
+      <c r="G315" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10507,27 +9080,22 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="G316" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="H316" t="n">
-        <v>2</v>
+          <t>45.1</t>
+        </is>
+      </c>
+      <c r="G316" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="317">
@@ -10547,18 +9115,13 @@
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>50.5</t>
-        </is>
-      </c>
-      <c r="F317" t="inlineStr"/>
-      <c r="G317" t="inlineStr">
+      <c r="E317" t="inlineStr"/>
+      <c r="F317" t="inlineStr">
         <is>
           <t>50.1</t>
         </is>
       </c>
-      <c r="H317" t="n">
+      <c r="G317" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10575,27 +9138,22 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>45.5</t>
-        </is>
-      </c>
-      <c r="G318" t="inlineStr">
-        <is>
-          <t>45.1</t>
-        </is>
-      </c>
-      <c r="H318" t="n">
-        <v>1</v>
+          <t>51.9</t>
+        </is>
+      </c>
+      <c r="G318" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="319">
@@ -10611,26 +9169,21 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="H319" t="n">
+          <t>1.7%</t>
+        </is>
+      </c>
+      <c r="G319" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10647,27 +9200,22 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>1.7%</t>
-        </is>
-      </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>1.7%</t>
-        </is>
-      </c>
-      <c r="H320" t="n">
-        <v>3</v>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="G320" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="321">
@@ -10683,27 +9231,22 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="H321" t="n">
-        <v>2</v>
+          <t>-0.7%</t>
+        </is>
+      </c>
+      <c r="G321" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="322">
@@ -10719,26 +9262,21 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="H322" t="n">
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="G322" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10755,26 +9293,21 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>46.8</t>
-        </is>
-      </c>
-      <c r="H323" t="n">
+          <t>51.2</t>
+        </is>
+      </c>
+      <c r="G323" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10791,22 +9324,21 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr">
         <is>
-          <t>50.2</t>
-        </is>
-      </c>
-      <c r="F324" t="inlineStr"/>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H324" t="n">
+          <t>47</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>46.8</t>
+        </is>
+      </c>
+      <c r="G324" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10823,26 +9355,17 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
-      <c r="E325" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
+      <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
         <is>
-          <t>51.5</t>
-        </is>
-      </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>51.2</t>
-        </is>
-      </c>
-      <c r="H325" t="n">
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G325" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10865,7 +9388,7 @@
       <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
@@ -10873,12 +9396,7 @@
           <t>48.5</t>
         </is>
       </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>48.5</t>
-        </is>
-      </c>
-      <c r="H326" t="n">
+      <c r="G326" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10901,7 +9419,7 @@
       <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -10909,12 +9427,7 @@
           <t>51</t>
         </is>
       </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="H327" t="n">
+      <c r="G327" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10935,18 +9448,13 @@
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>50.6</t>
-        </is>
-      </c>
-      <c r="F328" t="inlineStr"/>
-      <c r="G328" t="inlineStr">
+      <c r="E328" t="inlineStr"/>
+      <c r="F328" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H328" t="n">
+      <c r="G328" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10969,8 +9477,7 @@
       <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr"/>
-      <c r="G329" t="inlineStr"/>
-      <c r="H329" t="n">
+      <c r="G329" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10991,14 +9498,9 @@
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
-      <c r="E330" t="inlineStr">
-        <is>
-          <t>$638.26B</t>
-        </is>
-      </c>
+      <c r="E330" t="inlineStr"/>
       <c r="F330" t="inlineStr"/>
-      <c r="G330" t="inlineStr"/>
-      <c r="H330" t="n">
+      <c r="G330" t="n">
         <v>3</v>
       </c>
     </row>
@@ -11015,22 +9517,17 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Economic Activity YoYDEC</t>
+          <t>Economic Activity MoMDEC</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
-      <c r="E331" t="inlineStr">
+      <c r="E331" t="inlineStr"/>
+      <c r="F331" t="inlineStr">
         <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="F331" t="inlineStr"/>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="H331" t="n">
+      <c r="G331" t="n">
         <v>3</v>
       </c>
     </row>
@@ -11047,22 +9544,17 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Economic Activity MoMDEC</t>
+          <t>Economic Activity YoYDEC</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="F332" t="inlineStr"/>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="H332" t="n">
+      <c r="E332" t="inlineStr"/>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="G332" t="n">
         <v>3</v>
       </c>
     </row>
@@ -11079,26 +9571,21 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ FinalQ4</t>
+          <t>GDP Growth Rate YoY FinalQ4</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-      <c r="H333" t="n">
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="G333" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11115,26 +9602,21 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>GDP Growth Rate YoY FinalQ4</t>
+          <t>GDP Growth Rate QoQ FinalQ4</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="H334" t="n">
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="G334" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11151,23 +9633,22 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
-          <t>1.6%</t>
-        </is>
-      </c>
-      <c r="F335" t="inlineStr"/>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="H335" t="n">
-        <v>3</v>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="G335" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="336">
@@ -11183,26 +9664,21 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Retail Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="H336" t="n">
+          <t>1.6%</t>
+        </is>
+      </c>
+      <c r="G336" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11219,26 +9695,17 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Retail Sales MoM FinalDEC</t>
+          <t>Retail Sales MoM PrelJAN</t>
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
-      <c r="E337" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+      <c r="E337" t="inlineStr"/>
       <c r="F337" t="inlineStr">
         <is>
-          <t>1.6%</t>
-        </is>
-      </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
-      <c r="H337" t="n">
+          <t>-0.3%</t>
+        </is>
+      </c>
+      <c r="G337" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11255,19 +9722,18 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Retail Sales MoM PrelJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr"/>
-      <c r="F338" t="inlineStr"/>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
-      <c r="H338" t="n">
-        <v>2</v>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="G338" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="339">
@@ -11289,8 +9755,7 @@
       <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr"/>
       <c r="F339" t="inlineStr"/>
-      <c r="G339" t="inlineStr"/>
-      <c r="H339" t="n">
+      <c r="G339" t="n">
         <v>3</v>
       </c>
     </row>
@@ -11307,22 +9772,17 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
-      <c r="E340" t="inlineStr">
-        <is>
-          <t>51.2</t>
-        </is>
-      </c>
-      <c r="F340" t="inlineStr"/>
-      <c r="G340" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="H340" t="n">
+      <c r="E340" t="inlineStr"/>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>52.7</t>
+        </is>
+      </c>
+      <c r="G340" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11339,22 +9799,17 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
-      <c r="E341" t="inlineStr">
-        <is>
-          <t>52.9</t>
-        </is>
-      </c>
-      <c r="F341" t="inlineStr"/>
-      <c r="G341" t="inlineStr">
+      <c r="E341" t="inlineStr"/>
+      <c r="F341" t="inlineStr">
         <is>
           <t>52.7</t>
         </is>
       </c>
-      <c r="H341" t="n">
+      <c r="G341" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11371,22 +9826,17 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
-      <c r="E342" t="inlineStr">
-        <is>
-          <t>52.7</t>
-        </is>
-      </c>
-      <c r="F342" t="inlineStr"/>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>52.7</t>
-        </is>
-      </c>
-      <c r="H342" t="n">
+      <c r="E342" t="inlineStr"/>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
+      <c r="G342" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11403,26 +9853,21 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="G343" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="H343" t="n">
+          <t>67.3</t>
+        </is>
+      </c>
+      <c r="G343" t="n">
         <v>3</v>
       </c>
     </row>
@@ -11439,26 +9884,21 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>68.7</t>
-        </is>
-      </c>
-      <c r="G344" t="inlineStr">
-        <is>
-          <t>68.7</t>
-        </is>
-      </c>
-      <c r="H344" t="n">
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="G344" t="n">
         <v>3</v>
       </c>
     </row>
@@ -11475,26 +9915,21 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>67.3</t>
-        </is>
-      </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
-      </c>
-      <c r="H345" t="n">
+          <t>68.7</t>
+        </is>
+      </c>
+      <c r="G345" t="n">
         <v>3</v>
       </c>
     </row>
@@ -11517,7 +9952,7 @@
       <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
@@ -11525,12 +9960,7 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="G346" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="H346" t="n">
+      <c r="G346" t="n">
         <v>3</v>
       </c>
     </row>
@@ -11551,18 +9981,13 @@
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
-      <c r="E347" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="F347" t="inlineStr"/>
-      <c r="G347" t="inlineStr">
+      <c r="E347" t="inlineStr"/>
+      <c r="F347" t="inlineStr">
         <is>
           <t>-1.7%</t>
         </is>
       </c>
-      <c r="H347" t="n">
+      <c r="G347" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11579,27 +10004,22 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
       <c r="E348" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>4.17M</t>
-        </is>
-      </c>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t>4.16M</t>
-        </is>
-      </c>
-      <c r="H348" t="n">
-        <v>1</v>
+          <t>67.8</t>
+        </is>
+      </c>
+      <c r="G348" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="349">
@@ -11615,27 +10035,22 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="G349" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="H349" t="n">
-        <v>2</v>
+          <t>4.16M</t>
+        </is>
+      </c>
+      <c r="G349" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="350">
@@ -11657,8 +10072,7 @@
       <c r="D350" t="inlineStr"/>
       <c r="E350" t="inlineStr"/>
       <c r="F350" t="inlineStr"/>
-      <c r="G350" t="inlineStr"/>
-      <c r="H350" t="n">
+      <c r="G350" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11681,8 +10095,7 @@
       <c r="D351" t="inlineStr"/>
       <c r="E351" t="inlineStr"/>
       <c r="F351" t="inlineStr"/>
-      <c r="G351" t="inlineStr"/>
-      <c r="H351" t="n">
+      <c r="G351" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11703,14 +10116,9 @@
         </is>
       </c>
       <c r="D352" t="inlineStr"/>
-      <c r="E352" t="inlineStr">
-        <is>
-          <t>481</t>
-        </is>
-      </c>
+      <c r="E352" t="inlineStr"/>
       <c r="F352" t="inlineStr"/>
-      <c r="G352" t="inlineStr"/>
-      <c r="H352" t="n">
+      <c r="G352" t="n">
         <v>3</v>
       </c>
     </row>
@@ -11731,14 +10139,9 @@
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
-      <c r="E353" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
+      <c r="E353" t="inlineStr"/>
       <c r="F353" t="inlineStr"/>
-      <c r="G353" t="inlineStr"/>
-      <c r="H353" t="n">
+      <c r="G353" t="n">
         <v>3</v>
       </c>
     </row>
@@ -11759,18 +10162,13 @@
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
-      <c r="E354" t="inlineStr">
-        <is>
-          <t>-27.1%</t>
-        </is>
-      </c>
-      <c r="F354" t="inlineStr"/>
-      <c r="G354" t="inlineStr">
+      <c r="E354" t="inlineStr"/>
+      <c r="F354" t="inlineStr">
         <is>
           <t>-18.0%</t>
         </is>
       </c>
-      <c r="H354" t="n">
+      <c r="G354" t="n">
         <v>3</v>
       </c>
     </row>
@@ -11791,14 +10189,9 @@
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
-      <c r="E355" t="inlineStr">
-        <is>
-          <t>BRL261.3B</t>
-        </is>
-      </c>
+      <c r="E355" t="inlineStr"/>
       <c r="F355" t="inlineStr"/>
-      <c r="G355" t="inlineStr"/>
-      <c r="H355" t="n">
+      <c r="G355" t="n">
         <v>3</v>
       </c>
     </row>
@@ -11822,7 +10215,6 @@
       <c r="E356" t="inlineStr"/>
       <c r="F356" t="inlineStr"/>
       <c r="G356" t="inlineStr"/>
-      <c r="H356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -11841,18 +10233,13 @@
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
-      <c r="E357" t="inlineStr">
-        <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="F357" t="inlineStr"/>
-      <c r="G357" t="inlineStr">
+      <c r="E357" t="inlineStr"/>
+      <c r="F357" t="inlineStr">
         <is>
           <t>2.0%</t>
         </is>
       </c>
-      <c r="H357" t="n">
+      <c r="G357" t="n">
         <v>3</v>
       </c>
     </row>
@@ -11873,18 +10260,13 @@
         </is>
       </c>
       <c r="D358" t="inlineStr"/>
-      <c r="E358" t="inlineStr">
-        <is>
-          <t>0.30%</t>
-        </is>
-      </c>
-      <c r="F358" t="inlineStr"/>
-      <c r="G358" t="inlineStr">
+      <c r="E358" t="inlineStr"/>
+      <c r="F358" t="inlineStr">
         <is>
           <t>-0.1%</t>
         </is>
       </c>
-      <c r="H358" t="n">
+      <c r="G358" t="n">
         <v>3</v>
       </c>
     </row>
@@ -11905,18 +10287,13 @@
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
-      <c r="E359" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
-      <c r="F359" t="inlineStr"/>
-      <c r="G359" t="inlineStr">
+      <c r="E359" t="inlineStr"/>
+      <c r="F359" t="inlineStr">
         <is>
           <t>2.1%</t>
         </is>
       </c>
-      <c r="H359" t="n">
+      <c r="G359" t="n">
         <v>3</v>
       </c>
     </row>
@@ -11937,14 +10314,9 @@
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
-      <c r="E360" t="inlineStr">
-        <is>
-          <t>2.725%</t>
-        </is>
-      </c>
+      <c r="E360" t="inlineStr"/>
       <c r="F360" t="inlineStr"/>
-      <c r="G360" t="inlineStr"/>
-      <c r="H360" t="n">
+      <c r="G360" t="n">
         <v>3</v>
       </c>
     </row>
@@ -11965,14 +10337,9 @@
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
-      <c r="E361" t="inlineStr">
-        <is>
-          <t>100.9</t>
-        </is>
-      </c>
+      <c r="E361" t="inlineStr"/>
       <c r="F361" t="inlineStr"/>
-      <c r="G361" t="inlineStr"/>
-      <c r="H361" t="n">
+      <c r="G361" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11993,14 +10360,9 @@
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
-      <c r="E362" t="inlineStr">
-        <is>
-          <t>74.6%</t>
-        </is>
-      </c>
+      <c r="E362" t="inlineStr"/>
       <c r="F362" t="inlineStr"/>
-      <c r="G362" t="inlineStr"/>
-      <c r="H362" t="n">
+      <c r="G362" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12021,18 +10383,13 @@
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
-      <c r="E363" t="inlineStr">
-        <is>
-          <t>84.2</t>
-        </is>
-      </c>
-      <c r="F363" t="inlineStr"/>
-      <c r="G363" t="inlineStr">
+      <c r="E363" t="inlineStr"/>
+      <c r="F363" t="inlineStr">
         <is>
           <t>83</t>
         </is>
       </c>
-      <c r="H363" t="n">
+      <c r="G363" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12053,18 +10410,13 @@
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
-      <c r="E364" t="inlineStr">
-        <is>
-          <t>85.1</t>
-        </is>
-      </c>
-      <c r="F364" t="inlineStr"/>
-      <c r="G364" t="inlineStr">
+      <c r="E364" t="inlineStr"/>
+      <c r="F364" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="H364" t="n">
+      <c r="G364" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12085,18 +10437,13 @@
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
-      <c r="E365" t="inlineStr">
-        <is>
-          <t>86.1</t>
-        </is>
-      </c>
-      <c r="F365" t="inlineStr"/>
-      <c r="G365" t="inlineStr">
+      <c r="E365" t="inlineStr"/>
+      <c r="F365" t="inlineStr">
         <is>
           <t>85.1</t>
         </is>
       </c>
-      <c r="H365" t="n">
+      <c r="G365" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12119,7 +10466,7 @@
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
@@ -12127,12 +10474,7 @@
           <t>-0.3%</t>
         </is>
       </c>
-      <c r="G366" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
-      <c r="H366" t="n">
+      <c r="G366" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12155,7 +10497,7 @@
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr">
         <is>
-          <t>127.07</t>
+          <t>126.71</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
@@ -12163,12 +10505,7 @@
           <t>126.71</t>
         </is>
       </c>
-      <c r="G367" t="inlineStr">
-        <is>
-          <t>126.71</t>
-        </is>
-      </c>
-      <c r="H367" t="n">
+      <c r="G367" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12185,27 +10522,22 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Core Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="G368" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="H368" t="n">
-        <v>2</v>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="G368" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="369">
@@ -12221,27 +10553,22 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="G369" t="inlineStr">
-        <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="H369" t="n">
-        <v>3</v>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="G369" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="370">
@@ -12261,14 +10588,9 @@
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>2.576%</t>
-        </is>
-      </c>
+      <c r="E370" t="inlineStr"/>
       <c r="F370" t="inlineStr"/>
-      <c r="G370" t="inlineStr"/>
-      <c r="H370" t="n">
+      <c r="G370" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12289,14 +10611,9 @@
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>2.223%</t>
-        </is>
-      </c>
+      <c r="E371" t="inlineStr"/>
       <c r="F371" t="inlineStr"/>
-      <c r="G371" t="inlineStr"/>
-      <c r="H371" t="n">
+      <c r="G371" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12319,8 +10636,7 @@
       <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr"/>
       <c r="F372" t="inlineStr"/>
-      <c r="G372" t="inlineStr"/>
-      <c r="H372" t="n">
+      <c r="G372" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12341,14 +10657,9 @@
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
-      <c r="E373" t="inlineStr">
-        <is>
-          <t>86.2</t>
-        </is>
-      </c>
+      <c r="E373" t="inlineStr"/>
       <c r="F373" t="inlineStr"/>
-      <c r="G373" t="inlineStr"/>
-      <c r="H373" t="n">
+      <c r="G373" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12369,14 +10680,9 @@
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
-      <c r="E374" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E374" t="inlineStr"/>
       <c r="F374" t="inlineStr"/>
-      <c r="G374" t="inlineStr"/>
-      <c r="H374" t="n">
+      <c r="G374" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12397,14 +10703,9 @@
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
-      <c r="E375" t="inlineStr">
-        <is>
-          <t>0.28%</t>
-        </is>
-      </c>
+      <c r="E375" t="inlineStr"/>
       <c r="F375" t="inlineStr"/>
-      <c r="G375" t="inlineStr"/>
-      <c r="H375" t="n">
+      <c r="G375" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12425,14 +10726,9 @@
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
-      <c r="E376" t="inlineStr">
-        <is>
-          <t>3.72%</t>
-        </is>
-      </c>
+      <c r="E376" t="inlineStr"/>
       <c r="F376" t="inlineStr"/>
-      <c r="G376" t="inlineStr"/>
-      <c r="H376" t="n">
+      <c r="G376" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12453,14 +10749,9 @@
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
-      <c r="E377" t="inlineStr">
-        <is>
-          <t>3.69%</t>
-        </is>
-      </c>
+      <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr"/>
-      <c r="G377" t="inlineStr"/>
-      <c r="H377" t="n">
+      <c r="G377" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12483,8 +10774,7 @@
       <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr"/>
       <c r="F378" t="inlineStr"/>
-      <c r="G378" t="inlineStr"/>
-      <c r="H378" t="n">
+      <c r="G378" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12505,14 +10795,9 @@
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
-      <c r="E379" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
+      <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr"/>
-      <c r="G379" t="inlineStr"/>
-      <c r="H379" t="n">
+      <c r="G379" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12535,8 +10820,7 @@
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr"/>
-      <c r="G380" t="inlineStr"/>
-      <c r="H380" t="n">
+      <c r="G380" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12559,8 +10843,7 @@
       <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="inlineStr"/>
-      <c r="G381" t="inlineStr"/>
-      <c r="H381" t="n">
+      <c r="G381" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12583,8 +10866,7 @@
       <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="inlineStr"/>
-      <c r="G382" t="inlineStr"/>
-      <c r="H382" t="n">
+      <c r="G382" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12605,14 +10887,9 @@
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
-      <c r="E383" t="inlineStr">
-        <is>
-          <t>14.1</t>
-        </is>
-      </c>
+      <c r="E383" t="inlineStr"/>
       <c r="F383" t="inlineStr"/>
-      <c r="G383" t="inlineStr"/>
-      <c r="H383" t="n">
+      <c r="G383" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12635,8 +10912,7 @@
       <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="inlineStr"/>
-      <c r="G384" t="inlineStr"/>
-      <c r="H384" t="n">
+      <c r="G384" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12659,8 +10935,7 @@
       <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="inlineStr"/>
-      <c r="G385" t="inlineStr"/>
-      <c r="H385" t="n">
+      <c r="G385" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12683,8 +10958,7 @@
       <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="inlineStr"/>
-      <c r="G386" t="inlineStr"/>
-      <c r="H386" t="n">
+      <c r="G386" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12705,18 +10979,13 @@
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
-      <c r="E387" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="F387" t="inlineStr"/>
-      <c r="G387" t="inlineStr">
+      <c r="E387" t="inlineStr"/>
+      <c r="F387" t="inlineStr">
         <is>
           <t>2.75%</t>
         </is>
       </c>
-      <c r="H387" t="n">
+      <c r="G387" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12739,8 +11008,7 @@
       <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr"/>
-      <c r="G388" t="inlineStr"/>
-      <c r="H388" t="n">
+      <c r="G388" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12763,8 +11031,7 @@
       <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="inlineStr"/>
-      <c r="G389" t="inlineStr"/>
-      <c r="H389" t="n">
+      <c r="G389" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12785,14 +11052,90 @@
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
-      <c r="E390" t="inlineStr">
-        <is>
-          <t>2.770%</t>
-        </is>
-      </c>
+      <c r="E390" t="inlineStr"/>
       <c r="F390" t="inlineStr"/>
-      <c r="G390" t="inlineStr"/>
-      <c r="H390" t="n">
+      <c r="G390" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2025-02-25 01:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Balance of TradeDEC</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr"/>
+      <c r="E391" t="inlineStr"/>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>SAR 34B</t>
+        </is>
+      </c>
+      <c r="G391" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2025-02-25 01:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>ExportsDEC</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr"/>
+      <c r="E392" t="inlineStr"/>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>SAR 94.5B</t>
+        </is>
+      </c>
+      <c r="G392" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2025-02-25 01:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>ImportsDEC</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr"/>
+      <c r="E393" t="inlineStr"/>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>SAR 60.5B</t>
+        </is>
+      </c>
+      <c r="G393" t="n">
         <v>3</v>
       </c>
     </row>

--- a/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -699,22 +699,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Core Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -734,7 +734,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -769,22 +769,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -804,22 +804,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -839,22 +839,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Deposit Growth YoYJAN/31</t>
+          <t>Bank Loan Growth YoYJAN/31</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Foreign Exchange ReservesFEB/07</t>
+          <t>Deposit Growth YoYJAN/31</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>$638.26B</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bank Loan Growth YoYJAN/31</t>
+          <t>Foreign Exchange ReservesFEB/07</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>$638.26B</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1319,20 +1319,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Wholesale Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>0.2%</t>
@@ -1355,22 +1359,26 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1381,23 +1389,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Manufacturing Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1412,31 +1424,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>New Motor Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>135.5K</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>153K</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1452,12 +1460,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1467,7 +1475,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -1487,22 +1495,26 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1518,12 +1530,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1533,7 +1545,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -1553,26 +1565,26 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1583,27 +1595,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Wholesale Sales MoM FinalDEC</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -1618,23 +1626,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New Motor Vehicle SalesDEC</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>135.5K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>153K</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -1649,27 +1657,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Manufacturing Sales MoM FinalDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -1689,26 +1693,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -1724,26 +1724,26 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -1759,26 +1759,26 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -1794,18 +1794,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>77.8%</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -1825,22 +1829,18 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -1891,26 +1891,26 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMDEC</t>
+          <t>Business Inventories MoMDEC</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>-0.1%</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
       <c r="G45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -1926,26 +1926,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Business Inventories MoMDEC</t>
+          <t>Retail Inventories Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -1984,22 +1984,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -2019,22 +2019,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2131,22 +2131,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ PrelQ4</t>
+          <t>GDP External Demand QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GDP Growth Annualized PrelQ4</t>
+          <t>GDP Capital Expenditure QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -2173,11 +2173,11 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -2193,18 +2193,18 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GDP Capital Expenditure QoQ PrelQ4</t>
+          <t>GDP Private Consumption QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -2224,22 +2224,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GDP External Demand QoQ PrelQ4</t>
+          <t>GDP Growth Rate QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -2255,18 +2255,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GDP Price Index YoY PrelQ4</t>
+          <t>GDP Growth Annualized PrelQ4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -2282,18 +2286,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GDP Private Consumption QoQ PrelQ4</t>
+          <t>GDP Price Index YoY PrelQ4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -2313,18 +2313,18 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Non-Oil Exports YoYJAN</t>
+          <t>Non-Oil Exports MoMJAN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -2344,18 +2344,18 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Non-Oil Exports MoMJAN</t>
+          <t>Non-Oil Exports YoYJAN</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -2402,22 +2402,18 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Imports YoYJAN</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>$1.91B</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>$2.2B</t>
-        </is>
-      </c>
+          <t>9.95%</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -2433,18 +2429,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Exports YoYJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>6.99%</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
+          <t>$1.91B</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>$2.2B</t>
+        </is>
+      </c>
       <c r="G63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -2460,13 +2460,13 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Imports YoYJAN</t>
+          <t>Exports YoYJAN</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>9.95%</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -2482,17 +2482,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Eurogroup Meeting</t>
+          <t>Wholesale Prices YoYJAN</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1.3%</t>
+        </is>
+      </c>
       <c r="G65" t="n">
         <v>3</v>
       </c>
@@ -2505,25 +2509,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Eurogroup Meeting</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2.0%</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
         <v>3</v>
       </c>
@@ -2599,14 +2595,18 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Wholesale Prices YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -2653,18 +2653,18 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Industrial Production MoM FinalDEC</t>
+          <t>Tertiary Industry Index MoMDEC</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -2684,18 +2684,18 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tertiary Industry Index MoMDEC</t>
+          <t>Industrial Production MoM FinalDEC</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ECOFIN Meeting</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -3260,12 +3260,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>ECOFIN Meeting</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>

--- a/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G397"/>
+  <dimension ref="A1:G400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -699,22 +699,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Core Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -734,22 +734,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -769,7 +769,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -779,12 +779,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -804,22 +804,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -839,22 +839,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Foreign Exchange ReservesFEB/07</t>
+          <t>Deposit Growth YoYJAN/31</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>$638.26B</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bank Loan Growth YoYJAN/31</t>
+          <t>Foreign Exchange ReservesFEB/07</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>$638.26B</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Deposit Growth YoYJAN/31</t>
+          <t>Bank Loan Growth YoYJAN/31</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1319,23 +1319,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Manufacturing Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1355,22 +1359,26 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1381,20 +1389,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Wholesale Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>0.2%</t>
@@ -1417,22 +1429,26 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1448,12 +1464,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1463,7 +1479,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -1478,31 +1494,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>New Motor Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>135.5K</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>153K</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -1518,12 +1530,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1533,7 +1545,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -1548,23 +1560,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New Motor Vehicle SalesDEC</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>135.5K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>153K</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -1579,27 +1591,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Manufacturing Sales MoM FinalDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -1619,26 +1627,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -1649,27 +1653,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Wholesale Sales MoM FinalDEC</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -1689,26 +1689,26 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -1724,18 +1724,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
+          <t>77.8%</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -1755,22 +1759,18 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -1790,26 +1790,26 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1825,26 +1825,26 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1891,26 +1891,26 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMDEC</t>
+          <t>Business Inventories MoMDEC</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>-0.1%</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
       <c r="G45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -1926,26 +1926,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Business Inventories MoMDEC</t>
+          <t>Retail Inventories Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -1984,22 +1984,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -2019,22 +2019,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -3283,12 +3283,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BCB Focus Market Readout</t>
+          <t>European Commission Winter Forecasts</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -3333,12 +3333,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>European Commission Winter Forecasts</t>
+          <t>BCB Focus Market Readout</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -4595,22 +4595,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Imports YoYJAN</t>
+          <t>Machinery Orders YoYDEC</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -4657,22 +4657,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Machinery Orders YoYDEC</t>
+          <t>Imports YoYJAN</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148">
@@ -4935,14 +4935,18 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Retail Price Index MoMJAN</t>
+          <t>Retail Price Index YoYJAN</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>3.7%</t>
+        </is>
+      </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -4962,14 +4966,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>PPI Output YoYJAN</t>
+          <t>Retail Price Index MoMJAN</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -4989,18 +4993,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>PPI Output MoMJAN</t>
+          <t>PPI Output YoYJAN</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr">
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr">
         <is>
           <t>0.2%</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>0.3%</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -5020,14 +5020,18 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>PPI Input YoYJAN</t>
+          <t>PPI Output MoMJAN</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -5047,18 +5051,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>PPI Input MoMJAN</t>
+          <t>PPI Input YoYJAN</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -5078,14 +5078,18 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>PPI Core Output YoYJAN</t>
+          <t>PPI Input MoMJAN</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -5105,22 +5109,18 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G163" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164">
@@ -5136,14 +5136,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>PPI Core Output MoMJAN</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -5221,22 +5221,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Retail Price Index YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G167" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168">
@@ -5252,14 +5252,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>PPI Core Output MoMJAN</t>
+          <t>PPI Core Output YoYJAN</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -5306,22 +5306,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Deposit Facility RateFEB</t>
+          <t>Interest Rate Decision</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>5.75%</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>5.75%</t>
         </is>
       </c>
       <c r="G170" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171">
@@ -5337,18 +5337,18 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Lending Facility RateFEB</t>
+          <t>Deposit Facility RateFEB</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -5368,22 +5368,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Interest Rate Decision</t>
+          <t>Lending Facility RateFEB</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>5.75%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>5.75%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="G172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
@@ -5394,17 +5394,21 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>ECB Non-Monetary Policy Meeting</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G173" t="n">
         <v>3</v>
       </c>
@@ -5422,18 +5426,18 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -5471,21 +5475,17 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>ECB Non-Monetary Policy Meeting</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="F176" t="inlineStr"/>
       <c r="G176" t="n">
         <v>3</v>
       </c>
@@ -5503,18 +5503,18 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G177" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="178">
@@ -5661,14 +5661,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -5688,14 +5688,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -5784,14 +5784,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -5853,14 +5853,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="192">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -5899,22 +5899,18 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="G193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="194">
@@ -5930,18 +5926,18 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
-          <t>1.39M</t>
+          <t>1.45M</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -5961,18 +5957,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
-      <c r="E195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="G195" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196">
@@ -5988,14 +5988,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -6065,14 +6065,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -6092,14 +6092,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Stock Investment by ForeignersFEB/15</t>
+          <t>Foreign Bond InvestmentFEB/15</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentFEB/15</t>
+          <t>Stock Investment by ForeignersFEB/15</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -6388,22 +6388,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="G212" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="213">
@@ -6419,22 +6419,18 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Employment ChangeJAN</t>
+          <t>Part Time Employment ChgJAN</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>20K</t>
-        </is>
-      </c>
+      <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>23.0K</t>
+          <t>-10.0K</t>
         </is>
       </c>
       <c r="G213" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="214">
@@ -6477,18 +6473,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Part Time Employment ChgJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
-      <c r="E215" t="inlineStr"/>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>4.1%</t>
+        </is>
+      </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>-10.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G215" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Employment ChangeJAN</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>20K</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>23.0K</t>
         </is>
       </c>
       <c r="G216" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="217">
@@ -6535,14 +6535,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Loan Prime Rate 1Y</t>
+          <t>Loan Prime Rate 5YFEB</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -6562,14 +6562,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Loan Prime Rate 5YFEB</t>
+          <t>Loan Prime Rate 1Y</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -6584,19 +6584,19 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Leading Indicator MoMJAN</t>
+          <t>Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -6616,16 +6616,12 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Current AccountQ4</t>
+          <t>M2 Money Supply YoYJAN</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>$ -0.6B</t>
-        </is>
-      </c>
+      <c r="F220" t="inlineStr"/>
       <c r="G220" t="n">
         <v>3</v>
       </c>
@@ -6643,12 +6639,16 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>M2 Money Supply YoYJAN</t>
+          <t>Current AccountQ4</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr"/>
-      <c r="F221" t="inlineStr"/>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>$ -0.6B</t>
+        </is>
+      </c>
       <c r="G221" t="n">
         <v>3</v>
       </c>
@@ -6661,19 +6661,19 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Consumer ConfidenceJAN</t>
+          <t>Leading Indicator MoMJAN</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -6688,23 +6688,27 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Consumer ConfidenceFEB</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
-      <c r="E223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G223" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="224">
@@ -6715,27 +6719,23 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+      <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G224" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="225">
@@ -6965,17 +6965,21 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>6-Year Index-Linked OAT Auction</t>
+          <t>Building Permits YoYDEC</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
-      <c r="F234" t="inlineStr"/>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>18.0%</t>
+        </is>
+      </c>
       <c r="G234" t="n">
         <v>3</v>
       </c>
@@ -7019,21 +7023,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Building Permits YoYDEC</t>
+          <t>7-Year OATi Auction</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>18.0%</t>
-        </is>
-      </c>
+      <c r="F236" t="inlineStr"/>
       <c r="G236" t="n">
         <v>3</v>
       </c>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>7-Year OATi Auction</t>
+          <t>6-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>11-Year Index-Linked OAT Auction</t>
+          <t>18-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>18-Year Index-Linked OAT Auction</t>
+          <t>11-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -7197,12 +7197,16 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr"/>
-      <c r="F243" t="inlineStr"/>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="G243" t="n">
         <v>3</v>
       </c>
@@ -7220,16 +7224,12 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr"/>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="F244" t="inlineStr"/>
       <c r="G244" t="n">
         <v>3</v>
       </c>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
@@ -7270,16 +7270,12 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr"/>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="F246" t="inlineStr"/>
       <c r="G246" t="n">
         <v>3</v>
       </c>
@@ -7297,7 +7293,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
@@ -7320,12 +7316,16 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr"/>
-      <c r="F248" t="inlineStr"/>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="G248" t="n">
         <v>3</v>
       </c>
@@ -7343,7 +7343,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
@@ -7392,23 +7392,27 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Raw Materials Prices YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
-      <c r="E251" t="inlineStr"/>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="G251" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252">
@@ -7424,14 +7428,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Raw Materials Prices MoMJAN</t>
+          <t>Raw Materials Prices YoYJAN</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -7451,14 +7455,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Raw Materials Prices MoMJAN</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -7478,14 +7482,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -7505,18 +7509,18 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>New Housing Price Index YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
@@ -7532,14 +7536,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>New Housing Price Index MoMJAN</t>
+          <t>New Housing Price Index YoYJAN</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -7554,23 +7558,19 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>New Housing Price Index MoMJAN</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
@@ -7886,7 +7886,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
@@ -7955,7 +7955,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
@@ -8262,14 +8262,14 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Australia Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -8289,14 +8289,14 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Services PMI FlashFEB</t>
+          <t>S&amp;P Global Australia Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -8343,18 +8343,18 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
       <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G289" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="290">
@@ -8370,18 +8370,22 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
-      <c r="E290" t="inlineStr"/>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G290" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291">
@@ -8397,22 +8401,18 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate Ex-Food and Energy YoYJAN</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
+      <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G291" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="292">
@@ -8428,14 +8428,14 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Inflation Rate Ex-Food and Energy YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>6-Month LTN Auction</t>
+          <t>2-Year LTN Auction</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2-Year LTN Auction</t>
+          <t>10-Year NTN-F Auction</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -8612,21 +8612,17 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Central Government DebtJAN</t>
+          <t>6-Month LTN Auction</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr"/>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>TRY 9.4T</t>
-        </is>
-      </c>
+      <c r="F299" t="inlineStr"/>
       <c r="G299" t="n">
         <v>3</v>
       </c>
@@ -8639,12 +8635,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>10-Year NTN-F Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -8662,17 +8658,21 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>Central Government DebtJAN</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr"/>
-      <c r="F301" t="inlineStr"/>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>TRY 9.4T</t>
+        </is>
+      </c>
       <c r="G301" t="n">
         <v>3</v>
       </c>
@@ -8914,18 +8914,18 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Business Climate IndicatorFEB</t>
+          <t>Business ConfidenceFEB</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>94</t>
         </is>
       </c>
       <c r="G310" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="311">
@@ -8941,18 +8941,18 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Business ConfidenceFEB</t>
+          <t>Business Climate IndicatorFEB</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>92</t>
         </is>
       </c>
       <c r="G311" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="312">
@@ -8991,14 +8991,18 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
-      <c r="E313" t="inlineStr"/>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -9049,18 +9053,14 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
+      <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -9195,27 +9195,23 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+      <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G320" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="321">
@@ -9226,23 +9222,23 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G321" t="n">
@@ -9257,23 +9253,23 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -9288,23 +9284,23 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G323" t="n">
@@ -9319,23 +9315,23 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="G324" t="n">
@@ -9350,23 +9346,27 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
-      <c r="E325" t="inlineStr"/>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G325" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="326">
@@ -9382,22 +9382,18 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
-      <c r="E326" t="inlineStr">
-        <is>
-          <t>48.5</t>
-        </is>
-      </c>
+      <c r="E326" t="inlineStr"/>
       <c r="F326" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>51</t>
         </is>
       </c>
       <c r="G326" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="327">
@@ -9444,18 +9440,22 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr"/>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>48.5</t>
+        </is>
+      </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G328" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329">
@@ -9517,18 +9517,22 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Economic Activity YoYDEC</t>
+          <t>GDP Growth Rate QoQ FinalQ4</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
-      <c r="E331" t="inlineStr"/>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>-0.6%</t>
+        </is>
+      </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="G331" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -9602,22 +9606,18 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ FinalQ4</t>
+          <t>Economic Activity YoYDEC</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
+      <c r="E334" t="inlineStr"/>
       <c r="F334" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G334" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="335">
@@ -9772,7 +9772,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
@@ -9826,7 +9826,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
@@ -9853,22 +9853,22 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="G343" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344">
@@ -9884,22 +9884,18 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
-      <c r="E344" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+      <c r="E344" t="inlineStr"/>
       <c r="F344" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="G344" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="345">
@@ -9915,22 +9911,22 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="G345" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="346">
@@ -9977,22 +9973,22 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="G347" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="348">
@@ -10008,18 +10004,22 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
-      <c r="E348" t="inlineStr"/>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="G348" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="349">
@@ -10035,22 +10035,22 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G349" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="350">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Federal Tax RevenuesJAN</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
@@ -10153,21 +10153,17 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>FDI (YTD) YoYJAN</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr"/>
-      <c r="F354" t="inlineStr">
-        <is>
-          <t>-18.0%</t>
-        </is>
-      </c>
+      <c r="F354" t="inlineStr"/>
       <c r="G354" t="n">
         <v>3</v>
       </c>
@@ -10180,17 +10176,21 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Federal Tax RevenuesJAN</t>
+          <t>FDI (YTD) YoYJAN</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr"/>
-      <c r="F355" t="inlineStr"/>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>-18.0%</t>
+        </is>
+      </c>
       <c r="G355" t="n">
         <v>3</v>
       </c>
@@ -10379,18 +10379,18 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Ifo Business ClimateFEB</t>
+          <t>Ifo ExpectationsFEB</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr"/>
       <c r="F363" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="G363" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="364">
@@ -10433,18 +10433,18 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Ifo ExpectationsFEB</t>
+          <t>Ifo Business ClimateFEB</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G365" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="366">
@@ -10460,22 +10460,22 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>CPI FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr">
         <is>
-          <t>126.71</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>126.71</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G366" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="367">
@@ -10491,18 +10491,18 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Core Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G367" t="n">
@@ -10522,18 +10522,18 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoY FinalJAN</t>
+          <t>CPI FinalJAN</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>126.71</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>126.71</t>
         </is>
       </c>
       <c r="G368" t="n">
@@ -10553,22 +10553,22 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="G369" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="370">
@@ -10699,7 +10699,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Mid-month Core Inflation Rate MoMFEB</t>
+          <t>Mid-month Core Inflation Rate YoYFEB</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
@@ -10722,7 +10722,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Mid-month Core Inflation Rate YoYFEB</t>
+          <t>Mid-month Inflation Rate MoMFEB</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Mid-month Inflation Rate MoMFEB</t>
+          <t>Mid-month Core Inflation Rate MoMFEB</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
@@ -10906,7 +10906,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -11251,6 +11251,79 @@
         <v>3</v>
       </c>
     </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2025-02-25 05:10:00-05:00</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>2-Year BTP Short Term Auction</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr"/>
+      <c r="E398" t="inlineStr"/>
+      <c r="F398" t="inlineStr"/>
+      <c r="G398" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2025-02-25 05:10:00-05:00</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>BTP€i Auction</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr"/>
+      <c r="E399" t="inlineStr"/>
+      <c r="F399" t="inlineStr"/>
+      <c r="G399" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2025-02-25 05:10:00-05:00</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Negotiated Wage GrowthQ4</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr"/>
+      <c r="E400" t="inlineStr"/>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
+      <c r="G400" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G400"/>
+  <dimension ref="A1:G403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -699,22 +699,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -734,7 +734,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -769,22 +769,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -804,22 +804,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Core Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -839,22 +839,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Deposit Growth YoYJAN/31</t>
+          <t>Bank Loan Growth YoYJAN/31</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Foreign Exchange ReservesFEB/07</t>
+          <t>Deposit Growth YoYJAN/31</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>$638.26B</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bank Loan Growth YoYJAN/31</t>
+          <t>Foreign Exchange ReservesFEB/07</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>$638.26B</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1319,27 +1319,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Manufacturing Sales MoM FinalDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1359,26 +1355,26 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1389,27 +1385,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wholesale Sales MoM FinalDEC</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1429,26 +1421,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1464,12 +1452,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1479,7 +1467,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -1494,23 +1482,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New Motor Vehicle SalesDEC</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>135.5K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>153K</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -1530,12 +1518,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1545,7 +1533,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -1565,22 +1553,26 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1591,20 +1583,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Wholesale Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>0.2%</t>
@@ -1627,22 +1623,26 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1653,23 +1653,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Manufacturing Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -1684,31 +1688,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>New Motor Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>135.5K</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>153K</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -1724,26 +1724,26 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -1759,18 +1759,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
+          <t>77.8%</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -1790,22 +1794,18 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -1825,26 +1825,26 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -1891,26 +1891,26 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Business Inventories MoMDEC</t>
+          <t>Retail Inventories Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -1926,26 +1926,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMDEC</t>
+          <t>Business Inventories MoMDEC</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>-0.1%</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -1984,22 +1984,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -2019,22 +2019,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2131,18 +2131,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GDP External Demand QoQ PrelQ4</t>
+          <t>GDP Price Index YoY PrelQ4</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -2162,22 +2158,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GDP Capital Expenditure QoQ PrelQ4</t>
+          <t>GDP Growth Rate QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -2193,22 +2189,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GDP Private Consumption QoQ PrelQ4</t>
+          <t>GDP Growth Annualized PrelQ4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -2224,22 +2220,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ PrelQ4</t>
+          <t>GDP Capital Expenditure QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -2255,22 +2251,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GDP Growth Annualized PrelQ4</t>
+          <t>GDP External Demand QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -2286,14 +2282,18 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GDP Price Index YoY PrelQ4</t>
+          <t>GDP Private Consumption QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -2537,18 +2537,18 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -2595,18 +2595,18 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -3283,12 +3283,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>European Commission Winter Forecasts</t>
+          <t>BCB Focus Market Readout</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -3333,12 +3333,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BCB Focus Market Readout</t>
+          <t>European Commission Winter Forecasts</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -3939,17 +3939,25 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>40-Year Treasury Gilt Auction</t>
+          <t>ZEW Current ConditionsFEB</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>-89</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>-89</t>
+        </is>
+      </c>
       <c r="G120" t="n">
         <v>3</v>
       </c>
@@ -3962,25 +3970,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ZEW Current ConditionsFEB</t>
+          <t>40-Year Treasury Gilt Auction</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>-89</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>-89</t>
-        </is>
-      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
         <v>3</v>
       </c>
@@ -4074,23 +4074,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>NY Empire State Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126">
@@ -4106,18 +4110,18 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
@@ -4133,18 +4137,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -4164,18 +4164,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
@@ -4191,18 +4195,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>CPI Median YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>2.4%</t>
-        </is>
-      </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -4222,18 +4222,18 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>CPI Trimmed-Mean YoYJAN</t>
+          <t>CPI Median YoYJAN</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -4248,27 +4248,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexFEB</t>
+          <t>CPI Trimmed-Mean YoYJAN</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
@@ -4549,14 +4549,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144">
@@ -4572,14 +4572,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -4595,18 +4595,18 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Machinery Orders YoYDEC</t>
+          <t>Machinery Orders MoMDEC</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -4626,22 +4626,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Machinery Orders MoMDEC</t>
+          <t>Imports YoYJAN</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147">
@@ -4657,22 +4657,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Imports YoYJAN</t>
+          <t>Exports YoYJAN</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
@@ -4688,22 +4688,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Machinery Orders YoYDEC</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>¥-2104B</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>¥-1400.0B</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
@@ -4719,22 +4719,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Exports YoYJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>¥-2104B</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>¥-1400.0B</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -4935,18 +4935,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Retail Price Index YoYJAN</t>
+          <t>Retail Price Index MoMJAN</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>3.7%</t>
-        </is>
-      </c>
+      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -4966,14 +4962,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Retail Price Index MoMJAN</t>
+          <t>PPI Output YoYJAN</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -4993,14 +4989,18 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>PPI Output YoYJAN</t>
+          <t>PPI Output MoMJAN</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -5020,18 +5020,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>PPI Output MoMJAN</t>
+          <t>PPI Input YoYJAN</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -5051,14 +5047,18 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>PPI Input YoYJAN</t>
+          <t>PPI Input MoMJAN</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -5078,18 +5078,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>PPI Input MoMJAN</t>
+          <t>PPI Core Output YoYJAN</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -5109,18 +5105,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
-      <c r="E163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G163" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164">
@@ -5136,14 +5136,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>PPI Core Output MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -5221,22 +5221,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Retail Price Index YoYJAN</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G167" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168">
@@ -5252,14 +5252,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>PPI Core Output YoYJAN</t>
+          <t>PPI Core Output MoMJAN</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -5394,21 +5394,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>ECB Non-Monetary Policy Meeting</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="F173" t="inlineStr"/>
       <c r="G173" t="n">
         <v>3</v>
       </c>
@@ -5426,18 +5422,18 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -5475,17 +5471,21 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>ECB Non-Monetary Policy Meeting</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G176" t="n">
         <v>3</v>
       </c>
@@ -5503,18 +5503,18 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G177" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178">
@@ -5784,14 +5784,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -5853,14 +5853,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="192">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -6535,14 +6535,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Loan Prime Rate 5YFEB</t>
+          <t>Loan Prime Rate 1Y</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -6562,14 +6562,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Loan Prime Rate 1Y</t>
+          <t>Loan Prime Rate 5YFEB</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -6584,19 +6584,19 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Consumer ConfidenceJAN</t>
+          <t>Leading Indicator MoMJAN</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -6616,12 +6616,16 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>M2 Money Supply YoYJAN</t>
+          <t>Current AccountQ4</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr"/>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>$ -0.6B</t>
+        </is>
+      </c>
       <c r="G220" t="n">
         <v>3</v>
       </c>
@@ -6634,19 +6638,19 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Current AccountQ4</t>
+          <t>Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
         <is>
-          <t>$ -0.6B</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -6661,21 +6665,17 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Leading Indicator MoMJAN</t>
+          <t>M2 Money Supply YoYJAN</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr"/>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
+      <c r="F222" t="inlineStr"/>
       <c r="G222" t="n">
         <v>3</v>
       </c>
@@ -6688,27 +6688,23 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+      <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G223" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="224">
@@ -6719,19 +6715,19 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Consumer ConfidenceFEB</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -6751,18 +6747,22 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
-      <c r="E225" t="inlineStr"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G225" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="226">
@@ -6869,21 +6869,17 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Construction Output YoYDEC</t>
+          <t>5-Year OAT Auction</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr"/>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
+      <c r="F230" t="inlineStr"/>
       <c r="G230" t="n">
         <v>3</v>
       </c>
@@ -6896,17 +6892,21 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>3-Year OAT Auction</t>
+          <t>Construction Output YoYDEC</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr"/>
-      <c r="F231" t="inlineStr"/>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
       <c r="G231" t="n">
         <v>3</v>
       </c>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>4-Year OAT Auction</t>
+          <t>3-Year OAT Auction</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
@@ -6947,7 +6947,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>5-Year OAT Auction</t>
+          <t>4-Year OAT Auction</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -6965,23 +6965,27 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Building Permits YoYDEC</t>
+          <t>CBI Industrial Trends OrdersFEB</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
-      <c r="E234" t="inlineStr"/>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>-30</t>
+        </is>
+      </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>-25</t>
         </is>
       </c>
       <c r="G234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
@@ -6992,27 +6996,23 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>CBI Industrial Trends OrdersFEB</t>
+          <t>Building Permits YoYDEC</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>-30</t>
-        </is>
-      </c>
+      <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
-          <t>-25</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="G235" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>18-Year Index-Linked OAT Auction</t>
+          <t>11-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>11-Year Index-Linked OAT Auction</t>
+          <t>18-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -7143,14 +7143,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -7170,14 +7170,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -7197,16 +7197,12 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr"/>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="F243" t="inlineStr"/>
       <c r="G243" t="n">
         <v>3</v>
       </c>
@@ -7224,12 +7220,16 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr"/>
-      <c r="F244" t="inlineStr"/>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="G244" t="n">
         <v>3</v>
       </c>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
@@ -7270,14 +7270,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
-      <c r="E246" t="inlineStr"/>
-      <c r="F246" t="inlineStr"/>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="G246" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="247">
@@ -7293,7 +7301,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
@@ -7316,16 +7324,12 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr"/>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="F248" t="inlineStr"/>
       <c r="G248" t="n">
         <v>3</v>
       </c>
@@ -7343,7 +7347,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
@@ -7366,18 +7370,18 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -7397,22 +7401,18 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="G251" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -7428,14 +7428,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Raw Materials Prices YoYJAN</t>
+          <t>Raw Materials Prices MoMJAN</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -7455,14 +7455,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Raw Materials Prices MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -7482,14 +7482,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -7509,18 +7509,18 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>New Housing Price Index YoYJAN</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -7536,14 +7536,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>New Housing Price Index YoYJAN</t>
+          <t>New Housing Price Index MoMJAN</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -7563,18 +7563,18 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>New Housing Price Index MoMJAN</t>
+          <t>Raw Materials Prices YoYJAN</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="G257" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="258">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
@@ -7886,7 +7886,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
@@ -7955,7 +7955,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
@@ -8207,19 +8207,23 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>S&amp;P Global Australia Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr"/>
-      <c r="F284" t="inlineStr"/>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>50.6</t>
+        </is>
+      </c>
       <c r="G284" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="285">
@@ -8235,18 +8239,18 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Australia Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
       <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G285" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="286">
@@ -8257,21 +8261,17 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Services PMI FlashFEB</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr"/>
-      <c r="F286" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
+      <c r="F286" t="inlineStr"/>
       <c r="G286" t="n">
         <v>2</v>
       </c>
@@ -8571,7 +8571,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2-Year LTN Auction</t>
+          <t>10-Year NTN-F Auction</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -8589,17 +8589,21 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>10-Year NTN-F Auction</t>
+          <t>Central Government DebtJAN</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr"/>
-      <c r="F298" t="inlineStr"/>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>TRY 9.4T</t>
+        </is>
+      </c>
       <c r="G298" t="n">
         <v>3</v>
       </c>
@@ -8658,21 +8662,17 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Central Government DebtJAN</t>
+          <t>2-Year LTN Auction</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr"/>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>TRY 9.4T</t>
-        </is>
-      </c>
+      <c r="F301" t="inlineStr"/>
       <c r="G301" t="n">
         <v>3</v>
       </c>
@@ -8690,14 +8690,14 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>HSBC Composite PMI FlashFEB</t>
+          <t>HSBC Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -8744,14 +8744,14 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>HSBC Services PMI FlashFEB</t>
+          <t>HSBC Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -8914,18 +8914,18 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Business ConfidenceFEB</t>
+          <t>Business Climate IndicatorFEB</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>92</t>
         </is>
       </c>
       <c r="G310" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311">
@@ -8941,18 +8941,18 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Business Climate IndicatorFEB</t>
+          <t>Business ConfidenceFEB</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>94</t>
         </is>
       </c>
       <c r="G311" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="312">
@@ -8991,18 +8991,14 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
+      <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -9053,14 +9049,18 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
-      <c r="E315" t="inlineStr"/>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -9080,22 +9080,22 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G316" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="317">
@@ -9138,22 +9138,22 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="G318" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319">
@@ -9195,23 +9195,27 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
-      <c r="E320" t="inlineStr"/>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G320" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="321">
@@ -9222,23 +9226,23 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G321" t="n">
@@ -9289,18 +9293,18 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="G323" t="n">
@@ -9315,23 +9319,19 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
-      <c r="E324" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
+      <c r="E324" t="inlineStr"/>
       <c r="F324" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G324" t="n">
@@ -9346,27 +9346,27 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G325" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="326">
@@ -9382,18 +9382,22 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
-      <c r="E326" t="inlineStr"/>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>48.5</t>
+        </is>
+      </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G326" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327">
@@ -9440,22 +9444,18 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>48.5</t>
-        </is>
-      </c>
+      <c r="E328" t="inlineStr"/>
       <c r="F328" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>51</t>
         </is>
       </c>
       <c r="G328" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="329">
@@ -9517,22 +9517,18 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ FinalQ4</t>
+          <t>Economic Activity YoYDEC</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
+      <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G331" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="332">
@@ -9548,22 +9544,18 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>GDP Growth Rate YoY FinalQ4</t>
+          <t>Economic Activity MoMDEC</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+      <c r="E332" t="inlineStr"/>
       <c r="F332" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G332" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="333">
@@ -9579,18 +9571,22 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Economic Activity MoMDEC</t>
+          <t>GDP Growth Rate YoY FinalQ4</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
-      <c r="E333" t="inlineStr"/>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G333" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -9606,18 +9602,22 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Economic Activity YoYDEC</t>
+          <t>GDP Growth Rate QoQ FinalQ4</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
-      <c r="E334" t="inlineStr"/>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>-0.6%</t>
+        </is>
+      </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="G334" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="335">
@@ -9799,14 +9799,14 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr"/>
       <c r="F341" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G341" t="n">
@@ -9826,14 +9826,14 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr"/>
       <c r="F342" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G342" t="n">
@@ -9853,22 +9853,22 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="G343" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="344">
@@ -9884,18 +9884,22 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
-      <c r="E344" t="inlineStr"/>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G344" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -9911,18 +9915,14 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
-      <c r="E345" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
+      <c r="E345" t="inlineStr"/>
       <c r="F345" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="G345" t="n">
@@ -9942,18 +9942,18 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G346" t="n">
@@ -10004,22 +10004,22 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
       <c r="E348" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="G348" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="349">
@@ -10035,18 +10035,18 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="G349" t="n">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Federal Tax RevenuesJAN</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
@@ -10153,17 +10153,21 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>FDI (YTD) YoYJAN</t>
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr"/>
-      <c r="F354" t="inlineStr"/>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>-18.0%</t>
+        </is>
+      </c>
       <c r="G354" t="n">
         <v>3</v>
       </c>
@@ -10176,21 +10180,17 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>FDI (YTD) YoYJAN</t>
+          <t>Federal Tax RevenuesJAN</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr"/>
-      <c r="F355" t="inlineStr">
-        <is>
-          <t>-18.0%</t>
-        </is>
-      </c>
+      <c r="F355" t="inlineStr"/>
       <c r="G355" t="n">
         <v>3</v>
       </c>
@@ -10229,14 +10229,14 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr"/>
       <c r="F357" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G357" t="n">
@@ -10256,14 +10256,14 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D358" t="inlineStr"/>
       <c r="E358" t="inlineStr"/>
       <c r="F358" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G358" t="n">
@@ -10333,14 +10333,14 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Business ConfidenceFEB</t>
+          <t>Capacity UtilizationFEB</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
       <c r="E361" t="inlineStr"/>
       <c r="F361" t="inlineStr"/>
       <c r="G361" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="362">
@@ -10356,14 +10356,14 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Capacity UtilizationFEB</t>
+          <t>Business ConfidenceFEB</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr"/>
       <c r="F362" t="inlineStr"/>
       <c r="G362" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="363">
@@ -10379,14 +10379,14 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Ifo ExpectationsFEB</t>
+          <t>Ifo Current ConditionsFEB</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr"/>
       <c r="F363" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="G363" t="n">
@@ -10406,18 +10406,18 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Ifo Current ConditionsFEB</t>
+          <t>Ifo Business ClimateFEB</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G364" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="365">
@@ -10433,18 +10433,18 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Ifo Business ClimateFEB</t>
+          <t>Ifo ExpectationsFEB</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="G365" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="366">
@@ -10491,18 +10491,18 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="G367" t="n">
@@ -10522,18 +10522,18 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>CPI FinalJAN</t>
+          <t>Core Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr">
         <is>
-          <t>126.71</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>126.71</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G368" t="n">
@@ -10553,18 +10553,18 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>CPI FinalJAN</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>126.71</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>126.71</t>
         </is>
       </c>
       <c r="G369" t="n">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Mid-month Inflation Rate YoYFEB</t>
+          <t>Mid-month Core Inflation Rate MoMFEB</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Mid-month Core Inflation Rate MoMFEB</t>
+          <t>Mid-month Inflation Rate YoYFEB</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
@@ -10997,12 +10997,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>MAS 12-Week Bill Auction</t>
+          <t>20-Year KTB Auction</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>MAS 4-Week Bill Auction</t>
+          <t>MAS 12-Week Bill Auction</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -11043,12 +11043,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>20-Year KTB Auction</t>
+          <t>MAS 4-Week Bill Auction</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -11098,14 +11098,14 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="D392" t="inlineStr"/>
       <c r="E392" t="inlineStr"/>
       <c r="F392" t="inlineStr">
         <is>
-          <t>SAR 94.5B</t>
+          <t>SAR 60.5B</t>
         </is>
       </c>
       <c r="G392" t="n">
@@ -11125,14 +11125,14 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="D393" t="inlineStr"/>
       <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr">
         <is>
-          <t>SAR 60.5B</t>
+          <t>SAR 94.5B</t>
         </is>
       </c>
       <c r="G393" t="n">
@@ -11147,25 +11147,17 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ FinalQ4</t>
+          <t>New Car Registrations YoYJAN</t>
         </is>
       </c>
       <c r="D394" t="inlineStr"/>
-      <c r="E394" t="inlineStr">
-        <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="F394" t="inlineStr">
-        <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
+      <c r="E394" t="inlineStr"/>
+      <c r="F394" t="inlineStr"/>
       <c r="G394" t="n">
         <v>2</v>
       </c>
@@ -11183,7 +11175,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>GDP Growth Rate YoY FinalQ4</t>
+          <t>GDP Growth Rate QoQ FinalQ4</t>
         </is>
       </c>
       <c r="D395" t="inlineStr"/>
@@ -11209,17 +11201,25 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>New Car Registrations YoYJAN</t>
+          <t>GDP Growth Rate YoY FinalQ4</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
-      <c r="E396" t="inlineStr"/>
-      <c r="F396" t="inlineStr"/>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
       <c r="G396" t="n">
         <v>2</v>
       </c>
@@ -11264,7 +11264,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>2-Year BTP Short Term Auction</t>
+          <t>BTP€i Auction</t>
         </is>
       </c>
       <c r="D398" t="inlineStr"/>
@@ -11287,7 +11287,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>BTP€i Auction</t>
+          <t>2-Year BTP Short Term Auction</t>
         </is>
       </c>
       <c r="D399" t="inlineStr"/>
@@ -11324,6 +11324,83 @@
         <v>3</v>
       </c>
     </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2025-02-25 05:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Bund/g Auction</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr"/>
+      <c r="E401" t="inlineStr"/>
+      <c r="F401" t="inlineStr"/>
+      <c r="G401" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2025-02-25 06:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>CBI Distributive TradesFEB</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr"/>
+      <c r="E402" t="inlineStr"/>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>-26</t>
+        </is>
+      </c>
+      <c r="G402" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2025-02-25 06:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Negotiated Wage GrowthQ4</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr"/>
+      <c r="E403" t="inlineStr"/>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
+      <c r="G403" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G406"/>
+  <dimension ref="A1:G414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -699,22 +699,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -734,22 +734,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -769,7 +769,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -779,12 +779,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -804,22 +804,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Core Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -839,22 +839,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Deposit Growth YoYJAN/31</t>
+          <t>Foreign Exchange ReservesFEB/07</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>$638.26B</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Foreign Exchange ReservesFEB/07</t>
+          <t>Bank Loan Growth YoYJAN/31</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>$638.26B</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bank Loan Growth YoYJAN/31</t>
+          <t>Deposit Growth YoYJAN/31</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1319,27 +1319,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Manufacturing Sales MoM FinalDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1354,23 +1350,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New Motor Vehicle SalesDEC</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>135.5K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>153K</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1390,26 +1386,26 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1425,26 +1421,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1460,12 +1452,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1475,7 +1467,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -1490,27 +1482,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Wholesale Sales MoM FinalDEC</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -1530,12 +1518,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1545,7 +1533,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -1565,22 +1553,26 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1596,22 +1588,26 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1622,31 +1618,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>New Motor Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>135.5K</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>153K</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -1657,23 +1649,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Manufacturing Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -1688,23 +1684,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Wholesale Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -1891,26 +1891,26 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Business Inventories MoMDEC</t>
+          <t>Retail Inventories Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -1926,26 +1926,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMDEC</t>
+          <t>Business Inventories MoMDEC</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>-0.1%</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -1984,22 +1984,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -2019,22 +2019,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/14</t>
+          <t>Baker Hughes Total Rigs CountFEB/14</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>588</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/14</t>
+          <t>Baker Hughes Oil Rig CountFEB/14</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>481</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2131,14 +2131,18 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GDP Price Index YoY PrelQ4</t>
+          <t>GDP Private Consumption QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -2220,22 +2224,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GDP Private Consumption QoQ PrelQ4</t>
+          <t>GDP Growth Annualized PrelQ4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -2251,22 +2255,18 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ PrelQ4</t>
+          <t>GDP Price Index YoY PrelQ4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -2282,22 +2282,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GDP Growth Annualized PrelQ4</t>
+          <t>GDP Growth Rate QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -2487,18 +2487,18 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -2518,14 +2518,18 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Wholesale Prices YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -2567,25 +2571,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Eurogroup Meeting</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
         <v>3</v>
       </c>
@@ -2629,17 +2625,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Eurogroup Meeting</t>
+          <t>Wholesale Prices YoYJAN</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1.3%</t>
+        </is>
+      </c>
       <c r="G70" t="n">
         <v>3</v>
       </c>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2769,14 +2769,10 @@
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>€4.35B</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>€4.5B</t>
+          <t>€ -4.9B</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -2791,7 +2787,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2800,10 +2796,14 @@
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>€4.35B</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>€ -4.9B</t>
+          <t>€4.5B</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>12-Month BTF Auction</t>
+          <t>3-Month BTF Auction</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>3-Month BTF Auction</t>
+          <t>12-Month BTF Auction</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -3214,12 +3214,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>ECOFIN Meeting</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -3242,16 +3242,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>$-24.0B</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="n">
         <v>2</v>
       </c>
@@ -3264,12 +3260,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>BCB Focus Market Readout</t>
+          <t>European Commission Winter Forecasts</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -3287,17 +3283,21 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ECOFIN Meeting</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>$-24.0B</t>
+        </is>
+      </c>
       <c r="G96" t="n">
         <v>2</v>
       </c>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -3360,12 +3360,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>European Commission Winter Forecasts</t>
+          <t>BCB Focus Market Readout</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Claimant Count ChangeJAN</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>7.0K</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -3542,18 +3542,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>HMRC Payrolls ChangeJAN</t>
+          <t>Average Earnings incl. Bonus (3Mo/Yr)DEC</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>5.9%</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>-55.0K</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -3569,18 +3573,18 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Average Earnings excl. Bonus (3Mo/Yr)DEC</t>
+          <t>Employment ChangeDEC</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>-130K</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3596,22 +3600,18 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Average Earnings incl. Bonus (3Mo/Yr)DEC</t>
+          <t>Average Earnings excl. Bonus (3Mo/Yr)DEC</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr">
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
         <is>
           <t>5.9%</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>5.9%</t>
-        </is>
-      </c>
       <c r="G108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3627,18 +3627,18 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Employment ChangeDEC</t>
+          <t>HMRC Payrolls ChangeJAN</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>-130K</t>
+          <t>-55.0K</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3654,22 +3654,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Claimant Count ChangeJAN</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>7.0K</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3685,22 +3685,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3716,18 +3716,18 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -3747,22 +3747,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
@@ -3804,23 +3804,19 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Labour Productivity QoQ FinalQ3</t>
+          <t>Unemployed PersonsQ4</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>8.1M</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -3862,19 +3858,23 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Unemployed PersonsQ4</t>
+          <t>Labour Productivity QoQ FinalQ3</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>8.1M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3948,18 +3948,14 @@
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr">
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="G120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
@@ -3975,22 +3971,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ZEW Current ConditionsFEB</t>
+          <t>ZEW Economic Sentiment IndexFEB</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>-89</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>-89</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -4001,17 +3997,25 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>40-Year Treasury Gilt Auction</t>
+          <t>ZEW Current ConditionsFEB</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>-89</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>-89</t>
+        </is>
+      </c>
       <c r="G122" t="n">
         <v>3</v>
       </c>
@@ -4024,23 +4028,19 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ZEW Economic Sentiment IndexFEB</t>
+          <t>40-Year Treasury Gilt Auction</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="F123" t="inlineStr"/>
       <c r="G123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
@@ -4172,18 +4172,18 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
@@ -4257,18 +4257,18 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
@@ -4595,22 +4595,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Imports YoYJAN</t>
+          <t>Machinery Orders YoYDEC</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -4657,22 +4657,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Exports YoYJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>¥-2104B</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>¥-1400.0B</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -4688,18 +4688,18 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Machinery Orders YoYDEC</t>
+          <t>Exports YoYJAN</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -4719,22 +4719,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Imports YoYJAN</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>¥-2104B</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>¥-1400.0B</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="150">
@@ -4884,12 +4884,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Annual Budget Speech</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -4907,12 +4907,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Annual Budget Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -4935,14 +4935,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>PPI Output YoYJAN</t>
+          <t>PPI Input YoYJAN</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -4962,18 +4962,18 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>PPI Output MoMJAN</t>
+          <t>PPI Input MoMJAN</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -4993,14 +4993,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>PPI Input YoYJAN</t>
+          <t>PPI Core Output YoYJAN</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -5020,18 +5020,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>PPI Input MoMJAN</t>
+          <t>PPI Core Output MoMJAN</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -5051,14 +5047,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>PPI Core Output YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -5078,18 +5074,18 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>PPI Core Output MoMJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="G162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -5105,7 +5101,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Retail Price Index YoYJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -5116,11 +5112,11 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G163" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
@@ -5136,18 +5132,18 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Retail Price Index MoMJAN</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165">
@@ -5163,22 +5159,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>PPI Output MoMJAN</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G165" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="166">
@@ -5194,22 +5190,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Retail Price Index YoYJAN</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G166" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="167">
@@ -5225,18 +5221,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Retail Price Index MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G167" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168">
@@ -5252,14 +5252,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>PPI Output YoYJAN</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -5394,19 +5394,23 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>ECB Non-Monetary Policy Meeting</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="G173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -5422,7 +5426,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -5433,7 +5437,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -5449,18 +5453,18 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -5476,7 +5480,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -5487,7 +5491,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -5498,21 +5502,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>ECB Non-Monetary Policy Meeting</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>3.6%</t>
-        </is>
-      </c>
+      <c r="F177" t="inlineStr"/>
       <c r="G177" t="n">
         <v>3</v>
       </c>
@@ -5583,17 +5583,21 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>4-Year Treasury Gilt Auction</t>
+          <t>Current AccountDEC</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>€ 3780M</t>
+        </is>
+      </c>
       <c r="G180" t="n">
         <v>3</v>
       </c>
@@ -5606,21 +5610,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Current AccountDEC</t>
+          <t>4-Year Treasury Gilt Auction</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>€ 3780M</t>
-        </is>
-      </c>
+      <c r="F181" t="inlineStr"/>
       <c r="G181" t="n">
         <v>3</v>
       </c>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -5784,14 +5784,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189">
@@ -5807,14 +5807,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -5899,18 +5899,18 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
-          <t>1.45M</t>
+          <t>1.39M</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -5930,14 +5930,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -5957,14 +5957,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -5984,18 +5984,18 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
-          <t>1.39M</t>
+          <t>1.45M</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -6242,14 +6242,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -6269,14 +6269,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -6388,22 +6388,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G212" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213">
@@ -6419,22 +6419,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="G213" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="214">
@@ -6589,12 +6589,16 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>M2 Money Supply YoYJAN</t>
+          <t>Current AccountQ4</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr"/>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>$ -0.6B</t>
+        </is>
+      </c>
       <c r="G219" t="n">
         <v>3</v>
       </c>
@@ -6612,16 +6616,12 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Current AccountQ4</t>
+          <t>M2 Money Supply YoYJAN</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>$ -0.6B</t>
-        </is>
-      </c>
+      <c r="F220" t="inlineStr"/>
       <c r="G220" t="n">
         <v>3</v>
       </c>
@@ -6688,19 +6688,19 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Consumer ConfidenceFEB</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -6720,18 +6720,22 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
-      <c r="E224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G224" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="225">
@@ -6742,27 +6746,23 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+      <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G225" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="226">
@@ -6869,17 +6869,21 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>4-Year OAT Auction</t>
+          <t>Construction Output YoYDEC</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr"/>
-      <c r="F230" t="inlineStr"/>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
       <c r="G230" t="n">
         <v>3</v>
       </c>
@@ -6892,21 +6896,17 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Construction Output YoYDEC</t>
+          <t>3-Year OAT Auction</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr"/>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
+      <c r="F231" t="inlineStr"/>
       <c r="G231" t="n">
         <v>3</v>
       </c>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>3-Year OAT Auction</t>
+          <t>4-Year OAT Auction</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
@@ -6965,27 +6965,23 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>CBI Industrial Trends OrdersFEB</t>
+          <t>Building Permits YoYDEC</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>-30</t>
-        </is>
-      </c>
+      <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
-          <t>-25</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="G234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235">
@@ -6996,23 +6992,27 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Building Permits YoYDEC</t>
+          <t>CBI Industrial Trends OrdersFEB</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>-30</t>
+        </is>
+      </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>-25</t>
         </is>
       </c>
       <c r="G235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>11-Year Index-Linked OAT Auction</t>
+          <t>7-Year OATi Auction</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>18-Year Index-Linked OAT Auction</t>
+          <t>11-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>6-Year Index-Linked OAT Auction</t>
+          <t>18-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>7-Year OATi Auction</t>
+          <t>6-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -7224,14 +7224,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
-      <c r="E244" t="inlineStr"/>
-      <c r="F244" t="inlineStr"/>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="G244" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="245">
@@ -7270,22 +7278,14 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr"/>
       <c r="G246" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="247">
@@ -7301,16 +7301,12 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr"/>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="F247" t="inlineStr"/>
       <c r="G247" t="n">
         <v>3</v>
       </c>
@@ -7374,14 +7370,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
-      <c r="E250" t="inlineStr"/>
-      <c r="F250" t="inlineStr"/>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="G250" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
@@ -7392,27 +7396,23 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Raw Materials Prices YoYJAN</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="G251" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -7423,19 +7423,19 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Raw Materials Prices YoYJAN</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -7455,14 +7455,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Raw Materials Prices MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -7482,14 +7482,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -7509,18 +7509,18 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>New Housing Price Index YoYJAN</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -7536,14 +7536,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>New Housing Price Index YoYJAN</t>
+          <t>New Housing Price Index MoMJAN</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -7563,18 +7563,18 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>New Housing Price Index MoMJAN</t>
+          <t>Raw Materials Prices MoMJAN</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G257" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="258">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
@@ -7886,7 +7886,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
@@ -7932,7 +7932,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
@@ -7955,7 +7955,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
@@ -8235,18 +8235,18 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Australia Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
       <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="G285" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="286">
@@ -8262,14 +8262,14 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Services PMI FlashFEB</t>
+          <t>S&amp;P Global Australia Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -8289,18 +8289,18 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Australia Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G287" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="288">
@@ -8401,14 +8401,14 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate Ex-Food and Energy YoYJAN</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -8428,14 +8428,14 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Inflation Rate Ex-Food and Energy YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -8517,18 +8517,18 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Jibun Bank Composite PMI FlashFEB</t>
+          <t>Jibun Bank Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
       <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G295" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="296">
@@ -8544,18 +8544,18 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Jibun Bank Services PMI FlashFEB</t>
+          <t>Jibun Bank Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr"/>
       <c r="F296" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="G296" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="297">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>10-Year NTN-F Auction</t>
+          <t>2-Year LTN Auction</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -8589,21 +8589,17 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Central Government DebtJAN</t>
+          <t>6-Month LTN Auction</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr"/>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t>TRY 9.4T</t>
-        </is>
-      </c>
+      <c r="F298" t="inlineStr"/>
       <c r="G298" t="n">
         <v>3</v>
       </c>
@@ -8616,12 +8612,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>6-Month LTN Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -8639,17 +8635,21 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2-Year LTN Auction</t>
+          <t>Central Government DebtJAN</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr"/>
-      <c r="F300" t="inlineStr"/>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>TRY 9.4T</t>
+        </is>
+      </c>
       <c r="G300" t="n">
         <v>3</v>
       </c>
@@ -8662,12 +8662,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>10-Year NTN-F Auction</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -8690,14 +8690,14 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>HSBC Services PMI FlashFEB</t>
+          <t>HSBC Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -8717,14 +8717,14 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>HSBC Composite PMI FlashFEB</t>
+          <t>HSBC Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -8744,14 +8744,14 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>HSBC Manufacturing PMI FlashFEB</t>
+          <t>HSBC Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -8771,22 +8771,22 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Public Sector Net Borrowing Ex BanksJAN</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>£20.5B</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>£19.0B</t>
         </is>
       </c>
       <c r="G305" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306">
@@ -8829,18 +8829,14 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Public Sector Net Borrowing Ex BanksJAN</t>
+          <t>Retail Sales ex Fuel YoYJAN</t>
         </is>
       </c>
       <c r="D307" t="inlineStr"/>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>£20.5B</t>
-        </is>
-      </c>
+      <c r="E307" t="inlineStr"/>
       <c r="F307" t="inlineStr">
         <is>
-          <t>£19.0B</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -8860,18 +8856,22 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Retail Sales ex Fuel MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
-      <c r="E308" t="inlineStr"/>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G308" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309">
@@ -8887,14 +8887,14 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Retail Sales ex Fuel YoYJAN</t>
+          <t>Retail Sales ex Fuel MoMJAN</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -8991,18 +8991,18 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -9022,18 +9022,14 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
+      <c r="E314" t="inlineStr"/>
       <c r="F314" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -9053,14 +9049,18 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
-      <c r="E315" t="inlineStr"/>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -9080,22 +9080,22 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G316" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="317">
@@ -9111,18 +9111,22 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
-      <c r="E317" t="inlineStr"/>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>45.5</t>
+        </is>
+      </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="G317" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318">
@@ -9138,18 +9142,14 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>52.5</t>
-        </is>
-      </c>
+      <c r="E318" t="inlineStr"/>
       <c r="F318" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="G318" t="n">
@@ -9169,18 +9169,18 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -9200,18 +9200,18 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G320" t="n">
@@ -9226,27 +9226,23 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
-      <c r="E321" t="inlineStr">
-        <is>
-          <t>1.7%</t>
-        </is>
-      </c>
+      <c r="E321" t="inlineStr"/>
       <c r="F321" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G321" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="322">
@@ -9262,18 +9258,18 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -9293,22 +9289,22 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G323" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="324">
@@ -9319,23 +9315,27 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
-      <c r="E324" t="inlineStr"/>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>1.7%</t>
+        </is>
+      </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="G324" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="325">
@@ -9351,22 +9351,22 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G325" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="326">
@@ -9517,18 +9517,22 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Economic Activity YoYDEC</t>
+          <t>GDP Growth Rate QoQ FinalQ4</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
-      <c r="E331" t="inlineStr"/>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>-0.6%</t>
+        </is>
+      </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="G331" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -9544,18 +9548,18 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ FinalQ4</t>
+          <t>GDP Growth Rate YoY FinalQ4</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G332" t="n">
@@ -9575,22 +9579,18 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>GDP Growth Rate YoY FinalQ4</t>
+          <t>Economic Activity MoMDEC</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+      <c r="E333" t="inlineStr"/>
       <c r="F333" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G333" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="334">
@@ -9606,14 +9606,14 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Economic Activity MoMDEC</t>
+          <t>Economic Activity YoYDEC</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr"/>
       <c r="F334" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G334" t="n">
@@ -9772,14 +9772,14 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr"/>
       <c r="F340" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G340" t="n">
@@ -9799,14 +9799,14 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr"/>
       <c r="F341" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G341" t="n">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
@@ -9853,22 +9853,18 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
-      <c r="E343" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="E343" t="inlineStr"/>
       <c r="F343" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="G343" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="344">
@@ -9884,22 +9880,22 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="G344" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
@@ -9946,22 +9942,22 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G346" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="347">
@@ -9977,22 +9973,22 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="G347" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="348">
@@ -10008,22 +10004,22 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
       <c r="E348" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="G348" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="349">
@@ -10039,18 +10035,22 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
-      <c r="E349" t="inlineStr"/>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G349" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="350">
@@ -10107,21 +10107,17 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>FDI (YTD) YoYJAN</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="D352" t="inlineStr"/>
       <c r="E352" t="inlineStr"/>
-      <c r="F352" t="inlineStr">
-        <is>
-          <t>-18.0%</t>
-        </is>
-      </c>
+      <c r="F352" t="inlineStr"/>
       <c r="G352" t="n">
         <v>3</v>
       </c>
@@ -10134,17 +10130,21 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Federal Tax RevenuesJAN</t>
+          <t>FDI (YTD) YoYJAN</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr"/>
-      <c r="F353" t="inlineStr"/>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>-18.0%</t>
+        </is>
+      </c>
       <c r="G353" t="n">
         <v>3</v>
       </c>
@@ -10162,7 +10162,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
@@ -10180,12 +10180,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Federal Tax RevenuesJAN</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
@@ -10224,17 +10224,21 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>5-Year KTB Auction</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr"/>
-      <c r="F357" t="inlineStr"/>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
       <c r="G357" t="n">
         <v>3</v>
       </c>
@@ -10247,21 +10251,17 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>5-Year KTB Auction</t>
         </is>
       </c>
       <c r="D358" t="inlineStr"/>
       <c r="E358" t="inlineStr"/>
-      <c r="F358" t="inlineStr">
-        <is>
-          <t>2.0%</t>
-        </is>
-      </c>
+      <c r="F358" t="inlineStr"/>
       <c r="G358" t="n">
         <v>3</v>
       </c>
@@ -10306,14 +10306,14 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
       <c r="E360" t="inlineStr"/>
       <c r="F360" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G360" t="n">
@@ -10333,14 +10333,14 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Business ConfidenceFEB</t>
+          <t>Capacity UtilizationFEB</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
       <c r="E361" t="inlineStr"/>
       <c r="F361" t="inlineStr"/>
       <c r="G361" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="362">
@@ -10356,14 +10356,14 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Capacity UtilizationFEB</t>
+          <t>Business ConfidenceFEB</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr"/>
       <c r="F362" t="inlineStr"/>
       <c r="G362" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="363">
@@ -10379,18 +10379,18 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Ifo ExpectationsFEB</t>
+          <t>Ifo Business ClimateFEB</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr"/>
       <c r="F363" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G363" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="364">
@@ -10406,18 +10406,18 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Ifo Business ClimateFEB</t>
+          <t>Ifo Current ConditionsFEB</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="G364" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="365">
@@ -10433,14 +10433,14 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Ifo Current ConditionsFEB</t>
+          <t>Ifo ExpectationsFEB</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>83</t>
         </is>
       </c>
       <c r="G365" t="n">
@@ -10460,22 +10460,22 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G366" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="367">
@@ -10491,22 +10491,22 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="G367" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="368">
@@ -10522,18 +10522,18 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>CPI FinalJAN</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>126.71</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>126.71</t>
         </is>
       </c>
       <c r="G368" t="n">
@@ -10553,18 +10553,18 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>CPI FinalJAN</t>
+          <t>Core Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
-          <t>126.71</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>126.71</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G369" t="n">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Mid-month Core Inflation Rate MoMFEB</t>
+          <t>Mid-month Core Inflation Rate YoYFEB</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Mid-month Core Inflation Rate YoYFEB</t>
+          <t>Mid-month Inflation Rate YoYFEB</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Mid-month Inflation Rate YoYFEB</t>
+          <t>Mid-month Core Inflation Rate MoMFEB</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
@@ -10997,12 +10997,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>20-Year KTB Auction</t>
+          <t>MAS 12-Week Bill Auction</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>MAS 12-Week Bill Auction</t>
+          <t>MAS 4-Week Bill Auction</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -11043,12 +11043,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>MAS 4-Week Bill Auction</t>
+          <t>20-Year KTB Auction</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -11071,14 +11071,14 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
       <c r="E391" t="inlineStr"/>
       <c r="F391" t="inlineStr">
         <is>
-          <t>SAR 94.5B</t>
+          <t>SAR 60.5B</t>
         </is>
       </c>
       <c r="G391" t="n">
@@ -11098,14 +11098,14 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="D392" t="inlineStr"/>
       <c r="E392" t="inlineStr"/>
       <c r="F392" t="inlineStr">
         <is>
-          <t>SAR 34B</t>
+          <t>SAR 94.5B</t>
         </is>
       </c>
       <c r="G392" t="n">
@@ -11125,14 +11125,14 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>Balance of TradeDEC</t>
         </is>
       </c>
       <c r="D393" t="inlineStr"/>
       <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr">
         <is>
-          <t>SAR 60.5B</t>
+          <t>SAR 34B</t>
         </is>
       </c>
       <c r="G393" t="n">
@@ -11147,23 +11147,19 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Leading Business Cycle Indicator MoMDEC</t>
+          <t>New Car Registrations YoYJAN</t>
         </is>
       </c>
       <c r="D394" t="inlineStr"/>
       <c r="E394" t="inlineStr"/>
-      <c r="F394" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="F394" t="inlineStr"/>
       <c r="G394" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="395">
@@ -11179,7 +11175,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>GDP Growth Rate YoY FinalQ4</t>
+          <t>GDP Growth Rate QoQ FinalQ4</t>
         </is>
       </c>
       <c r="D395" t="inlineStr"/>
@@ -11210,7 +11206,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ FinalQ4</t>
+          <t>GDP Growth Rate YoY FinalQ4</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
@@ -11236,19 +11232,23 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>New Car Registrations YoYJAN</t>
+          <t>Leading Business Cycle Indicator MoMDEC</t>
         </is>
       </c>
       <c r="D397" t="inlineStr"/>
       <c r="E397" t="inlineStr"/>
-      <c r="F397" t="inlineStr"/>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="G397" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="398">
@@ -11259,17 +11259,21 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>2-Year BTP Short Term Auction</t>
+          <t>Negotiated Wage GrowthQ4</t>
         </is>
       </c>
       <c r="D398" t="inlineStr"/>
       <c r="E398" t="inlineStr"/>
-      <c r="F398" t="inlineStr"/>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
       <c r="G398" t="n">
         <v>3</v>
       </c>
@@ -11282,21 +11286,17 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Negotiated Wage GrowthQ4</t>
+          <t>BTP€i Auction</t>
         </is>
       </c>
       <c r="D399" t="inlineStr"/>
       <c r="E399" t="inlineStr"/>
-      <c r="F399" t="inlineStr">
-        <is>
-          <t>5.1%</t>
-        </is>
-      </c>
+      <c r="F399" t="inlineStr"/>
       <c r="G399" t="n">
         <v>3</v>
       </c>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>BTP€i Auction</t>
+          <t>2-Year BTP Short Term Auction</t>
         </is>
       </c>
       <c r="D400" t="inlineStr"/>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>IPCA mid-month CPI YoYFEB</t>
+          <t>IPCA mid-month CPI MoMFEB</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
@@ -11437,7 +11437,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>IPCA mid-month CPI MoMFEB</t>
+          <t>IPCA mid-month CPI YoYFEB</t>
         </is>
       </c>
       <c r="D405" t="inlineStr"/>
@@ -11474,6 +11474,198 @@
         <v>3</v>
       </c>
     </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2025-02-25 08:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Manufacturing Sales MoM PrelJAN</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr"/>
+      <c r="E407" t="inlineStr"/>
+      <c r="F407" t="inlineStr"/>
+      <c r="G407" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2025-02-25 08:55:00-05:00</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Redbook YoYFEB/22</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr"/>
+      <c r="E408" t="inlineStr"/>
+      <c r="F408" t="inlineStr"/>
+      <c r="G408" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2025-02-25 09:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr"/>
+      <c r="E409" t="inlineStr"/>
+      <c r="F409" t="inlineStr"/>
+      <c r="G409" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2025-02-25 09:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr"/>
+      <c r="E410" t="inlineStr"/>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="G410" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2025-02-25 09:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>House Price IndexDEC</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr"/>
+      <c r="E411" t="inlineStr"/>
+      <c r="F411" t="inlineStr"/>
+      <c r="G411" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2025-02-25 09:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>House Price Index MoMDEC</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr"/>
+      <c r="E412" t="inlineStr"/>
+      <c r="F412" t="inlineStr"/>
+      <c r="G412" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2025-02-25 09:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>House Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr"/>
+      <c r="G413" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2025-02-25 09:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Negotiated Wage GrowthQ4</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
+      <c r="G414" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G414"/>
+  <dimension ref="A1:G420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -699,22 +699,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Core Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -734,7 +734,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -769,22 +769,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -804,22 +804,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -839,22 +839,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Foreign Exchange ReservesFEB/07</t>
+          <t>Bank Loan Growth YoYJAN/31</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>$638.26B</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bank Loan Growth YoYJAN/31</t>
+          <t>Deposit Growth YoYJAN/31</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Deposit Growth YoYJAN/31</t>
+          <t>Foreign Exchange ReservesFEB/07</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>$638.26B</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1319,23 +1319,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Manufacturing Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1350,23 +1354,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Wholesale Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1381,31 +1389,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>New Motor Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>135.5K</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>153K</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1421,22 +1425,26 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1452,12 +1460,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1467,7 +1475,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -1487,22 +1495,26 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1518,12 +1530,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1533,7 +1545,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -1553,26 +1565,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -1588,26 +1596,26 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -1618,23 +1626,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New Motor Vehicle SalesDEC</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>135.5K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>153K</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -1649,27 +1657,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Manufacturing Sales MoM FinalDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -1684,27 +1688,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Wholesale Sales MoM FinalDEC</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -1891,26 +1891,26 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMDEC</t>
+          <t>Business Inventories MoMDEC</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>-0.1%</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
       <c r="G45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -1926,26 +1926,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Business Inventories MoMDEC</t>
+          <t>Retail Inventories Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -1984,22 +1984,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -2019,22 +2019,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/14</t>
+          <t>Baker Hughes Oil Rig CountFEB/14</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>481</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/14</t>
+          <t>Baker Hughes Total Rigs CountFEB/14</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>588</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2482,23 +2482,19 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Vehicle Sales YoYJAN</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -2518,18 +2514,18 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -2544,19 +2540,19 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Vehicle Sales YoYJAN</t>
+          <t>Wholesale Prices YoYJAN</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -2571,17 +2567,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Eurogroup Meeting</t>
+          <t>Tertiary Industry Index MoMDEC</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G68" t="n">
         <v>3</v>
       </c>
@@ -2594,25 +2598,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tertiary Industry Index MoMDEC</t>
+          <t>Eurogroup Meeting</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
         <v>3</v>
       </c>
@@ -2625,19 +2621,19 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Wholesale Prices YoYJAN</t>
+          <t>Industrial Production YoY FinalDEC</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -2652,23 +2648,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Industrial Production MoM FinalDEC</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -2715,14 +2711,18 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Industrial Production YoY FinalDEC</t>
+          <t>Industrial Production MoM FinalDEC</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -3260,12 +3260,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>European Commission Winter Forecasts</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -3283,19 +3283,19 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Budget BalanceJAN</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>$-24.0B</t>
+          <t>TRY-150.0B</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>BCB Focus Market Readout</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -3333,19 +3333,19 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Budget BalanceJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>TRY-150.0B</t>
+          <t>$-24.0B</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -3360,17 +3360,21 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>BCB Focus Market Readout</t>
+          <t>Auto Sales YoYJAN</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>6.0%</t>
+        </is>
+      </c>
       <c r="G99" t="n">
         <v>2</v>
       </c>
@@ -3383,21 +3387,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Auto Production YoYJAN</t>
+          <t>European Commission Winter Forecasts</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="F100" t="inlineStr"/>
       <c r="G100" t="n">
         <v>2</v>
       </c>
@@ -3438,14 +3438,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Auto Sales YoYJAN</t>
+          <t>Auto Production YoYJAN</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -3685,18 +3685,18 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -3716,18 +3716,18 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -3747,18 +3747,18 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -3778,18 +3778,18 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -4079,18 +4079,18 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CPI Trimmed-Mean YoYJAN</t>
+          <t>CPI Median YoYJAN</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -4141,18 +4141,18 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>CPI Median YoYJAN</t>
+          <t>CPI Trimmed-Mean YoYJAN</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -4199,14 +4199,18 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -4226,18 +4230,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -4453,14 +4453,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
@@ -4476,14 +4476,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141">
@@ -4526,14 +4526,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143">
@@ -4549,14 +4549,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -4657,22 +4657,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Exports YoYJAN</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>¥-2104B</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>¥-1400.0B</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
@@ -4688,22 +4688,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Exports YoYJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>¥-2104B</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>¥-1400.0B</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -4884,12 +4884,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Annual Budget Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -4907,12 +4907,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Annual Budget Speech</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -4935,14 +4935,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>PPI Input YoYJAN</t>
+          <t>PPI Core Output YoYJAN</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -4962,18 +4962,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>PPI Input MoMJAN</t>
+          <t>PPI Core Output MoMJAN</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -4993,14 +4989,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>PPI Core Output YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -5020,18 +5016,18 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>PPI Core Output MoMJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="G160" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
@@ -5047,18 +5043,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>3.7%</t>
+        </is>
+      </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
@@ -5074,18 +5074,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
@@ -5101,22 +5105,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>PPI Input MoMJAN</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164">
@@ -5132,14 +5136,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Retail Price Index MoMJAN</t>
+          <t>PPI Output YoYJAN</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -5159,18 +5163,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>PPI Output MoMJAN</t>
+          <t>Retail Price Index MoMJAN</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -5221,22 +5221,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>PPI Output MoMJAN</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G167" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168">
@@ -5252,14 +5252,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>PPI Output YoYJAN</t>
+          <t>PPI Input YoYJAN</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -5337,18 +5337,18 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Deposit Facility RateFEB</t>
+          <t>Lending Facility RateFEB</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -5368,18 +5368,18 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Lending Facility RateFEB</t>
+          <t>Deposit Facility RateFEB</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -5399,14 +5399,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -5426,18 +5426,18 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -5453,14 +5453,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -5480,18 +5480,18 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -5530,14 +5530,18 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Current AccountDEC</t>
+          <t>Current Account s.aDEC</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>€30B</t>
+        </is>
+      </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>€32B</t>
+          <t>€30B</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -5557,18 +5561,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Current Account s.aDEC</t>
+          <t>Current AccountDEC</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>€30B</t>
-        </is>
-      </c>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>€30B</t>
+          <t>€32B</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -5583,21 +5583,17 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Current AccountDEC</t>
+          <t>4-Year Treasury Gilt Auction</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>€ 3780M</t>
-        </is>
-      </c>
+      <c r="F180" t="inlineStr"/>
       <c r="G180" t="n">
         <v>3</v>
       </c>
@@ -5610,17 +5606,21 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>4-Year Treasury Gilt Auction</t>
+          <t>Current AccountDEC</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>€ 3780M</t>
+        </is>
+      </c>
       <c r="G181" t="n">
         <v>3</v>
       </c>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -5876,7 +5876,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -5899,18 +5899,18 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
-          <t>1.39M</t>
+          <t>1.45M</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -5930,18 +5930,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
-      <c r="E194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="G194" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195">
@@ -5957,14 +5961,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -5984,22 +5988,18 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197">
@@ -6242,14 +6242,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -6269,14 +6269,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -6450,22 +6450,18 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Employment ChangeJAN</t>
+          <t>Part Time Employment ChgJAN</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>20K</t>
-        </is>
-      </c>
+      <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
-          <t>23.0K</t>
+          <t>-10.0K</t>
         </is>
       </c>
       <c r="G214" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="215">
@@ -6508,18 +6504,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Part Time Employment ChgJAN</t>
+          <t>Employment ChangeJAN</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
-      <c r="E216" t="inlineStr"/>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>20K</t>
+        </is>
+      </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>-10.0K</t>
+          <t>23.0K</t>
         </is>
       </c>
       <c r="G216" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="217">
@@ -6584,19 +6584,19 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Current AccountQ4</t>
+          <t>Leading Indicator MoMJAN</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
-          <t>$ -0.6B</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -6611,17 +6611,21 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>M2 Money Supply YoYJAN</t>
+          <t>Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr"/>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
       <c r="G220" t="n">
         <v>3</v>
       </c>
@@ -6634,19 +6638,19 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Leading Indicator MoMJAN</t>
+          <t>Current AccountQ4</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>$ -0.6B</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -6661,21 +6665,17 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Consumer ConfidenceJAN</t>
+          <t>M2 Money Supply YoYJAN</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr"/>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>85.5</t>
-        </is>
-      </c>
+      <c r="F222" t="inlineStr"/>
       <c r="G222" t="n">
         <v>3</v>
       </c>
@@ -6715,27 +6715,23 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+      <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G224" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="225">
@@ -6746,23 +6742,27 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Consumer ConfidenceFEB</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
-      <c r="E225" t="inlineStr"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G225" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="226">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>3-Year OAT Auction</t>
+          <t>5-Year OAT Auction</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>4-Year OAT Auction</t>
+          <t>3-Year OAT Auction</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
@@ -6947,7 +6947,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>5-Year OAT Auction</t>
+          <t>4-Year OAT Auction</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -6965,21 +6965,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Building Permits YoYDEC</t>
+          <t>7-Year OATi Auction</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>18.0%</t>
-        </is>
-      </c>
+      <c r="F234" t="inlineStr"/>
       <c r="G234" t="n">
         <v>3</v>
       </c>
@@ -6992,27 +6988,19 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>CBI Industrial Trends OrdersFEB</t>
+          <t>6-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>-30</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>-25</t>
-        </is>
-      </c>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr"/>
       <c r="G235" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
@@ -7028,7 +7016,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>7-Year OATi Auction</t>
+          <t>18-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -7069,17 +7057,21 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>18-Year Index-Linked OAT Auction</t>
+          <t>Building Permits YoYDEC</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
-      <c r="F238" t="inlineStr"/>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>18.0%</t>
+        </is>
+      </c>
       <c r="G238" t="n">
         <v>3</v>
       </c>
@@ -7092,19 +7084,27 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>6-Year Index-Linked OAT Auction</t>
+          <t>CBI Industrial Trends OrdersFEB</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
-      <c r="E239" t="inlineStr"/>
-      <c r="F239" t="inlineStr"/>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>-30</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>-25</t>
+        </is>
+      </c>
       <c r="G239" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240">
@@ -7197,18 +7197,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
-      <c r="E243" t="inlineStr"/>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G243" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244">
@@ -7224,22 +7228,18 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
+      <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="G244" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="245">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
@@ -7278,7 +7278,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
@@ -7428,14 +7428,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -7886,7 +7886,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
@@ -7932,7 +7932,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
@@ -7955,7 +7955,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
@@ -8001,14 +8001,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr"/>
       <c r="G275" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="276">
@@ -8070,14 +8070,14 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr"/>
       <c r="G278" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="279">
@@ -8235,18 +8235,18 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Australia Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
       <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G285" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="286">
@@ -8289,18 +8289,18 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Services PMI FlashFEB</t>
+          <t>S&amp;P Global Australia Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="G287" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="288">
@@ -8343,18 +8343,18 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
       <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G289" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="290">
@@ -8370,22 +8370,18 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
+      <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G290" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="291">
@@ -8401,18 +8397,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Inflation Rate Ex-Food and Energy YoYJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
-      <c r="E291" t="inlineStr"/>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G291" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="292">
@@ -8428,14 +8428,14 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate Ex-Food and Energy YoYJAN</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -8486,22 +8486,18 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Jibun Bank Manufacturing PMI FlashFEB</t>
+          <t>Jibun Bank Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
+      <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="G294" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="295">
@@ -8544,18 +8540,22 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Jibun Bank Composite PMI FlashFEB</t>
+          <t>Jibun Bank Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D296" t="inlineStr"/>
-      <c r="E296" t="inlineStr"/>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="G296" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="297">
@@ -8566,12 +8566,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2-Year LTN Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -8589,17 +8589,21 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>6-Month LTN Auction</t>
+          <t>Central Government DebtJAN</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr"/>
-      <c r="F298" t="inlineStr"/>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>TRY 9.4T</t>
+        </is>
+      </c>
       <c r="G298" t="n">
         <v>3</v>
       </c>
@@ -8612,12 +8616,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>10-Year NTN-F Auction</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -8635,21 +8639,17 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Central Government DebtJAN</t>
+          <t>2-Year LTN Auction</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr"/>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>TRY 9.4T</t>
-        </is>
-      </c>
+      <c r="F300" t="inlineStr"/>
       <c r="G300" t="n">
         <v>3</v>
       </c>
@@ -8667,7 +8667,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>10-Year NTN-F Auction</t>
+          <t>6-Month LTN Auction</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -8690,14 +8690,14 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>HSBC Composite PMI FlashFEB</t>
+          <t>HSBC Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -8717,14 +8717,14 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>HSBC Manufacturing PMI FlashFEB</t>
+          <t>HSBC Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -8802,18 +8802,22 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
-      <c r="E306" t="inlineStr"/>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G306" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="307">
@@ -8856,22 +8860,18 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales ex Fuel MoMJAN</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
-      <c r="E308" t="inlineStr">
+      <c r="E308" t="inlineStr"/>
+      <c r="F308" t="inlineStr">
         <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
       <c r="G308" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="309">
@@ -8887,18 +8887,18 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Retail Sales ex Fuel MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G309" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="310">
@@ -8914,18 +8914,18 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Business ConfidenceFEB</t>
+          <t>Business Climate IndicatorFEB</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>92</t>
         </is>
       </c>
       <c r="G310" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311">
@@ -8941,18 +8941,18 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Business Climate IndicatorFEB</t>
+          <t>Business ConfidenceFEB</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>94</t>
         </is>
       </c>
       <c r="G311" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="312">
@@ -8991,18 +8991,14 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
+      <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -9022,14 +9018,18 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
-      <c r="E314" t="inlineStr"/>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -9080,22 +9080,22 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="G316" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317">
@@ -9111,22 +9111,18 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>45.5</t>
-        </is>
-      </c>
+      <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="G317" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="318">
@@ -9142,14 +9138,18 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
-      <c r="E318" t="inlineStr"/>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G318" t="n">
@@ -9164,27 +9164,27 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G319" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="320">
@@ -9195,27 +9195,27 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="G320" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="321">
@@ -9226,19 +9226,23 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
-      <c r="E321" t="inlineStr"/>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
+      </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="G321" t="n">
@@ -9253,23 +9257,19 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
-      <c r="E322" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
+      <c r="E322" t="inlineStr"/>
       <c r="F322" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -9284,27 +9284,27 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G323" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="324">
@@ -9315,27 +9315,27 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G324" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="325">
@@ -9413,18 +9413,22 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D327" t="inlineStr"/>
-      <c r="E327" t="inlineStr"/>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>48.5</t>
+        </is>
+      </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G327" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328">
@@ -9440,22 +9444,18 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>48.5</t>
-        </is>
-      </c>
+      <c r="E328" t="inlineStr"/>
       <c r="F328" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>51</t>
         </is>
       </c>
       <c r="G328" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="329">
@@ -9517,22 +9517,18 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ FinalQ4</t>
+          <t>Economic Activity MoMDEC</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
+      <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G331" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="332">
@@ -9548,18 +9544,18 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>GDP Growth Rate YoY FinalQ4</t>
+          <t>GDP Growth Rate QoQ FinalQ4</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="G332" t="n">
@@ -9579,18 +9575,22 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Economic Activity MoMDEC</t>
+          <t>GDP Growth Rate YoY FinalQ4</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
-      <c r="E333" t="inlineStr"/>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G333" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -9633,22 +9633,18 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="E335" t="inlineStr"/>
       <c r="F335" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G335" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="336">
@@ -9664,18 +9660,14 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Retail Sales MoM FinalDEC</t>
+          <t>Retail Sales MoM PrelJAN</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+      <c r="E336" t="inlineStr"/>
       <c r="F336" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="G336" t="n">
@@ -9695,14 +9687,18 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Retail Sales MoM PrelJAN</t>
+          <t>Retail Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
-      <c r="E337" t="inlineStr"/>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="G337" t="n">
@@ -9722,18 +9718,22 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="D338" t="inlineStr"/>
-      <c r="E338" t="inlineStr"/>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G338" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="339">
@@ -9772,7 +9772,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
@@ -9826,7 +9826,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
@@ -9853,18 +9853,22 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
-      <c r="E343" t="inlineStr"/>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>4.17M</t>
+        </is>
+      </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="G343" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344">
@@ -9880,22 +9884,22 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="G344" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -9911,18 +9915,18 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="G345" t="n">
@@ -9942,18 +9946,18 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G346" t="n">
@@ -9973,18 +9977,14 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
-      <c r="E347" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
+      <c r="E347" t="inlineStr"/>
       <c r="F347" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="G347" t="n">
@@ -10004,22 +10004,22 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
       <c r="E348" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="G348" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="349">
@@ -10035,18 +10035,18 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G349" t="n">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="D352" t="inlineStr"/>
@@ -10130,21 +10130,17 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>FDI (YTD) YoYJAN</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr"/>
-      <c r="F353" t="inlineStr">
-        <is>
-          <t>-18.0%</t>
-        </is>
-      </c>
+      <c r="F353" t="inlineStr"/>
       <c r="G353" t="n">
         <v>3</v>
       </c>
@@ -10157,17 +10153,21 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>FDI (YTD) YoYJAN</t>
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr"/>
-      <c r="F354" t="inlineStr"/>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>-18.0%</t>
+        </is>
+      </c>
       <c r="G354" t="n">
         <v>3</v>
       </c>
@@ -10224,21 +10224,17 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>5-Year KTB Auction</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr"/>
-      <c r="F357" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
+      <c r="F357" t="inlineStr"/>
       <c r="G357" t="n">
         <v>3</v>
       </c>
@@ -10251,17 +10247,21 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>5-Year KTB Auction</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D358" t="inlineStr"/>
       <c r="E358" t="inlineStr"/>
-      <c r="F358" t="inlineStr"/>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>2.0%</t>
+        </is>
+      </c>
       <c r="G358" t="n">
         <v>3</v>
       </c>
@@ -10306,14 +10306,14 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
       <c r="E360" t="inlineStr"/>
       <c r="F360" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="G360" t="n">
@@ -10379,18 +10379,18 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Ifo Business ClimateFEB</t>
+          <t>Ifo Current ConditionsFEB</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr"/>
       <c r="F363" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="G363" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="364">
@@ -10406,18 +10406,18 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Ifo Current ConditionsFEB</t>
+          <t>Ifo Business ClimateFEB</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G364" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="365">
@@ -10491,18 +10491,18 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Core Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G367" t="n">
@@ -10553,18 +10553,18 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="G369" t="n">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>9-Month Bubill Auction</t>
+          <t>3-Month Bubill Auction</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>3-Month Bubill Auction</t>
+          <t>9-Month Bubill Auction</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
@@ -10676,7 +10676,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Mid-month Core Inflation Rate YoYFEB</t>
+          <t>Mid-month Inflation Rate YoYFEB</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Mid-month Inflation Rate YoYFEB</t>
+          <t>Mid-month Core Inflation Rate YoYFEB</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>12-Month BTF Auction</t>
+          <t>3-Month BTF Auction</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
@@ -10837,7 +10837,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>3-Month BTF Auction</t>
+          <t>6-Month BTF Auction</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>6-Month BTF Auction</t>
+          <t>12-Month BTF Auction</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -11071,14 +11071,14 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>Balance of TradeDEC</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
       <c r="E391" t="inlineStr"/>
       <c r="F391" t="inlineStr">
         <is>
-          <t>SAR 60.5B</t>
+          <t>SAR 34B</t>
         </is>
       </c>
       <c r="G391" t="n">
@@ -11098,14 +11098,14 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="D392" t="inlineStr"/>
       <c r="E392" t="inlineStr"/>
       <c r="F392" t="inlineStr">
         <is>
-          <t>SAR 94.5B</t>
+          <t>SAR 60.5B</t>
         </is>
       </c>
       <c r="G392" t="n">
@@ -11125,14 +11125,14 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="D393" t="inlineStr"/>
       <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr">
         <is>
-          <t>SAR 34B</t>
+          <t>SAR 94.5B</t>
         </is>
       </c>
       <c r="G393" t="n">
@@ -11147,19 +11147,23 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>New Car Registrations YoYJAN</t>
+          <t>Leading Business Cycle Indicator MoMDEC</t>
         </is>
       </c>
       <c r="D394" t="inlineStr"/>
       <c r="E394" t="inlineStr"/>
-      <c r="F394" t="inlineStr"/>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="G394" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="395">
@@ -11175,7 +11179,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ FinalQ4</t>
+          <t>GDP Growth Rate YoY FinalQ4</t>
         </is>
       </c>
       <c r="D395" t="inlineStr"/>
@@ -11206,7 +11210,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>GDP Growth Rate YoY FinalQ4</t>
+          <t>GDP Growth Rate QoQ FinalQ4</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
@@ -11232,23 +11236,19 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Leading Business Cycle Indicator MoMDEC</t>
+          <t>New Car Registrations YoYJAN</t>
         </is>
       </c>
       <c r="D397" t="inlineStr"/>
       <c r="E397" t="inlineStr"/>
-      <c r="F397" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="F397" t="inlineStr"/>
       <c r="G397" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="398">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>BTP€i Auction</t>
+          <t>2-Year BTP Short Term Auction</t>
         </is>
       </c>
       <c r="D399" t="inlineStr"/>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>2-Year BTP Short Term Auction</t>
+          <t>BTP€i Auction</t>
         </is>
       </c>
       <c r="D400" t="inlineStr"/>
@@ -11533,7 +11533,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="D409" t="inlineStr"/>
@@ -11556,18 +11556,14 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="D410" t="inlineStr"/>
       <c r="E410" t="inlineStr"/>
-      <c r="F410" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="F410" t="inlineStr"/>
       <c r="G410" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="411">
@@ -11583,7 +11579,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="D411" t="inlineStr"/>
@@ -11601,17 +11597,21 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>Negotiated Wage GrowthQ4</t>
         </is>
       </c>
       <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
       <c r="G412" t="n">
         <v>3</v>
       </c>
@@ -11629,14 +11629,18 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="D413" t="inlineStr"/>
       <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="G413" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="414">
@@ -11647,22 +11651,164 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Negotiated Wage GrowthQ4</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="D414" t="inlineStr"/>
       <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr">
+      <c r="F414" t="inlineStr"/>
+      <c r="G414" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2025-02-25 10:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2025-02-25 10:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Current AccountQ4</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr"/>
+      <c r="E416" t="inlineStr"/>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>$ 7500M</t>
+        </is>
+      </c>
+      <c r="G416" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2025-02-25 10:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>CB Consumer ConfidenceFEB</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr"/>
+      <c r="E417" t="inlineStr"/>
+      <c r="F417" t="inlineStr"/>
+      <c r="G417" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2025-02-25 10:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr"/>
+      <c r="E418" t="inlineStr"/>
+      <c r="F418" t="inlineStr"/>
+      <c r="G418" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2025-02-25 10:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr"/>
+      <c r="E419" t="inlineStr"/>
+      <c r="F419" t="inlineStr"/>
+      <c r="G419" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2025-02-25 10:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Negotiated Wage GrowthQ4</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr"/>
+      <c r="E420" t="inlineStr"/>
+      <c r="F420" t="inlineStr">
         <is>
           <t>5.1%</t>
         </is>
       </c>
-      <c r="G414" t="n">
+      <c r="G420" t="n">
         <v>3</v>
       </c>
     </row>

--- a/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G420"/>
+  <dimension ref="A1:G423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -699,22 +699,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -734,22 +734,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -769,22 +769,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -804,22 +804,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Core Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -839,7 +839,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bank Loan Growth YoYJAN/31</t>
+          <t>Deposit Growth YoYJAN/31</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Deposit Growth YoYJAN/31</t>
+          <t>Foreign Exchange ReservesFEB/07</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>$638.26B</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Foreign Exchange ReservesFEB/07</t>
+          <t>Bank Loan Growth YoYJAN/31</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>$638.26B</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1319,27 +1319,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Manufacturing Sales MoM FinalDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1354,27 +1350,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wholesale Sales MoM FinalDEC</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1389,23 +1381,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New Motor Vehicle SalesDEC</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>135.5K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>153K</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1425,26 +1417,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1460,12 +1448,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1475,7 +1463,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -1495,26 +1483,26 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -1530,12 +1518,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1545,7 +1533,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -1565,22 +1553,26 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1591,31 +1583,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>New Motor Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>135.5K</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>153K</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -1626,23 +1614,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Wholesale Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -1657,23 +1649,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Manufacturing Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -1693,22 +1689,26 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1891,26 +1891,26 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Business Inventories MoMDEC</t>
+          <t>Retail Inventories Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -1926,26 +1926,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMDEC</t>
+          <t>Business Inventories MoMDEC</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>-0.1%</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -1984,22 +1984,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -2019,22 +2019,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/14</t>
+          <t>Baker Hughes Total Rigs CountFEB/14</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>588</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/14</t>
+          <t>Baker Hughes Oil Rig CountFEB/14</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>481</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2162,18 +2162,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GDP External Demand QoQ PrelQ4</t>
+          <t>GDP Price Index YoY PrelQ4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -2255,18 +2251,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GDP Price Index YoY PrelQ4</t>
+          <t>GDP Growth Rate QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -2282,22 +2282,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ PrelQ4</t>
+          <t>GDP External Demand QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -2402,22 +2402,18 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Imports YoYJAN</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>$1.91B</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>$2.2B</t>
-        </is>
-      </c>
+          <t>9.95%</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -2433,18 +2429,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Exports YoYJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>6.99%</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
+          <t>$1.91B</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>$2.2B</t>
+        </is>
+      </c>
       <c r="G63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -2460,13 +2460,13 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Imports YoYJAN</t>
+          <t>Exports YoYJAN</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>9.95%</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -2514,18 +2514,18 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -2567,25 +2567,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tertiary Industry Index MoMDEC</t>
+          <t>Eurogroup Meeting</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
         <v>3</v>
       </c>
@@ -2598,17 +2590,25 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Eurogroup Meeting</t>
+          <t>Tertiary Industry Index MoMDEC</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G69" t="n">
         <v>3</v>
       </c>
@@ -2653,18 +2653,18 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -2954,15 +2954,11 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Foreign Securities PurchasesDEC</t>
+          <t>Foreign Securities Purchases by CanadiansDEC</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>C$14.23B</t>
-        </is>
-      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
         <v>3</v>
@@ -2981,11 +2977,15 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Foreign Securities Purchases by CanadiansDEC</t>
+          <t>Foreign Securities PurchasesDEC</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>C$14.23B</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
         <v>3</v>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>3-Month BTF Auction</t>
+          <t>12-Month BTF Auction</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>12-Month BTF Auction</t>
+          <t>3-Month BTF Auction</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -3242,12 +3242,16 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>$-24.0B</t>
+        </is>
+      </c>
       <c r="G94" t="n">
         <v>2</v>
       </c>
@@ -3265,7 +3269,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -3283,21 +3287,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Budget BalanceJAN</t>
+          <t>European Commission Winter Forecasts</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>TRY-150.0B</t>
-        </is>
-      </c>
+      <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
         <v>2</v>
       </c>
@@ -3333,19 +3333,19 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Budget BalanceJAN</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>$-24.0B</t>
+          <t>TRY-150.0B</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -3387,12 +3387,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>European Commission Winter Forecasts</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MAS 12-Week Bill Auction</t>
+          <t>MAS 4-Week Bill Auction</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MAS 4-Week Bill Auction</t>
+          <t>MAS 12-Week Bill Auction</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -3716,22 +3716,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3778,22 +3778,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
@@ -3863,18 +3863,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Labour Productivity QoQ FinalQ3</t>
+          <t>Labour Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -3917,14 +3913,18 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Labour Productivity QoQ PrelQ4</t>
+          <t>Labour Productivity QoQ FinalQ3</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -4074,27 +4074,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CPI Median YoYJAN</t>
+          <t>NY Empire State Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126">
@@ -4105,27 +4105,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexFEB</t>
+          <t>CPI Trimmed-Mean YoYJAN</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127">
@@ -4141,18 +4141,18 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>CPI Trimmed-Mean YoYJAN</t>
+          <t>CPI Median YoYJAN</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -4172,18 +4172,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
@@ -4199,18 +4203,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -4230,18 +4230,18 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -4257,18 +4257,18 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -4549,14 +4549,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144">
@@ -4572,14 +4572,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -4595,22 +4595,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Machinery Orders YoYDEC</t>
+          <t>Imports YoYJAN</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
@@ -4719,22 +4719,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Imports YoYJAN</t>
+          <t>Machinery Orders YoYDEC</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -4935,14 +4935,18 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>PPI Core Output YoYJAN</t>
+          <t>PPI Input MoMJAN</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -4962,14 +4966,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>PPI Core Output MoMJAN</t>
+          <t>PPI Core Output YoYJAN</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -4989,14 +4993,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>PPI Core Output MoMJAN</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -5016,18 +5020,18 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
@@ -5043,18 +5047,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>3.7%</t>
-        </is>
-      </c>
+      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -5074,22 +5074,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -5105,18 +5105,18 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>PPI Input MoMJAN</t>
+          <t>Retail Price Index YoYJAN</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -5163,14 +5163,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Retail Price Index MoMJAN</t>
+          <t>PPI Input YoYJAN</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -5190,18 +5190,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Retail Price Index YoYJAN</t>
+          <t>Retail Price Index MoMJAN</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>3.7%</t>
-        </is>
-      </c>
+      <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -5221,22 +5217,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>PPI Output MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G167" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168">
@@ -5252,14 +5248,18 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>PPI Input YoYJAN</t>
+          <t>PPI Output MoMJAN</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -5337,18 +5337,18 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Lending Facility RateFEB</t>
+          <t>Deposit Facility RateFEB</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -5368,18 +5368,18 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Deposit Facility RateFEB</t>
+          <t>Lending Facility RateFEB</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -5410,7 +5410,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -5426,18 +5426,18 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -5453,18 +5453,18 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -5475,21 +5475,17 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>ECB Non-Monetary Policy Meeting</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>3.6%</t>
-        </is>
-      </c>
+      <c r="F176" t="inlineStr"/>
       <c r="G176" t="n">
         <v>3</v>
       </c>
@@ -5502,19 +5498,23 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>ECB Non-Monetary Policy Meeting</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G177" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="178">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
@@ -5807,14 +5807,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="190">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -5876,14 +5876,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="193">
@@ -5899,22 +5899,18 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="G193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="194">
@@ -5930,18 +5926,18 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
-          <t>1.39M</t>
+          <t>1.45M</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -5961,14 +5957,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -5988,18 +5984,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
-      <c r="E196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="G196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -6065,14 +6065,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -6092,14 +6092,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentFEB/15</t>
+          <t>Stock Investment by ForeignersFEB/15</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Stock Investment by ForeignersFEB/15</t>
+          <t>Foreign Bond InvestmentFEB/15</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -6388,22 +6388,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="G212" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="213">
@@ -6419,18 +6419,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Part Time Employment ChgJAN</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>67.1%</t>
-        </is>
-      </c>
+      <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>-10.0K</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -6450,18 +6446,18 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Part Time Employment ChgJAN</t>
+          <t>Full Time Employment ChgJAN</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
-          <t>-10.0K</t>
+          <t>33.0K</t>
         </is>
       </c>
       <c r="G214" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="215">
@@ -6477,14 +6473,18 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Full Time Employment ChgJAN</t>
+          <t>Employment ChangeJAN</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
-      <c r="E215" t="inlineStr"/>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>20K</t>
+        </is>
+      </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>33.0K</t>
+          <t>23.0K</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Employment ChangeJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr">
         <is>
-          <t>20K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>23.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
@@ -6535,14 +6535,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Loan Prime Rate 5YFEB</t>
+          <t>Loan Prime Rate 1Y</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -6562,14 +6562,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Loan Prime Rate 1Y</t>
+          <t>Loan Prime Rate 5YFEB</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -6584,19 +6584,19 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Leading Indicator MoMJAN</t>
+          <t>Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -6611,19 +6611,19 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Consumer ConfidenceJAN</t>
+          <t>Leading Indicator MoMJAN</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -6643,16 +6643,12 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Current AccountQ4</t>
+          <t>M2 Money Supply YoYJAN</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr"/>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>$ -0.6B</t>
-        </is>
-      </c>
+      <c r="F221" t="inlineStr"/>
       <c r="G221" t="n">
         <v>3</v>
       </c>
@@ -6670,12 +6666,16 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>M2 Money Supply YoYJAN</t>
+          <t>Current AccountQ4</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr"/>
-      <c r="F222" t="inlineStr"/>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>$ -0.6B</t>
+        </is>
+      </c>
       <c r="G222" t="n">
         <v>3</v>
       </c>
@@ -6805,7 +6805,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>3-Year Bonos Auction</t>
+          <t>8-Year Obligacion Auction</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>5-Year Bonos Auction</t>
+          <t>3-Year Bonos Auction</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>8-Year Obligacion Auction</t>
+          <t>5-Year Bonos Auction</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
@@ -6869,21 +6869,17 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Construction Output YoYDEC</t>
+          <t>5-Year OAT Auction</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr"/>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
+      <c r="F230" t="inlineStr"/>
       <c r="G230" t="n">
         <v>3</v>
       </c>
@@ -6901,7 +6897,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>5-Year OAT Auction</t>
+          <t>4-Year OAT Auction</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
@@ -6942,17 +6938,21 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>4-Year OAT Auction</t>
+          <t>Construction Output YoYDEC</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr"/>
-      <c r="F233" t="inlineStr"/>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
       <c r="G233" t="n">
         <v>3</v>
       </c>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>7-Year OATi Auction</t>
+          <t>6-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6993,7 +6993,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>6-Year Index-Linked OAT Auction</t>
+          <t>18-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>18-Year Index-Linked OAT Auction</t>
+          <t>11-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>11-Year Index-Linked OAT Auction</t>
+          <t>7-Year OATi Auction</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -7057,23 +7057,27 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Building Permits YoYDEC</t>
+          <t>CBI Industrial Trends OrdersFEB</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
-      <c r="E238" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>-30</t>
+        </is>
+      </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>-25</t>
         </is>
       </c>
       <c r="G238" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239">
@@ -7084,27 +7088,23 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>CBI Industrial Trends OrdersFEB</t>
+          <t>Building Permits YoYDEC</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>-30</t>
-        </is>
-      </c>
+      <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
-          <t>-25</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="G239" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="240">
@@ -7143,14 +7143,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -7170,14 +7170,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
@@ -7278,12 +7278,16 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr"/>
-      <c r="F246" t="inlineStr"/>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="G246" t="n">
         <v>3</v>
       </c>
@@ -7301,7 +7305,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
@@ -7324,7 +7328,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
@@ -7347,7 +7351,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
@@ -7370,22 +7374,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr"/>
       <c r="G250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -7423,19 +7419,19 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Raw Materials Prices MoMJAN</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -7450,23 +7446,27 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
-      <c r="E253" t="inlineStr"/>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -7509,18 +7509,18 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>New Housing Price Index YoYJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
@@ -7536,14 +7536,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>New Housing Price Index MoMJAN</t>
+          <t>New Housing Price Index YoYJAN</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -7563,18 +7563,18 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Raw Materials Prices MoMJAN</t>
+          <t>New Housing Price Index MoMJAN</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G257" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="258">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
@@ -7932,7 +7932,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
@@ -8235,14 +8235,14 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Services PMI FlashFEB</t>
+          <t>S&amp;P Global Australia Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
       <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -8262,14 +8262,14 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Australia Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -8370,18 +8370,18 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate Ex-Food and Energy YoYJAN</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G290" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="291">
@@ -8428,18 +8428,18 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Inflation Rate Ex-Food and Energy YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G292" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="293">
@@ -8486,18 +8486,18 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Jibun Bank Composite PMI FlashFEB</t>
+          <t>Jibun Bank Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G294" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="295">
@@ -8513,14 +8513,18 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Jibun Bank Services PMI FlashFEB</t>
+          <t>Jibun Bank Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
-      <c r="E295" t="inlineStr"/>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -8540,22 +8544,18 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Jibun Bank Manufacturing PMI FlashFEB</t>
+          <t>Jibun Bank Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D296" t="inlineStr"/>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
+      <c r="E296" t="inlineStr"/>
       <c r="F296" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="G296" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="297">
@@ -8566,12 +8566,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month LTN Auction</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -8589,21 +8589,17 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Central Government DebtJAN</t>
+          <t>2-Year LTN Auction</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr"/>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t>TRY 9.4T</t>
-        </is>
-      </c>
+      <c r="F298" t="inlineStr"/>
       <c r="G298" t="n">
         <v>3</v>
       </c>
@@ -8639,17 +8635,21 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2-Year LTN Auction</t>
+          <t>Central Government DebtJAN</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr"/>
-      <c r="F300" t="inlineStr"/>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>TRY 9.4T</t>
+        </is>
+      </c>
       <c r="G300" t="n">
         <v>3</v>
       </c>
@@ -8662,12 +8662,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>6-Month LTN Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -8690,14 +8690,14 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>HSBC Manufacturing PMI FlashFEB</t>
+          <t>HSBC Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -8717,14 +8717,14 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>HSBC Composite PMI FlashFEB</t>
+          <t>HSBC Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -8744,14 +8744,14 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>HSBC Services PMI FlashFEB</t>
+          <t>HSBC Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -8771,22 +8771,18 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Public Sector Net Borrowing Ex BanksJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>£20.5B</t>
-        </is>
-      </c>
+      <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr">
         <is>
-          <t>£19.0B</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G305" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="306">
@@ -8802,22 +8798,18 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales ex Fuel MoMJAN</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
-      <c r="E306" t="inlineStr">
+      <c r="E306" t="inlineStr"/>
+      <c r="F306" t="inlineStr">
         <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
       <c r="G306" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="307">
@@ -8860,18 +8852,22 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Retail Sales ex Fuel MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
-      <c r="E308" t="inlineStr"/>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G308" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309">
@@ -8887,18 +8883,22 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Public Sector Net Borrowing Ex BanksJAN</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
-      <c r="E309" t="inlineStr"/>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>£20.5B</t>
+        </is>
+      </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>£19.0B</t>
         </is>
       </c>
       <c r="G309" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="310">
@@ -8914,18 +8914,18 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Business Climate IndicatorFEB</t>
+          <t>Business ConfidenceFEB</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>94</t>
         </is>
       </c>
       <c r="G310" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="311">
@@ -8941,18 +8941,18 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Business ConfidenceFEB</t>
+          <t>Business Climate IndicatorFEB</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>92</t>
         </is>
       </c>
       <c r="G311" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="312">
@@ -8991,14 +8991,18 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
-      <c r="E313" t="inlineStr"/>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -9018,18 +9022,14 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
+      <c r="E314" t="inlineStr"/>
       <c r="F314" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -9080,22 +9080,22 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G316" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="317">
@@ -9138,22 +9138,22 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="G318" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319">
@@ -9164,27 +9164,27 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G319" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="320">
@@ -9195,27 +9195,27 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G320" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="321">
@@ -9226,23 +9226,19 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
-      <c r="E321" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
+      <c r="E321" t="inlineStr"/>
       <c r="F321" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G321" t="n">
@@ -9257,23 +9253,27 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
-      <c r="E322" t="inlineStr"/>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G322" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="323">
@@ -9284,27 +9284,27 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="G323" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="324">
@@ -9315,23 +9315,23 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G324" t="n">
@@ -9351,18 +9351,18 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="G325" t="n">
@@ -9382,18 +9382,18 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G326" t="n">
@@ -9413,18 +9413,18 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>51</t>
         </is>
       </c>
       <c r="G327" t="n">
@@ -9799,14 +9799,14 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr"/>
       <c r="F341" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G341" t="n">
@@ -9826,14 +9826,14 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr"/>
       <c r="F342" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G342" t="n">
@@ -9884,18 +9884,18 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G344" t="n">
@@ -9915,18 +9915,18 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="G345" t="n">
@@ -9946,18 +9946,18 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="G346" t="n">
@@ -9977,18 +9977,22 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
-      <c r="E347" t="inlineStr"/>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G347" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="348">
@@ -10035,22 +10039,18 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
-      <c r="E349" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+      <c r="E349" t="inlineStr"/>
       <c r="F349" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="G349" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="350">
@@ -10224,17 +10224,21 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>5-Year KTB Auction</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr"/>
-      <c r="F357" t="inlineStr"/>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>2.0%</t>
+        </is>
+      </c>
       <c r="G357" t="n">
         <v>3</v>
       </c>
@@ -10252,14 +10256,14 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D358" t="inlineStr"/>
       <c r="E358" t="inlineStr"/>
       <c r="F358" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="G358" t="n">
@@ -10274,21 +10278,17 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>5-Year KTB Auction</t>
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
       <c r="E359" t="inlineStr"/>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="F359" t="inlineStr"/>
       <c r="G359" t="n">
         <v>3</v>
       </c>
@@ -10306,14 +10306,14 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
       <c r="E360" t="inlineStr"/>
       <c r="F360" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G360" t="n">
@@ -10333,14 +10333,14 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Capacity UtilizationFEB</t>
+          <t>Business ConfidenceFEB</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
       <c r="E361" t="inlineStr"/>
       <c r="F361" t="inlineStr"/>
       <c r="G361" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="362">
@@ -10356,14 +10356,14 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Business ConfidenceFEB</t>
+          <t>Capacity UtilizationFEB</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr"/>
       <c r="F362" t="inlineStr"/>
       <c r="G362" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="363">
@@ -10406,18 +10406,18 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Ifo Business ClimateFEB</t>
+          <t>Ifo ExpectationsFEB</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="G364" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="365">
@@ -10433,18 +10433,18 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Ifo ExpectationsFEB</t>
+          <t>Ifo Business ClimateFEB</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G365" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="366">
@@ -10460,22 +10460,22 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="G366" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="367">
@@ -10491,18 +10491,18 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoY FinalJAN</t>
+          <t>CPI FinalJAN</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>126.71</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>126.71</t>
         </is>
       </c>
       <c r="G367" t="n">
@@ -10522,22 +10522,22 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>CPI FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr">
         <is>
-          <t>126.71</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>126.71</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G368" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="369">
@@ -10553,18 +10553,18 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Core Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G369" t="n">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Mid-month Inflation Rate YoYFEB</t>
+          <t>Mid-month Core Inflation Rate YoYFEB</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Mid-month Core Inflation Rate YoYFEB</t>
+          <t>Mid-month Inflation Rate MoMFEB</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
@@ -10722,7 +10722,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Mid-month Inflation Rate MoMFEB</t>
+          <t>Mid-month Inflation Rate YoYFEB</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>3-Month BTF Auction</t>
+          <t>6-Month BTF Auction</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
@@ -10837,7 +10837,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>6-Month BTF Auction</t>
+          <t>3-Month BTF Auction</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
@@ -11071,14 +11071,14 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
       <c r="E391" t="inlineStr"/>
       <c r="F391" t="inlineStr">
         <is>
-          <t>SAR 34B</t>
+          <t>SAR 94.5B</t>
         </is>
       </c>
       <c r="G391" t="n">
@@ -11125,14 +11125,14 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
+          <t>Balance of TradeDEC</t>
         </is>
       </c>
       <c r="D393" t="inlineStr"/>
       <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr">
         <is>
-          <t>SAR 94.5B</t>
+          <t>SAR 34B</t>
         </is>
       </c>
       <c r="G393" t="n">
@@ -11355,19 +11355,19 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>CBI Distributive TradesFEB</t>
+          <t>Negotiated Wage GrowthQ4</t>
         </is>
       </c>
       <c r="D402" t="inlineStr"/>
       <c r="E402" t="inlineStr"/>
       <c r="F402" t="inlineStr">
         <is>
-          <t>-26</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="G402" t="n">
@@ -11382,19 +11382,19 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Negotiated Wage GrowthQ4</t>
+          <t>CBI Distributive TradesFEB</t>
         </is>
       </c>
       <c r="D403" t="inlineStr"/>
       <c r="E403" t="inlineStr"/>
       <c r="F403" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>-26</t>
         </is>
       </c>
       <c r="G403" t="n">
@@ -11432,17 +11432,21 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>IPCA mid-month CPI YoYFEB</t>
+          <t>Negotiated Wage GrowthQ4</t>
         </is>
       </c>
       <c r="D405" t="inlineStr"/>
       <c r="E405" t="inlineStr"/>
-      <c r="F405" t="inlineStr"/>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
       <c r="G405" t="n">
         <v>3</v>
       </c>
@@ -11455,21 +11459,17 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Negotiated Wage GrowthQ4</t>
+          <t>IPCA mid-month CPI YoYFEB</t>
         </is>
       </c>
       <c r="D406" t="inlineStr"/>
       <c r="E406" t="inlineStr"/>
-      <c r="F406" t="inlineStr">
-        <is>
-          <t>5.1%</t>
-        </is>
-      </c>
+      <c r="F406" t="inlineStr"/>
       <c r="G406" t="n">
         <v>3</v>
       </c>
@@ -11533,14 +11533,18 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="D409" t="inlineStr"/>
       <c r="E409" t="inlineStr"/>
-      <c r="F409" t="inlineStr"/>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="G409" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="410">
@@ -11551,17 +11555,21 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>Negotiated Wage GrowthQ4</t>
         </is>
       </c>
       <c r="D410" t="inlineStr"/>
       <c r="E410" t="inlineStr"/>
-      <c r="F410" t="inlineStr"/>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
       <c r="G410" t="n">
         <v>3</v>
       </c>
@@ -11579,7 +11587,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="D411" t="inlineStr"/>
@@ -11597,21 +11605,17 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Negotiated Wage GrowthQ4</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr">
-        <is>
-          <t>5.1%</t>
-        </is>
-      </c>
+      <c r="F412" t="inlineStr"/>
       <c r="G412" t="n">
         <v>3</v>
       </c>
@@ -11629,18 +11633,14 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="D413" t="inlineStr"/>
       <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="F413" t="inlineStr"/>
       <c r="G413" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="414">
@@ -11656,7 +11656,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="D414" t="inlineStr"/>
@@ -11697,21 +11697,17 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Current AccountQ4</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr"/>
-      <c r="F416" t="inlineStr">
-        <is>
-          <t>$ 7500M</t>
-        </is>
-      </c>
+      <c r="F416" t="inlineStr"/>
       <c r="G416" t="n">
         <v>3</v>
       </c>
@@ -11729,14 +11725,14 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="inlineStr"/>
       <c r="G417" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="418">
@@ -11747,17 +11743,21 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Negotiated Wage GrowthQ4</t>
         </is>
       </c>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
-      <c r="F418" t="inlineStr"/>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
       <c r="G418" t="n">
         <v>3</v>
       </c>
@@ -11770,17 +11770,21 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Current AccountQ4</t>
         </is>
       </c>
       <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr"/>
-      <c r="F419" t="inlineStr"/>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>$ 7500M</t>
+        </is>
+      </c>
       <c r="G419" t="n">
         <v>3</v>
       </c>
@@ -11793,22 +11797,91 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Negotiated Wage GrowthQ4</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr"/>
-      <c r="F420" t="inlineStr">
+      <c r="F420" t="inlineStr"/>
+      <c r="G420" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2025-02-25 10:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr"/>
+      <c r="E421" t="inlineStr"/>
+      <c r="F421" t="inlineStr"/>
+      <c r="G421" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2025-02-25 10:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Dallas Fed Services IndexFEB</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr"/>
+      <c r="E422" t="inlineStr"/>
+      <c r="F422" t="inlineStr"/>
+      <c r="G422" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2025-02-25 10:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Negotiated Wage GrowthQ4</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr"/>
+      <c r="E423" t="inlineStr"/>
+      <c r="F423" t="inlineStr">
         <is>
           <t>5.1%</t>
         </is>
       </c>
-      <c r="G420" t="n">
+      <c r="G423" t="n">
         <v>3</v>
       </c>
     </row>

--- a/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G423"/>
+  <dimension ref="A1:G426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -699,22 +699,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -734,7 +734,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -769,22 +769,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -804,22 +804,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Core Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -839,22 +839,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Foreign Exchange ReservesFEB/07</t>
+          <t>Deposit Growth YoYJAN/31</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>$638.26B</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Deposit Growth YoYJAN/31</t>
+          <t>Foreign Exchange ReservesFEB/07</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>$638.26B</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1319,31 +1319,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Manufacturing Sales MoM FinalDEC</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1359,26 +1359,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1389,27 +1385,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wholesale Sales MoM FinalDEC</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1429,26 +1421,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1464,12 +1452,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1479,7 +1467,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -1494,23 +1482,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New Motor Vehicle SalesDEC</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>135.5K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>153K</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -1530,12 +1518,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1545,7 +1533,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -1565,22 +1553,26 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1591,23 +1583,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Wholesale Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -1627,22 +1623,26 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1653,23 +1653,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Manufacturing Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -1684,31 +1688,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>New Motor Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>135.5K</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>153K</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/14</t>
+          <t>Baker Hughes Total Rigs CountFEB/14</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>588</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/14</t>
+          <t>Baker Hughes Oil Rig CountFEB/14</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>481</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2131,18 +2131,18 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GDP Private Consumption QoQ PrelQ4</t>
+          <t>GDP Capital Expenditure QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -2162,18 +2162,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GDP Price Index YoY PrelQ4</t>
+          <t>GDP Growth Rate QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -2189,7 +2193,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GDP Capital Expenditure QoQ PrelQ4</t>
+          <t>GDP Growth Annualized PrelQ4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -2200,11 +2204,11 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -2220,22 +2224,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GDP Growth Annualized PrelQ4</t>
+          <t>GDP External Demand QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -2251,22 +2255,18 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ PrelQ4</t>
+          <t>GDP Price Index YoY PrelQ4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -2282,13 +2282,13 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GDP External Demand QoQ PrelQ4</t>
+          <t>GDP Private Consumption QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2313,18 +2313,18 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Non-Oil Exports MoMJAN</t>
+          <t>Non-Oil Exports YoYJAN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -2344,18 +2344,18 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Non-Oil Exports YoYJAN</t>
+          <t>Non-Oil Exports MoMJAN</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -2402,13 +2402,13 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Imports YoYJAN</t>
+          <t>Exports YoYJAN</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>9.95%</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Exports YoYJAN</t>
+          <t>Imports YoYJAN</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>9.95%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -2514,18 +2514,18 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -2545,14 +2545,18 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Wholesale Prices YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -2567,17 +2571,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Eurogroup Meeting</t>
+          <t>Wholesale Prices YoYJAN</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>1.3%</t>
+        </is>
+      </c>
       <c r="G68" t="n">
         <v>3</v>
       </c>
@@ -2590,25 +2598,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tertiary Industry Index MoMDEC</t>
+          <t>Eurogroup Meeting</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
         <v>3</v>
       </c>
@@ -2626,14 +2626,18 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Industrial Production YoY FinalDEC</t>
+          <t>Tertiary Industry Index MoMDEC</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -2648,23 +2652,19 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Industrial Production YoY FinalDEC</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2769,10 +2769,14 @@
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>€4.35B</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>€ -4.9B</t>
+          <t>€4.5B</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -2787,7 +2791,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2796,14 +2800,10 @@
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>€4.35B</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>€4.5B</t>
+          <t>€ -4.9B</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -2954,11 +2954,15 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Foreign Securities Purchases by CanadiansDEC</t>
+          <t>Foreign Securities PurchasesDEC</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>C$14.23B</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
         <v>3</v>
@@ -2977,15 +2981,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Foreign Securities PurchasesDEC</t>
+          <t>Foreign Securities Purchases by CanadiansDEC</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>C$14.23B</t>
-        </is>
-      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
         <v>3</v>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>12-Month BTF Auction</t>
+          <t>6-Month BTF Auction</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>6-Month BTF Auction</t>
+          <t>12-Month BTF Auction</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -3214,17 +3214,21 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ECOFIN Meeting</t>
+          <t>Budget BalanceJAN</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>TRY-150.0B</t>
+        </is>
+      </c>
       <c r="G93" t="n">
         <v>2</v>
       </c>
@@ -3333,21 +3337,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Budget BalanceJAN</t>
+          <t>ECOFIN Meeting</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>TRY-150.0B</t>
-        </is>
-      </c>
+      <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
         <v>2</v>
       </c>
@@ -3387,17 +3387,21 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>Auto Production YoYJAN</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="G100" t="n">
         <v>2</v>
       </c>
@@ -3410,12 +3414,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>RBA Press Conference</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -3433,21 +3437,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Auto Production YoYJAN</t>
+          <t>RBA Press Conference</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="F102" t="inlineStr"/>
       <c r="G102" t="n">
         <v>2</v>
       </c>
@@ -3511,22 +3511,18 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>HMRC Payrolls ChangeJAN</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>-55.0K</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -3542,22 +3538,18 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Average Earnings incl. Bonus (3Mo/Yr)DEC</t>
+          <t>Average Earnings excl. Bonus (3Mo/Yr)DEC</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr">
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
         <is>
           <t>5.9%</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>5.9%</t>
-        </is>
-      </c>
       <c r="G106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3600,18 +3592,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Average Earnings excl. Bonus (3Mo/Yr)DEC</t>
+          <t>Average Earnings incl. Bonus (3Mo/Yr)DEC</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>5.9%</t>
+        </is>
+      </c>
       <c r="F108" t="inlineStr">
         <is>
           <t>5.9%</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3627,18 +3623,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>HMRC Payrolls ChangeJAN</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>4.5%</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>-55.0K</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3685,22 +3685,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -3716,18 +3716,18 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -3747,22 +3747,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
@@ -3778,18 +3778,18 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -3809,18 +3809,18 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Unemployed PersonsQ4</t>
+          <t>Unemployment RateQ4</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>8.1M</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
@@ -3836,18 +3836,18 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Unemployment RateQ4</t>
+          <t>Unemployed PersonsQ4</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>8.1M</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
@@ -3863,14 +3863,18 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Labour Productivity QoQ PrelQ4</t>
+          <t>Labour Productivity QoQ FinalQ3</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -3890,14 +3894,18 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>BoE Gov Bailey Speech</t>
+          <t>Labour Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="G118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119">
@@ -3913,22 +3921,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Labour Productivity QoQ FinalQ3</t>
+          <t>BoE Gov Bailey Speech</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
       <c r="G119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
@@ -3939,23 +3939,19 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ZEW Economic Sentiment IndexFEB</t>
+          <t>40-Year Treasury Gilt Auction</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="F120" t="inlineStr"/>
       <c r="G120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121">
@@ -3966,7 +3962,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3975,18 +3971,14 @@
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr">
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="G121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
@@ -4002,22 +3994,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ZEW Current ConditionsFEB</t>
+          <t>ZEW Economic Sentiment IndexFEB</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>-89</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>-89</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -4028,17 +4020,25 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>40-Year Treasury Gilt Auction</t>
+          <t>ZEW Current ConditionsFEB</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>-89</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>-89</t>
+        </is>
+      </c>
       <c r="G123" t="n">
         <v>3</v>
       </c>
@@ -4172,22 +4172,18 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
@@ -4257,18 +4253,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
@@ -4333,19 +4333,19 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bundesbank Balz Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
@@ -4356,19 +4356,19 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Bundesbank Balz Speech</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
@@ -4453,14 +4453,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140">
@@ -4476,14 +4476,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141">
@@ -4549,14 +4549,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144">
@@ -4572,14 +4572,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
@@ -4935,18 +4935,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>PPI Input MoMJAN</t>
+          <t>PPI Core Output YoYJAN</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -4966,14 +4962,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>PPI Core Output YoYJAN</t>
+          <t>PPI Core Output MoMJAN</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -4993,14 +4989,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>PPI Core Output MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -5020,18 +5016,18 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="G160" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
@@ -5047,14 +5043,18 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>3.7%</t>
+        </is>
+      </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -5074,22 +5074,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
@@ -5105,18 +5105,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Retail Price Index YoYJAN</t>
+          <t>Retail Price Index MoMJAN</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>3.7%</t>
-        </is>
-      </c>
+      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -5136,14 +5132,18 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>PPI Output YoYJAN</t>
+          <t>PPI Input MoMJAN</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -5163,14 +5163,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>PPI Input YoYJAN</t>
+          <t>PPI Output YoYJAN</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -5190,14 +5190,18 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Retail Price Index MoMJAN</t>
+          <t>Retail Price Index YoYJAN</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>3.7%</t>
+        </is>
+      </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -5217,22 +5221,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>PPI Output MoMJAN</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G167" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168">
@@ -5248,18 +5252,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>PPI Output MoMJAN</t>
+          <t>PPI Input YoYJAN</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -5337,18 +5337,18 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Deposit Facility RateFEB</t>
+          <t>Lending Facility RateFEB</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -5368,18 +5368,18 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Lending Facility RateFEB</t>
+          <t>Deposit Facility RateFEB</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -5399,18 +5399,18 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -5453,18 +5453,18 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -5475,19 +5475,23 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>ECB Non-Monetary Policy Meeting</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -5498,23 +5502,19 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>ECB Non-Monetary Policy Meeting</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="F177" t="inlineStr"/>
       <c r="G177" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178">
@@ -5530,18 +5530,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Current Account s.aDEC</t>
+          <t>Current AccountDEC</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>€30B</t>
-        </is>
-      </c>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>€30B</t>
+          <t>€32B</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -5561,14 +5557,18 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Current AccountDEC</t>
+          <t>Current Account s.aDEC</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>€30B</t>
+        </is>
+      </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>€32B</t>
+          <t>€30B</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -5583,17 +5583,21 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>4-Year Treasury Gilt Auction</t>
+          <t>Current AccountDEC</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>€ 3780M</t>
+        </is>
+      </c>
       <c r="G180" t="n">
         <v>3</v>
       </c>
@@ -5606,21 +5610,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Current AccountDEC</t>
+          <t>4-Year Treasury Gilt Auction</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>€ 3780M</t>
-        </is>
-      </c>
+      <c r="F181" t="inlineStr"/>
       <c r="G181" t="n">
         <v>3</v>
       </c>
@@ -5661,14 +5661,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -5688,14 +5688,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -5784,14 +5784,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -5876,14 +5876,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="193">
@@ -5899,14 +5899,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -5926,22 +5926,18 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="G194" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="195">
@@ -5957,18 +5953,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
-      <c r="E195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="G195" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196">
@@ -5984,18 +5984,18 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
-          <t>1.39M</t>
+          <t>1.45M</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Stock Investment by ForeignersFEB/15</t>
+          <t>Foreign Bond InvestmentFEB/15</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentFEB/15</t>
+          <t>Stock Investment by ForeignersFEB/15</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -6388,22 +6388,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G212" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213">
@@ -6419,18 +6419,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Part Time Employment ChgJAN</t>
+          <t>Employment ChangeJAN</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>20K</t>
+        </is>
+      </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>-10.0K</t>
+          <t>23.0K</t>
         </is>
       </c>
       <c r="G213" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="214">
@@ -6473,22 +6477,18 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Employment ChangeJAN</t>
+          <t>Part Time Employment ChgJAN</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>20K</t>
-        </is>
-      </c>
+      <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
-          <t>23.0K</t>
+          <t>-10.0K</t>
         </is>
       </c>
       <c r="G215" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="216">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="G216" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="217">
@@ -6584,21 +6584,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Consumer ConfidenceJAN</t>
+          <t>M2 Money Supply YoYJAN</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>85.5</t>
-        </is>
-      </c>
+      <c r="F219" t="inlineStr"/>
       <c r="G219" t="n">
         <v>3</v>
       </c>
@@ -6638,17 +6634,21 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>M2 Money Supply YoYJAN</t>
+          <t>Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr"/>
-      <c r="F221" t="inlineStr"/>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
       <c r="G221" t="n">
         <v>3</v>
       </c>
@@ -6688,19 +6688,19 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -6715,23 +6715,27 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Consumer ConfidenceFEB</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
-      <c r="E224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G224" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="225">
@@ -6747,22 +6751,18 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+      <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G225" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="226">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>8-Year Obligacion Auction</t>
+          <t>3-Year Bonos Auction</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>3-Year Bonos Auction</t>
+          <t>8-Year Obligacion Auction</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>6-Year Index-Linked OAT Auction</t>
+          <t>11-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>11-Year Index-Linked OAT Auction</t>
+          <t>7-Year OATi Auction</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -7034,17 +7034,21 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>7-Year OATi Auction</t>
+          <t>Building Permits YoYDEC</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr"/>
-      <c r="F237" t="inlineStr"/>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>18.0%</t>
+        </is>
+      </c>
       <c r="G237" t="n">
         <v>3</v>
       </c>
@@ -7088,21 +7092,17 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Building Permits YoYDEC</t>
+          <t>6-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>18.0%</t>
-        </is>
-      </c>
+      <c r="F239" t="inlineStr"/>
       <c r="G239" t="n">
         <v>3</v>
       </c>
@@ -7228,16 +7228,12 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr"/>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="F244" t="inlineStr"/>
       <c r="G244" t="n">
         <v>3</v>
       </c>
@@ -7255,12 +7251,16 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr"/>
-      <c r="F245" t="inlineStr"/>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="G245" t="n">
         <v>3</v>
       </c>
@@ -7509,18 +7509,18 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>New Housing Price Index MoMJAN</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -7536,18 +7536,18 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>New Housing Price Index YoYJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G256" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="257">
@@ -7563,14 +7563,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>New Housing Price Index MoMJAN</t>
+          <t>New Housing Price Index YoYJAN</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
@@ -7886,7 +7886,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
@@ -7932,7 +7932,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
@@ -7955,7 +7955,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
@@ -8001,14 +8001,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr"/>
       <c r="G275" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="276">
@@ -8024,14 +8024,14 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr"/>
       <c r="G276" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="277">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
@@ -8207,19 +8207,23 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>S&amp;P Global Australia Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr"/>
-      <c r="F284" t="inlineStr"/>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>50.6</t>
+        </is>
+      </c>
       <c r="G284" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="285">
@@ -8284,23 +8288,19 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Composite PMI FlashFEB</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr"/>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>50.6</t>
-        </is>
-      </c>
+      <c r="F287" t="inlineStr"/>
       <c r="G287" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="288">
@@ -8486,14 +8486,18 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Jibun Bank Services PMI FlashFEB</t>
+          <t>Jibun Bank Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
-      <c r="E294" t="inlineStr"/>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -8513,22 +8517,18 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Jibun Bank Manufacturing PMI FlashFEB</t>
+          <t>Jibun Bank Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
+      <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="G295" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="296">
@@ -8544,18 +8544,18 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Jibun Bank Composite PMI FlashFEB</t>
+          <t>Jibun Bank Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr"/>
       <c r="F296" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G296" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="297">
@@ -8635,21 +8635,17 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Central Government DebtJAN</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr"/>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>TRY 9.4T</t>
-        </is>
-      </c>
+      <c r="F300" t="inlineStr"/>
       <c r="G300" t="n">
         <v>3</v>
       </c>
@@ -8662,17 +8658,21 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>Central Government DebtJAN</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr"/>
-      <c r="F301" t="inlineStr"/>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>TRY 9.4T</t>
+        </is>
+      </c>
       <c r="G301" t="n">
         <v>3</v>
       </c>
@@ -8798,14 +8798,18 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Retail Sales ex Fuel MoMJAN</t>
+          <t>Public Sector Net Borrowing Ex BanksJAN</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
-      <c r="E306" t="inlineStr"/>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>£20.5B</t>
+        </is>
+      </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>£19.0B</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -8825,14 +8829,14 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Retail Sales ex Fuel YoYJAN</t>
+          <t>Retail Sales ex Fuel MoMJAN</t>
         </is>
       </c>
       <c r="D307" t="inlineStr"/>
       <c r="E307" t="inlineStr"/>
       <c r="F307" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -8883,18 +8887,14 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Public Sector Net Borrowing Ex BanksJAN</t>
+          <t>Retail Sales ex Fuel YoYJAN</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>£20.5B</t>
-        </is>
-      </c>
+      <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
         <is>
-          <t>£19.0B</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -9022,14 +9022,18 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
-      <c r="E314" t="inlineStr"/>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -9049,18 +9053,14 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
+      <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -9169,18 +9169,18 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -9200,18 +9200,14 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
+      <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G320" t="n">
@@ -9226,23 +9222,27 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
-      <c r="E321" t="inlineStr"/>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>1.7%</t>
+        </is>
+      </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="G321" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="322">
@@ -9258,22 +9258,22 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="G322" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="323">
@@ -9289,18 +9289,18 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G323" t="n">
@@ -9315,23 +9315,23 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G324" t="n">
@@ -9351,18 +9351,18 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G325" t="n">
@@ -9517,14 +9517,14 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Economic Activity MoMDEC</t>
+          <t>Economic Activity YoYDEC</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G331" t="n">
@@ -9606,14 +9606,14 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Economic Activity YoYDEC</t>
+          <t>Economic Activity MoMDEC</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr"/>
       <c r="F334" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G334" t="n">
@@ -9687,18 +9687,18 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Retail Sales MoM FinalDEC</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G337" t="n">
@@ -9718,18 +9718,18 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Retail Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="G338" t="n">
@@ -9772,7 +9772,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
@@ -9799,14 +9799,14 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr"/>
       <c r="F341" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G341" t="n">
@@ -9826,14 +9826,14 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr"/>
       <c r="F342" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G342" t="n">
@@ -9884,18 +9884,18 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="G344" t="n">
@@ -9915,18 +9915,18 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G345" t="n">
@@ -9946,18 +9946,18 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G346" t="n">
@@ -9977,22 +9977,18 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
-      <c r="E347" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="E347" t="inlineStr"/>
       <c r="F347" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="G347" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="348">
@@ -10008,22 +10004,22 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
       <c r="E348" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="G348" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="349">
@@ -10039,14 +10035,18 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
-      <c r="E349" t="inlineStr"/>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>67.8</t>
+        </is>
+      </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="G349" t="n">
@@ -10130,17 +10130,21 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>FDI (YTD) YoYJAN</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr"/>
-      <c r="F353" t="inlineStr"/>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>-18.0%</t>
+        </is>
+      </c>
       <c r="G353" t="n">
         <v>3</v>
       </c>
@@ -10153,21 +10157,17 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>FDI (YTD) YoYJAN</t>
+          <t>Federal Tax RevenuesJAN</t>
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr"/>
-      <c r="F354" t="inlineStr">
-        <is>
-          <t>-18.0%</t>
-        </is>
-      </c>
+      <c r="F354" t="inlineStr"/>
       <c r="G354" t="n">
         <v>3</v>
       </c>
@@ -10180,12 +10180,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Federal Tax RevenuesJAN</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
@@ -10229,14 +10229,14 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr"/>
       <c r="F357" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G357" t="n">
@@ -10306,14 +10306,14 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
       <c r="E360" t="inlineStr"/>
       <c r="F360" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G360" t="n">
@@ -10406,18 +10406,18 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Ifo ExpectationsFEB</t>
+          <t>Ifo Business ClimateFEB</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G364" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="365">
@@ -10433,18 +10433,18 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Ifo Business ClimateFEB</t>
+          <t>Ifo ExpectationsFEB</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="G365" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="366">
@@ -10522,22 +10522,22 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Core Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G368" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="369">
@@ -10553,22 +10553,22 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G369" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="370">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>3-Month Bubill Auction</t>
+          <t>9-Month Bubill Auction</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>9-Month Bubill Auction</t>
+          <t>3-Month Bubill Auction</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
@@ -10676,7 +10676,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Mid-month Core Inflation Rate YoYFEB</t>
+          <t>Mid-month Core Inflation Rate MoMFEB</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Mid-month Core Inflation Rate MoMFEB</t>
+          <t>Mid-month Core Inflation Rate YoYFEB</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>6-Month BTF Auction</t>
+          <t>12-Month BTF Auction</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>12-Month BTF Auction</t>
+          <t>6-Month BTF Auction</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -10997,12 +10997,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>MAS 12-Week Bill Auction</t>
+          <t>20-Year KTB Auction</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>MAS 4-Week Bill Auction</t>
+          <t>MAS 12-Week Bill Auction</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -11043,12 +11043,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>20-Year KTB Auction</t>
+          <t>MAS 4-Week Bill Auction</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -11071,14 +11071,14 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
+          <t>Balance of TradeDEC</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
       <c r="E391" t="inlineStr"/>
       <c r="F391" t="inlineStr">
         <is>
-          <t>SAR 94.5B</t>
+          <t>SAR 34B</t>
         </is>
       </c>
       <c r="G391" t="n">
@@ -11098,14 +11098,14 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="D392" t="inlineStr"/>
       <c r="E392" t="inlineStr"/>
       <c r="F392" t="inlineStr">
         <is>
-          <t>SAR 60.5B</t>
+          <t>SAR 94.5B</t>
         </is>
       </c>
       <c r="G392" t="n">
@@ -11125,14 +11125,14 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="D393" t="inlineStr"/>
       <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr">
         <is>
-          <t>SAR 34B</t>
+          <t>SAR 60.5B</t>
         </is>
       </c>
       <c r="G393" t="n">
@@ -11147,23 +11147,19 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Leading Business Cycle Indicator MoMDEC</t>
+          <t>New Car Registrations YoYJAN</t>
         </is>
       </c>
       <c r="D394" t="inlineStr"/>
       <c r="E394" t="inlineStr"/>
-      <c r="F394" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="F394" t="inlineStr"/>
       <c r="G394" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="395">
@@ -11205,27 +11201,23 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ FinalQ4</t>
+          <t>Leading Business Cycle Indicator MoMDEC</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
-      <c r="E396" t="inlineStr">
-        <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
+      <c r="E396" t="inlineStr"/>
       <c r="F396" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G396" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="397">
@@ -11236,17 +11228,25 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>New Car Registrations YoYJAN</t>
+          <t>GDP Growth Rate QoQ FinalQ4</t>
         </is>
       </c>
       <c r="D397" t="inlineStr"/>
-      <c r="E397" t="inlineStr"/>
-      <c r="F397" t="inlineStr"/>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
       <c r="G397" t="n">
         <v>2</v>
       </c>
@@ -11259,21 +11259,17 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Negotiated Wage GrowthQ4</t>
+          <t>2-Year BTP Short Term Auction</t>
         </is>
       </c>
       <c r="D398" t="inlineStr"/>
       <c r="E398" t="inlineStr"/>
-      <c r="F398" t="inlineStr">
-        <is>
-          <t>5.1%</t>
-        </is>
-      </c>
+      <c r="F398" t="inlineStr"/>
       <c r="G398" t="n">
         <v>3</v>
       </c>
@@ -11291,7 +11287,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>2-Year BTP Short Term Auction</t>
+          <t>BTP€i Auction</t>
         </is>
       </c>
       <c r="D399" t="inlineStr"/>
@@ -11309,17 +11305,21 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>BTP€i Auction</t>
+          <t>Negotiated Wage GrowthQ4</t>
         </is>
       </c>
       <c r="D400" t="inlineStr"/>
       <c r="E400" t="inlineStr"/>
-      <c r="F400" t="inlineStr"/>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
       <c r="G400" t="n">
         <v>3</v>
       </c>
@@ -11355,19 +11355,19 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Negotiated Wage GrowthQ4</t>
+          <t>CBI Distributive TradesFEB</t>
         </is>
       </c>
       <c r="D402" t="inlineStr"/>
       <c r="E402" t="inlineStr"/>
       <c r="F402" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>-26</t>
         </is>
       </c>
       <c r="G402" t="n">
@@ -11382,19 +11382,19 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>CBI Distributive TradesFEB</t>
+          <t>Negotiated Wage GrowthQ4</t>
         </is>
       </c>
       <c r="D403" t="inlineStr"/>
       <c r="E403" t="inlineStr"/>
       <c r="F403" t="inlineStr">
         <is>
-          <t>-26</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="G403" t="n">
@@ -11409,17 +11409,21 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>IPCA mid-month CPI MoMFEB</t>
+          <t>Negotiated Wage GrowthQ4</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
       <c r="E404" t="inlineStr"/>
-      <c r="F404" t="inlineStr"/>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
       <c r="G404" t="n">
         <v>3</v>
       </c>
@@ -11432,21 +11436,17 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Negotiated Wage GrowthQ4</t>
+          <t>IPCA mid-month CPI YoYFEB</t>
         </is>
       </c>
       <c r="D405" t="inlineStr"/>
       <c r="E405" t="inlineStr"/>
-      <c r="F405" t="inlineStr">
-        <is>
-          <t>5.1%</t>
-        </is>
-      </c>
+      <c r="F405" t="inlineStr"/>
       <c r="G405" t="n">
         <v>3</v>
       </c>
@@ -11464,7 +11464,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>IPCA mid-month CPI YoYFEB</t>
+          <t>IPCA mid-month CPI MoMFEB</t>
         </is>
       </c>
       <c r="D406" t="inlineStr"/>
@@ -11555,21 +11555,17 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Negotiated Wage GrowthQ4</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="D410" t="inlineStr"/>
       <c r="E410" t="inlineStr"/>
-      <c r="F410" t="inlineStr">
-        <is>
-          <t>5.1%</t>
-        </is>
-      </c>
+      <c r="F410" t="inlineStr"/>
       <c r="G410" t="n">
         <v>3</v>
       </c>
@@ -11587,7 +11583,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="D411" t="inlineStr"/>
@@ -11605,17 +11601,21 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>Negotiated Wage GrowthQ4</t>
         </is>
       </c>
       <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
       <c r="G412" t="n">
         <v>3</v>
       </c>
@@ -11633,7 +11633,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="D413" t="inlineStr"/>
@@ -11656,7 +11656,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="D414" t="inlineStr"/>
@@ -11679,14 +11679,14 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="inlineStr"/>
       <c r="G415" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416">
@@ -11702,7 +11702,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="D416" t="inlineStr"/>
@@ -11720,17 +11720,21 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Current AccountQ4</t>
         </is>
       </c>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr"/>
-      <c r="F417" t="inlineStr"/>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>$ 7500M</t>
+        </is>
+      </c>
       <c r="G417" t="n">
         <v>3</v>
       </c>
@@ -11743,21 +11747,17 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Negotiated Wage GrowthQ4</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
-      <c r="F418" t="inlineStr">
-        <is>
-          <t>5.1%</t>
-        </is>
-      </c>
+      <c r="F418" t="inlineStr"/>
       <c r="G418" t="n">
         <v>3</v>
       </c>
@@ -11770,19 +11770,19 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Current AccountQ4</t>
+          <t>Negotiated Wage GrowthQ4</t>
         </is>
       </c>
       <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="inlineStr">
         <is>
-          <t>$ 7500M</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="G419" t="n">
@@ -11802,14 +11802,14 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr"/>
       <c r="F420" t="inlineStr"/>
       <c r="G420" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="421">
@@ -11825,7 +11825,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="D421" t="inlineStr"/>
@@ -11848,7 +11848,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="D422" t="inlineStr"/>
@@ -11885,6 +11885,79 @@
         <v>3</v>
       </c>
     </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2025-02-25 13:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Money SupplyJAN</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr"/>
+      <c r="E424" t="inlineStr"/>
+      <c r="F424" t="inlineStr"/>
+      <c r="G424" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2025-02-25 13:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>5-Year Note Auction</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr"/>
+      <c r="E425" t="inlineStr"/>
+      <c r="F425" t="inlineStr"/>
+      <c r="G425" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2025-02-25 13:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Negotiated Wage GrowthQ4</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr"/>
+      <c r="E426" t="inlineStr"/>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
+      <c r="G426" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/EST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -699,22 +699,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -734,22 +734,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -769,7 +769,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -779,12 +779,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -804,22 +804,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Core Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -839,22 +839,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Foreign Exchange ReservesFEB/07</t>
+          <t>Deposit Growth YoYJAN/31</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>$638.26B</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Deposit Growth YoYJAN/31</t>
+          <t>Foreign Exchange ReservesFEB/07</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>$638.26B</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1319,23 +1319,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New Motor Vehicle SalesDEC</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>135.5K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>153K</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1350,31 +1350,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Manufacturing Sales MoM FinalDEC</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1385,27 +1385,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wholesale Sales MoM FinalDEC</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1425,26 +1421,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1460,12 +1452,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1475,7 +1467,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -1495,26 +1487,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -1530,12 +1518,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1545,7 +1533,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -1565,22 +1553,26 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1591,23 +1583,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Wholesale Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -1622,23 +1618,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Manufacturing Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -1653,31 +1653,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>New Motor Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>135.5K</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>153K</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -1693,22 +1689,26 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/14</t>
+          <t>Baker Hughes Total Rigs CountFEB/14</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>588</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/14</t>
+          <t>Baker Hughes Oil Rig CountFEB/14</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>481</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
